--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -818,7 +818,7 @@
     <comment ref="AM23" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-매출액 × OPM(SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위))</t>
+매출액 × OPM(SLS 코호트 타겟 6.4% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위))</t>
       </text>
     </comment>
     <comment ref="AN23" authorId="0" shapeId="0">
@@ -878,7 +878,7 @@
     <comment ref="AM24" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위)</t>
+SLS 코호트 타겟 6.4% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위)</t>
       </text>
     </comment>
     <comment ref="AN24" authorId="0" shapeId="0">
@@ -896,55 +896,55 @@
     <comment ref="AD25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 36597억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 36598억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AF25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 39826억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 39841억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 43016억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 43046억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 46205억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 46252억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 49361억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 49423억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 52526억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 52603억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 55383억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 55476억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 58117억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 58226억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 60804억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 60929억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1730,61 +1730,61 @@
     <comment ref="AC43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 22649억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억)</t>
+SLS 해양 원화 22654억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억)</t>
       </text>
     </comment>
     <comment ref="AD43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 23617억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억)</t>
+SLS 해양 원화 23840억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억)</t>
       </text>
     </comment>
     <comment ref="AF43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 23104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억)</t>
+SLS 해양 원화 23322억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억)</t>
       </text>
     </comment>
     <comment ref="AG43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 22922억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억)</t>
+SLS 해양 원화 23143억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억)</t>
       </text>
     </comment>
     <comment ref="AH43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 22238억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억)</t>
+SLS 해양 원화 22461억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억)</t>
       </text>
     </comment>
     <comment ref="AI43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 22238억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억)</t>
+SLS 해양 원화 22461억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억)</t>
       </text>
     </comment>
     <comment ref="AK43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 19166억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억)</t>
+SLS 해양 원화 19387억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억)</t>
       </text>
     </comment>
     <comment ref="AL43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 17726억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억)</t>
+SLS 해양 원화 17946억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억)</t>
       </text>
     </comment>
     <comment ref="AM43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 17088억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억)</t>
+SLS 해양 원화 17312억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억)</t>
       </text>
     </comment>
     <comment ref="AN43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-SLS 해양 원화 14568억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억)</t>
+SLS 해양 원화 14791억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억)</t>
       </text>
     </comment>
     <comment ref="AC44" authorId="0" shapeId="0">
@@ -2267,7 +2267,7 @@
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 6.4% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위))
 [ratio]</t>
       </text>
     </comment>
@@ -2422,7 +2422,7 @@
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 6.5% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위)
+        <t>추정: SLS 코호트 타겟 6.4% + 회사 캘리브레이션 +3.6%p(최근 4분기 실측−타겟 중위)
 [yoy]</t>
       </text>
     </comment>
@@ -2440,55 +2440,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 36597억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 36598억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 39826억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 39841억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 43016억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 43046억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 46205억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 46252억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 49361억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 49423억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 52526억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 52603억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 55383억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 55476억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 58117억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 58226억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 60804억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 60929억 × 1.26% − 총차입금 11021억 × 6.95% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4034,61 +4034,61 @@
     </comment>
     <comment ref="AC34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 22649억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억)
+        <t>추정: SLS 해양 원화 22654억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AD34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23617억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억)
+        <t>추정: SLS 해양 원화 23840억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23104억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억)
+        <t>추정: SLS 해양 원화 23322억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 22922억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억)
+        <t>추정: SLS 해양 원화 23143억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 22238억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억)
+        <t>추정: SLS 해양 원화 22461억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 22238억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억)
+        <t>추정: SLS 해양 원화 22461억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19166억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억)
+        <t>추정: SLS 해양 원화 19387억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17726억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억)
+        <t>추정: SLS 해양 원화 17946억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17088억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억)
+        <t>추정: SLS 해양 원화 17312억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN34" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14568억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억)
+        <t>추정: SLS 해양 원화 14791억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억)
 [ratio]</t>
       </text>
     </comment>
@@ -8700,36 +8700,36 @@
         <v/>
       </c>
       <c r="AC21" s="24" t="n">
-        <v>0.282717</v>
+        <v>0.282904</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.225031</v>
+        <v>0.232897</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.180191</v>
+        <v>0.187716</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.054576</v>
+        <v>0.061411</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>-0.012148</v>
+        <v>-0.005687</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>-0.03966</v>
+        <v>-0.039406</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>-0.114966</v>
+        <v>-0.114167</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.152513</v>
+        <v>-0.151531</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.154244</v>
+        <v>-0.15322</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.229752</v>
+        <v>-0.228226</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -8849,7 +8849,7 @@
         <v>0.044639</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.044639</v>
+        <v>0.044638</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
@@ -8859,13 +8859,13 @@
         <v>0.044638</v>
       </c>
       <c r="AG22" s="24" t="n">
+        <v>0.044638</v>
+      </c>
+      <c r="AH22" s="24" t="n">
         <v>0.044639</v>
       </c>
-      <c r="AH22" s="24" t="n">
-        <v>0.044638</v>
-      </c>
       <c r="AI22" s="24" t="n">
-        <v>0.044638</v>
+        <v>0.044639</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
@@ -8875,13 +8875,13 @@
         <v>0.044638</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.044639</v>
+        <v>0.044638</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.044639</v>
+        <v>0.044638</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.044639</v>
+        <v>0.044638</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -9004,39 +9004,39 @@
         <v>0.100055</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.099955</v>
+        <v>0.099755</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.099955</v>
+        <v>0.099755</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.100155</v>
+        <v>0.100055</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.100855</v>
+        <v>0.100655</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.100855</v>
+        <v>0.100655</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
+        <v>0.099855</v>
+      </c>
+      <c r="AL23" s="24" t="n">
         <v>0.100055</v>
       </c>
-      <c r="AL23" s="24" t="n">
+      <c r="AM23" s="24" t="n">
         <v>0.100255</v>
       </c>
-      <c r="AM23" s="24" t="n">
-        <v>0.100455</v>
-      </c>
       <c r="AN23" s="24" t="n">
-        <v>0.102955</v>
+        <v>0.102655</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -9132,33 +9132,33 @@
         <v>0.107301</v>
       </c>
       <c r="AD24" s="24" t="n">
-        <v>-0.042146</v>
+        <v>-0.044061</v>
       </c>
       <c r="AE24" s="25" t="n"/>
       <c r="AF24" s="24" t="n">
-        <v>0.062699</v>
+        <v>0.060574</v>
       </c>
       <c r="AG24" s="24" t="n">
-        <v>-0.003976</v>
+        <v>-0.00497</v>
       </c>
       <c r="AH24" s="24" t="n">
-        <v>0.007992000000000001</v>
+        <v>0.005994</v>
       </c>
       <c r="AI24" s="24" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.009018</v>
       </c>
       <c r="AJ24" s="25" t="n"/>
       <c r="AK24" s="24" t="n">
-        <v>0.001</v>
+        <v>0.001002</v>
       </c>
       <c r="AL24" s="24" t="n">
-        <v>0.000998</v>
+        <v>0</v>
       </c>
       <c r="AM24" s="24" t="n">
-        <v>-0.003964</v>
+        <v>-0.003972</v>
       </c>
       <c r="AN24" s="24" t="n">
-        <v>0.020813</v>
+        <v>0.019861</v>
       </c>
       <c r="AO24" s="25" t="n"/>
     </row>
@@ -9285,32 +9285,32 @@
         <v/>
       </c>
       <c r="AF25" s="29" t="n">
-        <v>-65.77</v>
+        <v>-65.72</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>-55.69</v>
+        <v>-55.6</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>-45.62</v>
+        <v>-45.47</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>-35.65</v>
+        <v>-35.45</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-25.65</v>
+        <v>-25.41</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>-16.63</v>
+        <v>-16.33</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>-7.99</v>
+        <v>-7.65</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -9740,10 +9740,10 @@
         <v/>
       </c>
       <c r="AC28" s="24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AD28" s="24" t="n">
         <v>0.050001</v>
-      </c>
-      <c r="AD28" s="24" t="n">
-        <v>0.05</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE15/subQ!AE14,"")</f>
@@ -9756,10 +9756,10 @@
         <v>0.05</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.05</v>
+        <v>0.050001</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.05</v>
+        <v>0.050001</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
@@ -9772,7 +9772,7 @@
         <v>0.050001</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.050001</v>
+        <v>0.049999</v>
       </c>
       <c r="AN28" s="24" t="n">
         <v>0.049998</v>
@@ -10163,27 +10163,27 @@
         <v>0.004</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AH31" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AI31" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AI31" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AM31" s="29" t="n">
         <v>0</v>
@@ -10291,27 +10291,27 @@
         <v>0.004</v>
       </c>
       <c r="AD32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AE32" s="30" t="n"/>
       <c r="AF32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AG32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH32" s="29" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AI32" s="29" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AI32" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AM32" s="29" t="n">
         <v>0</v>
@@ -10544,36 +10544,36 @@
         <v/>
       </c>
       <c r="AC34" s="24" t="n">
-        <v>0.151837</v>
+        <v>0.151859</v>
       </c>
       <c r="AD34" s="24" t="n">
-        <v>0.135952</v>
+        <v>0.136563</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="24" t="n">
-        <v>0.118234</v>
+        <v>0.118695</v>
       </c>
       <c r="AG34" s="24" t="n">
-        <v>0.105692</v>
+        <v>0.106181</v>
       </c>
       <c r="AH34" s="24" t="n">
-        <v>0.094592</v>
+        <v>0.094912</v>
       </c>
       <c r="AI34" s="24" t="n">
-        <v>0.086677</v>
+        <v>0.08694499999999999</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="24" t="n">
-        <v>0.072003</v>
+        <v>0.072251</v>
       </c>
       <c r="AL34" s="24" t="n">
-        <v>0.064279</v>
+        <v>0.06451</v>
       </c>
       <c r="AM34" s="24" t="n">
-        <v>0.059356</v>
+        <v>0.059572</v>
       </c>
       <c r="AN34" s="24" t="n">
-        <v>0.052456</v>
+        <v>0.052628</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -10672,36 +10672,36 @@
         <v/>
       </c>
       <c r="AC35" s="24" t="n">
-        <v>0.093555</v>
+        <v>0.093569</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>0.088232</v>
+        <v>0.088629</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>0.080098</v>
+        <v>0.080425</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>0.07413</v>
+        <v>0.074494</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>0.06829399999999999</v>
+        <v>0.068552</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>0.06412</v>
+        <v>0.064346</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>0.054394</v>
+        <v>0.054607</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>0.04937</v>
+        <v>0.049572</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>0.046237</v>
+        <v>0.046429</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>0.041374</v>
+        <v>0.041532</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -11324,36 +11324,36 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-0.527174</v>
+        <v>-0.527383</v>
       </c>
       <c r="AD41" s="24" t="n">
-        <v>-0.564638</v>
+        <v>-0.565141</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="24" t="n">
-        <v>-0.6751779999999999</v>
+        <v>-0.675868</v>
       </c>
       <c r="AG41" s="24" t="n">
-        <v>-0.699816</v>
+        <v>-0.7009649999999999</v>
       </c>
       <c r="AH41" s="24" t="n">
-        <v>-0.423077</v>
+        <v>-0.425918</v>
       </c>
       <c r="AI41" s="24" t="n">
-        <v>-0.242634</v>
+        <v>-0.245228</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="24" t="n">
-        <v>-0.046034</v>
+        <v>-0.048971</v>
       </c>
       <c r="AL41" s="24" t="n">
-        <v>0.06962500000000001</v>
+        <v>0.068356</v>
       </c>
       <c r="AM41" s="24" t="n">
-        <v>0.114943</v>
+        <v>0.114792</v>
       </c>
       <c r="AN41" s="24" t="n">
-        <v>0.176964</v>
+        <v>0.175479</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -11472,7 +11472,7 @@
         <v>-0.152672</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>-0.136546</v>
+        <v>-0.140562</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -11589,42 +11589,42 @@
         <v/>
       </c>
       <c r="AC43" s="24" t="n">
-        <v>0.966009</v>
+        <v>0.966013</v>
       </c>
       <c r="AD43" s="24" t="n">
-        <v>0.966955</v>
+        <v>0.967166</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE34/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF43" s="24" t="n">
-        <v>0.96646</v>
+        <v>0.966672</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>0.9662809999999999</v>
+        <v>0.966498</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>0.965591</v>
+        <v>0.965819</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>0.965591</v>
+        <v>0.965819</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ34/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK43" s="24" t="n">
-        <v>0.962103</v>
+        <v>0.962377</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>0.960213</v>
+        <v>0.960515</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>0.959315</v>
+        <v>0.959635</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>0.955327</v>
+        <v>0.955712</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO34/subQ!AO5,"")</f>
@@ -11747,39 +11747,39 @@
         <v>0.100055</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.099955</v>
+        <v>0.099755</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE34,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.099955</v>
+        <v>0.099755</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.100155</v>
+        <v>0.100055</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.100855</v>
+        <v>0.100655</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.100855</v>
+        <v>0.100655</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ34,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
+        <v>0.099855</v>
+      </c>
+      <c r="AL44" s="24" t="n">
         <v>0.100055</v>
       </c>
-      <c r="AL44" s="24" t="n">
+      <c r="AM44" s="24" t="n">
         <v>0.100255</v>
       </c>
-      <c r="AM44" s="24" t="n">
-        <v>0.100455</v>
-      </c>
       <c r="AN44" s="24" t="n">
-        <v>0.102955</v>
+        <v>0.102655</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO34,"")</f>
@@ -11899,42 +11899,42 @@
         <v/>
       </c>
       <c r="AC45" s="24" t="n">
-        <v>0.033991</v>
+        <v>0.033986</v>
       </c>
       <c r="AD45" s="24" t="n">
-        <v>0.033045</v>
+        <v>0.032834</v>
       </c>
       <c r="AE45" s="25">
         <f>IFERROR(subQ!AE36/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.03354</v>
+        <v>0.033327</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.033719</v>
+        <v>0.033502</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.034409</v>
+        <v>0.034181</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.034409</v>
+        <v>0.034181</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.037897</v>
+        <v>0.037623</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.039787</v>
+        <v>0.039485</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.040685</v>
+        <v>0.040365</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.044673</v>
+        <v>0.044288</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO5,"")</f>
@@ -12057,39 +12057,39 @@
         <v>0.100051</v>
       </c>
       <c r="AD46" s="24" t="n">
-        <v>0.099956</v>
+        <v>0.099755</v>
       </c>
       <c r="AE46" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE36,"")</f>
         <v/>
       </c>
       <c r="AF46" s="24" t="n">
-        <v>0.099956</v>
+        <v>0.099755</v>
       </c>
       <c r="AG46" s="24" t="n">
-        <v>0.100156</v>
+        <v>0.100051</v>
       </c>
       <c r="AH46" s="24" t="n">
-        <v>0.100852</v>
+        <v>0.100652</v>
       </c>
       <c r="AI46" s="24" t="n">
-        <v>0.100852</v>
+        <v>0.100652</v>
       </c>
       <c r="AJ46" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ36,"")</f>
         <v/>
       </c>
       <c r="AK46" s="24" t="n">
+        <v>0.099851</v>
+      </c>
+      <c r="AL46" s="24" t="n">
         <v>0.100051</v>
       </c>
-      <c r="AL46" s="24" t="n">
+      <c r="AM46" s="24" t="n">
         <v>0.100252</v>
       </c>
-      <c r="AM46" s="24" t="n">
-        <v>0.100452</v>
-      </c>
       <c r="AN46" s="24" t="n">
-        <v>0.102959</v>
+        <v>0.102654</v>
       </c>
       <c r="AO46" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO36,"")</f>
@@ -38828,7 +38828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV82"/>
+  <dimension ref="A1:AV83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -39519,49 +39519,49 @@
         <v>1567.71</v>
       </c>
       <c r="W5" s="26" t="n">
-        <v>1663.003</v>
+        <v>1663.35</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1754.555</v>
+        <v>1770.503</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1716.412</v>
+        <v>1732.014</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1662.132</v>
+        <v>1677.907</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1592.827</v>
+        <v>1608.775</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1592.827</v>
+        <v>1608.775</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1344.258</v>
+        <v>1360.034</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1242.871</v>
+        <v>1258.647</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1197.427</v>
+        <v>1213.376</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1018.36</v>
+        <v>1034.309</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>695.082</v>
+        <v>710.684</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>542.4880000000001</v>
+        <v>558.263</v>
       </c>
       <c r="AI5" s="26" t="n">
-        <v>415.813</v>
+        <v>431.762</v>
       </c>
       <c r="AJ5" s="26" t="n">
-        <v>241.409</v>
+        <v>257.358</v>
       </c>
       <c r="AK5" s="26" t="n">
-        <v>171.856</v>
+        <v>182.084</v>
       </c>
       <c r="AL5" s="26" t="n">
         <v>173.766</v>
@@ -39582,19 +39582,19 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6299.423</v>
+        <v>6315.718</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6564.198</v>
+        <v>6627.471</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>4802.916</v>
+        <v>4866.366</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>1894.792</v>
+        <v>1958.067</v>
       </c>
       <c r="AV5" s="26" t="n">
-        <v>381.903</v>
+        <v>392.131</v>
       </c>
     </row>
     <row r="6">
@@ -40173,46 +40173,49 @@
         <v>120.258</v>
       </c>
       <c r="W11" s="26" t="n">
-        <v>131.434</v>
+        <v>131.78</v>
       </c>
       <c r="X11" s="26" t="n">
-        <v>131.434</v>
+        <v>147.383</v>
       </c>
       <c r="Y11" s="26" t="n">
-        <v>128.577</v>
+        <v>144.179</v>
       </c>
       <c r="Z11" s="26" t="n">
-        <v>130.005</v>
+        <v>145.781</v>
       </c>
       <c r="AA11" s="26" t="n">
-        <v>131.434</v>
+        <v>147.383</v>
       </c>
       <c r="AB11" s="26" t="n">
-        <v>131.434</v>
+        <v>147.383</v>
       </c>
       <c r="AC11" s="26" t="n">
-        <v>76.93899999999999</v>
+        <v>92.714</v>
       </c>
       <c r="AD11" s="26" t="n">
-        <v>59.109</v>
+        <v>74.884</v>
       </c>
       <c r="AE11" s="26" t="n">
-        <v>59.758</v>
+        <v>75.70699999999999</v>
       </c>
       <c r="AF11" s="26" t="n">
-        <v>59.758</v>
+        <v>75.70699999999999</v>
       </c>
       <c r="AG11" s="26" t="n">
-        <v>38.143</v>
+        <v>53.745</v>
       </c>
       <c r="AH11" s="26" t="n">
-        <v>28.415</v>
+        <v>44.191</v>
       </c>
       <c r="AI11" s="26" t="n">
-        <v>16.305</v>
+        <v>32.253</v>
       </c>
       <c r="AJ11" s="26" t="n">
-        <v>10.811</v>
+        <v>26.759</v>
+      </c>
+      <c r="AK11" s="26" t="n">
+        <v>10.228</v>
       </c>
       <c r="AP11" s="26" t="n">
         <v>3.855</v>
@@ -40221,16 +40224,19 @@
         <v>262.078</v>
       </c>
       <c r="AR11" s="26" t="n">
-        <v>470.781</v>
+        <v>487.076</v>
       </c>
       <c r="AS11" s="26" t="n">
-        <v>521.45</v>
+        <v>584.726</v>
       </c>
       <c r="AT11" s="26" t="n">
-        <v>255.564</v>
+        <v>319.012</v>
       </c>
       <c r="AU11" s="26" t="n">
-        <v>93.67400000000001</v>
+        <v>156.948</v>
+      </c>
+      <c r="AV11" s="26" t="n">
+        <v>10.228</v>
       </c>
     </row>
     <row r="12">
@@ -40506,46 +40512,49 @@
         <v>862.2859999999999</v>
       </c>
       <c r="W14" s="26" t="n">
-        <v>1040.203</v>
+        <v>1040.55</v>
       </c>
       <c r="X14" s="26" t="n">
-        <v>1110.467</v>
+        <v>1126.415</v>
       </c>
       <c r="Y14" s="26" t="n">
-        <v>1086.326</v>
+        <v>1101.928</v>
       </c>
       <c r="Z14" s="26" t="n">
-        <v>1066.044</v>
+        <v>1081.819</v>
       </c>
       <c r="AA14" s="26" t="n">
-        <v>1010.573</v>
+        <v>1026.522</v>
       </c>
       <c r="AB14" s="26" t="n">
-        <v>1010.573</v>
+        <v>1026.522</v>
       </c>
       <c r="AC14" s="26" t="n">
-        <v>928.14</v>
+        <v>943.915</v>
       </c>
       <c r="AD14" s="26" t="n">
-        <v>850.37</v>
+        <v>866.146</v>
       </c>
       <c r="AE14" s="26" t="n">
-        <v>812.949</v>
+        <v>828.897</v>
       </c>
       <c r="AF14" s="26" t="n">
-        <v>635.35</v>
+        <v>651.299</v>
       </c>
       <c r="AG14" s="26" t="n">
-        <v>482.535</v>
+        <v>498.137</v>
       </c>
       <c r="AH14" s="26" t="n">
-        <v>368.722</v>
+        <v>384.497</v>
       </c>
       <c r="AI14" s="26" t="n">
-        <v>240.137</v>
+        <v>256.086</v>
       </c>
       <c r="AJ14" s="26" t="n">
-        <v>65.73399999999999</v>
+        <v>81.68300000000001</v>
+      </c>
+      <c r="AK14" s="26" t="n">
+        <v>10.228</v>
       </c>
       <c r="AO14" s="26" t="n">
         <v>115.297</v>
@@ -40557,16 +40566,19 @@
         <v>1337.908</v>
       </c>
       <c r="AR14" s="26" t="n">
-        <v>3656.535</v>
+        <v>3672.83</v>
       </c>
       <c r="AS14" s="26" t="n">
-        <v>4173.516</v>
+        <v>4236.791</v>
       </c>
       <c r="AT14" s="26" t="n">
-        <v>3226.809</v>
+        <v>3290.257</v>
       </c>
       <c r="AU14" s="26" t="n">
-        <v>1157.128</v>
+        <v>1220.403</v>
+      </c>
+      <c r="AV14" s="26" t="n">
+        <v>10.228</v>
       </c>
     </row>
     <row r="15">
@@ -40860,46 +40872,46 @@
         <v>1443.03</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1441.82</v>
+        <v>1441.62</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1441.82</v>
+        <v>1441.62</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1444.83</v>
+        <v>1444.6</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1447.08</v>
+        <v>1446.81</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1447.08</v>
+        <v>1446.81</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1456.77</v>
+        <v>1456.34</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1457.39</v>
+        <v>1456.92</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1458.7</v>
+        <v>1458.19</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1463.54</v>
+        <v>1462.87</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1472.24</v>
+        <v>1471.08</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1474.28</v>
+        <v>1472.74</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1473.43</v>
+        <v>1471.44</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1489.79</v>
+        <v>1485.45</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1501.75</v>
+        <v>1497.14</v>
       </c>
       <c r="AL17" s="13" t="n">
         <v>1501.75</v>
@@ -41091,49 +41103,49 @@
         <v>1449.63</v>
       </c>
       <c r="W19" s="13" t="n">
-        <v>1436.04</v>
+        <v>1436.03</v>
       </c>
       <c r="X19" s="13" t="n">
-        <v>1415.28</v>
+        <v>1415.14</v>
       </c>
       <c r="Y19" s="13" t="n">
-        <v>1415.28</v>
+        <v>1415.14</v>
       </c>
       <c r="Z19" s="13" t="n">
-        <v>1417.39</v>
+        <v>1417.23</v>
       </c>
       <c r="AA19" s="13" t="n">
-        <v>1418.97</v>
+        <v>1418.78</v>
       </c>
       <c r="AB19" s="13" t="n">
-        <v>1418.97</v>
+        <v>1418.78</v>
       </c>
       <c r="AC19" s="13" t="n">
-        <v>1425.75</v>
+        <v>1425.45</v>
       </c>
       <c r="AD19" s="13" t="n">
-        <v>1426.18</v>
+        <v>1425.85</v>
       </c>
       <c r="AE19" s="13" t="n">
-        <v>1427.1</v>
+        <v>1426.74</v>
       </c>
       <c r="AF19" s="13" t="n">
-        <v>1430.49</v>
+        <v>1430.01</v>
       </c>
       <c r="AG19" s="13" t="n">
-        <v>1436.57</v>
+        <v>1435.77</v>
       </c>
       <c r="AH19" s="13" t="n">
-        <v>1438.01</v>
+        <v>1436.93</v>
       </c>
       <c r="AI19" s="13" t="n">
-        <v>1437.41</v>
+        <v>1436.02</v>
       </c>
       <c r="AJ19" s="13" t="n">
-        <v>1448.86</v>
+        <v>1445.82</v>
       </c>
       <c r="AK19" s="13" t="n">
-        <v>1457.23</v>
+        <v>1454.01</v>
       </c>
       <c r="AL19" s="13" t="n">
         <v>1457.23</v>
@@ -41208,49 +41220,49 @@
         <v>2272592.2</v>
       </c>
       <c r="W20" s="18" t="n">
-        <v>2388135.4</v>
+        <v>2388627.6</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2483183.6</v>
+        <v>2505508.9</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2429201.3</v>
+        <v>2451041.3</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2355892.6</v>
+        <v>2377975.2</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2260166.8</v>
+        <v>2282492.1</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2260166.8</v>
+        <v>2282492.1</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1916574.1</v>
+        <v>1938656.7</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1772559.5</v>
+        <v>1794642.1</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1708846</v>
+        <v>1731171.3</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1456751.1</v>
+        <v>1479076.4</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>998536.3</v>
+        <v>1020376.3</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>780100.2</v>
+        <v>802182.9</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>597692.7</v>
+        <v>620018</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>349768.9</v>
+        <v>372094.1</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>250434.9</v>
+        <v>264752.2</v>
       </c>
       <c r="AL20" s="18" t="n">
         <v>253217.5</v>
@@ -41271,19 +41283,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>9020462</v>
+        <v>9043279.5</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9305427.5</v>
+        <v>9394000.699999999</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>6854730.7</v>
+        <v>6943546.5</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2726098.1</v>
+        <v>2814671.3</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>556522</v>
+        <v>570839.3</v>
       </c>
     </row>
     <row r="21">
@@ -41355,46 +41367,46 @@
         <v>0.06419999999999999</v>
       </c>
       <c r="X21" s="21" t="n">
-        <v>0.0641</v>
+        <v>0.0639</v>
       </c>
       <c r="Y21" s="21" t="n">
-        <v>0.0641</v>
+        <v>0.0639</v>
       </c>
       <c r="Z21" s="21" t="n">
-        <v>0.0643</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="AA21" s="21" t="n">
-        <v>0.065</v>
+        <v>0.0648</v>
       </c>
       <c r="AB21" s="21" t="n">
-        <v>0.065</v>
+        <v>0.0648</v>
       </c>
       <c r="AC21" s="21" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AD21" s="21" t="n">
         <v>0.06419999999999999</v>
       </c>
-      <c r="AD21" s="21" t="n">
+      <c r="AE21" s="21" t="n">
         <v>0.0644</v>
       </c>
-      <c r="AE21" s="21" t="n">
-        <v>0.0646</v>
-      </c>
       <c r="AF21" s="21" t="n">
-        <v>0.06710000000000001</v>
+        <v>0.0668</v>
       </c>
       <c r="AG21" s="21" t="n">
-        <v>0.0629</v>
+        <v>0.0626</v>
       </c>
       <c r="AH21" s="21" t="n">
-        <v>0.066</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="AI21" s="21" t="n">
-        <v>0.0711</v>
+        <v>0.0703</v>
       </c>
       <c r="AJ21" s="21" t="n">
-        <v>0.0864</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="AK21" s="21" t="n">
-        <v>0.1</v>
+        <v>0.09719999999999999</v>
       </c>
       <c r="AL21" s="21" t="n">
         <v>0.1</v>
@@ -44018,49 +44030,101 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
-        </is>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260930800054</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>VLGC</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>307400</v>
+      </c>
+      <c r="E76" t="n">
+        <v>216.522</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1419.72</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2030-02-28</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>③중마진</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>linear_progress</t>
+        </is>
+      </c>
+      <c r="L76" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>⚠ 헤지비율 0.7 은 가정(약정환율 미공시 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
+          <t>⚠ 종료일 = 마지막 호선 인도 예정; 진행률 매출 분기는 계약기간 안에 선형 배분(가정)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>⚠ 공시 통화선도 매도 명목액 25538백만$ 을 현물(2026Q2 기말 1550.89원)로 잔고 대비 환산하면 1.13 — 가정 0.70 과 +0.43 차이. 약정환율 미공시라 적용하지 않음(참고치 hedge.hedge_ratio_implied_spot; 채택은 사용자 결정)</t>
+          <t>⚠ 헤지비율 0.7 은 가정(약정환율 미공시 → 레퍼런스 SLS 시트의 HEDGE 70% 가정. hedge_rate 는 계약별 수주시점 환율로 대체)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 1%, ③중마진 67%, ④호황 31% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
+          <t>⚠ 공시 통화선도 매도 명목액 25538백만$ 을 현물(2026Q2 기말 1550.89원)로 잔고 대비 환산하면 1.13 — 가정 0.70 과 +0.43 차이. 약정환율 미공시라 적용하지 않음(참고치 hedge.hedge_ratio_implied_spot; 채택은 사용자 결정)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>⚠ 스케줄 불가 3건(금액·기간 없음) — contracts[].schedule 비움</t>
+          <t>⚠ 코호트는 원장 내부 상대 등급(신조선가 지수 없음): 2025~ 수주 물량(백만$) 판정 ②BEP 1%, ③중마진 68%, ④호황 31% — 최다 ③중마진. 레퍼런스 HD현대미포 SLS 는 2025~ 물량을 100% ⑤초호황으로 두어 방향이 다르다(2021 이후 절대 호황 수준 미반영). 타겟 OPM 은 회사 calibrated_shift 로 실측 OPM 에 맞추고, 외부 지수 도입은 사용자 결정</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>⚠ 종료일 '-' 3건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+          <t>⚠ 스케줄 불가 3건(금액·기간 없음) — contracts[].schedule 비움</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 종료일 '-' 3건은 같은 선종 계약기간 중위로 종료 추정(end_estimated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>⚠ 정기보고서 부문 매출 3개월분 &gt; 연결 매출(fin) 1분기(2025Q2; 최대 +17.4%) — 부문표가 내부거래 제거 전이거나 파서 문제(yards 레인). reconcile[q].exceeds_consolidated_pct 에 표시, ratio 는 그대로</t>
         </is>
@@ -51540,7 +51604,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1491.6</v>
+        <v>1497.2</v>
       </c>
     </row>
     <row r="30">
@@ -51560,7 +51624,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.07</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="32">
@@ -51580,7 +51644,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
     </row>
     <row r="34">
@@ -51590,7 +51654,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="35">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21315억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21299억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3160억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20823억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3095억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20804억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3093억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20616억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3130억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19908억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3164억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19908억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3164억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16864억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3130억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 16849억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15426억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3130억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 15412억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14764억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3164억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 14751억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12267억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3143억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 12256억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3141억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39016억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39015억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41940억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41937억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45123억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45118억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48564억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48558억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52337억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52329억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 56226억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 56217억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 60341억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 60331억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 64733억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 64722억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39016억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39015억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41940억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41937억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 45123억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 45118억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48564억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48558억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52337억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52329억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 56226억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 56217억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 60341억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 60331억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 64733억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 64722억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21315억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21299억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3160억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20823억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3095억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20804억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3093억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20616억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3130억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19908억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3164억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19908억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3164억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16864억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3130억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 16849억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15426억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3130억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 15412억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14764억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3164억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 14751억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12267억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3143억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 12256억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3141억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,328억(2026 4,208억 · 2027 12,553억 · 2028 12,567억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,208억 vs 688억 · 2027 12,553억 vs 29,126억 · 2028 12,567억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,306억(2026 4,206억 · 2027 12,543억 · 2028 12,557억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,206억 vs 688억 · 2027 12,543억 vs 29,126억 · 2028 12,557억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1364.9</v>
+        <v>1364.3</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.59</v>
+        <v>14.45</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.57</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="33">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2443</v>
+        <v>0.2442</v>
       </c>
     </row>
     <row r="34">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19920</v>
+        <v>19720</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9645,7 +9645,7 @@
         <v>24500</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>19980</v>
+        <v>20150</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19830</v>
+        <v>19793.3</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.00755282</v>
+        <v>-0.010908918</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.003403671</v>
+        <v>0.001944965</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.001758265</v>
+        <v>-0.008914427000000001</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.002535885</v>
+        <v>-0.001749548</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.003559733</v>
+        <v>0.005355309</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.002062563</v>
+        <v>-0.006647515</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.004009801</v>
+        <v>-0.000176559</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.005132949</v>
+        <v>0.005316555</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.004380268</v>
+        <v>-0.001229607</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.003804414</v>
+        <v>-0.001187644</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.00755282</v>
+        <v>-0.010908918</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.00340367</v>
+        <v>0.001944965</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.001758266</v>
+        <v>-0.008914427000000001</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.002535885</v>
+        <v>-0.001749548</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.003559733</v>
+        <v>0.005355309</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.002062563</v>
+        <v>-0.006647515</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.004009801</v>
+        <v>-0.000176559</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.005132949</v>
+        <v>0.005316555</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.004380268</v>
+        <v>-0.001229607</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.003804414</v>
+        <v>-0.001187644</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.133444262</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.119736096</v>
+        <v>0.119676624</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.111707241</v>
+        <v>0.111651652</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.109406412</v>
+        <v>0.109361664</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.106601353</v>
+        <v>0.106567999</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.105646851</v>
+        <v>0.105620669</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.09846561700000001</v>
+        <v>0.098450853</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.094866067</v>
+        <v>0.094857469</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.09247274799999999</v>
+        <v>0.092467902</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086174057</v>
+        <v>0.086174192</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.082222368</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.077267997</v>
+        <v>0.07722989399999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.074928889</v>
+        <v>0.074890017</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.075895948</v>
+        <v>0.07586250999999999</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.076253812</v>
+        <v>0.076226618</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.077701514</v>
+        <v>0.07767911800000001</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.07429791400000001</v>
+        <v>0.074282971</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.073192352</v>
+        <v>0.07318219400000001</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.07278651799999999</v>
+        <v>0.072779316</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.06907343000000001</v>
+        <v>0.069070481</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>9999.694702999999</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>9999.698727999999</v>
+        <v>9999.704301</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>9999.764202</v>
+        <v>9999.769996000001</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>9999.620815</v>
+        <v>9999.619796000001</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>9999.693014</v>
+        <v>9999.691049999999</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>9999.706833</v>
+        <v>9999.704856</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>9999.799932</v>
+        <v>9999.806638</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>9999.699923</v>
+        <v>9999.698839999999</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>9999.766109</v>
+        <v>9999.765604</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>9999.703105000001</v>
+        <v>9999.701638</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.109264784</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.109501694</v>
+        <v>0.109501504</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.109506822</v>
+        <v>0.109506911</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.110644017</v>
+        <v>0.110644083</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.111217855</v>
+        <v>0.111217848</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.1112179</v>
+        <v>0.111217893</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.112086361</v>
+        <v>0.112086524</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.112086512</v>
+        <v>0.112086542</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.112086522</v>
+        <v>0.112086378</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.112086372</v>
+        <v>0.112086499</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,7 +13302,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>19920</v>
+        <v>19720</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.220000130952329</v>
+        <v>0.2200003187628856</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463849128444652</v>
+        <v>0.04463848392545808</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229669863868184</v>
+        <v>0.01229727986048935</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576683800643401</v>
+        <v>0.05576985615712875</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42500,37 +42500,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.032</v>
+        <v>1817.155</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.03</v>
+        <v>1778.152</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.434</v>
+        <v>1724.558</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1655.813</v>
+        <v>1655.938</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1655.813</v>
+        <v>1655.938</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.56</v>
+        <v>1406.684</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.174</v>
+        <v>1305.297</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.414</v>
+        <v>1260.539</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.346</v>
+        <v>1081.471</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>756.677</v>
+        <v>756.799</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.463</v>
+        <v>589.546</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42560,16 +42560,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.297</v>
+        <v>6362.42</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6814.09</v>
+        <v>6814.586</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5053.494</v>
+        <v>5053.991</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.343</v>
+        <v>2035.548</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42644,37 +42644,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1727.896</v>
+        <v>1728.02</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1690.832</v>
+        <v>1690.954</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.266</v>
+        <v>1677.39</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.512</v>
+        <v>1628.637</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.512</v>
+        <v>1628.637</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.56</v>
+        <v>1406.684</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.174</v>
+        <v>1305.297</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.414</v>
+        <v>1260.539</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.346</v>
+        <v>1081.471</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>756.677</v>
+        <v>756.799</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.463</v>
+        <v>589.546</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42704,16 +42704,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6008.662</v>
+        <v>6008.786</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6625.122</v>
+        <v>6625.618</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5053.494</v>
+        <v>5053.991</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.343</v>
+        <v>2035.548</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43118,37 +43118,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>832.701</v>
+        <v>832.824</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.097</v>
+        <v>815.22</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>791.801</v>
+        <v>791.925</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.317</v>
+        <v>733.442</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.317</v>
+        <v>733.442</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.425</v>
+        <v>691.549</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>664.86</v>
+        <v>664.9829999999999</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.4</v>
+        <v>625.525</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>447.801</v>
+        <v>447.926</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.487</v>
+        <v>315.609</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.704</v>
+        <v>199.787</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43160,16 +43160,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.607</v>
+        <v>2583.73</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3073.532</v>
+        <v>3074.029</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2429.486</v>
+        <v>2429.983</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.357</v>
+        <v>595.562</v>
       </c>
     </row>
     <row r="11">
@@ -43430,37 +43430,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1727.896</v>
+        <v>1728.02</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1690.832</v>
+        <v>1690.954</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.266</v>
+        <v>1677.39</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.512</v>
+        <v>1628.637</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.512</v>
+        <v>1628.637</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.56</v>
+        <v>1406.684</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.174</v>
+        <v>1305.297</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.414</v>
+        <v>1260.539</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.346</v>
+        <v>1081.471</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>756.677</v>
+        <v>756.799</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.463</v>
+        <v>589.546</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43490,16 +43490,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5484.723</v>
+        <v>5484.847</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6625.122</v>
+        <v>6625.618</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5053.494</v>
+        <v>5053.991</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.343</v>
+        <v>2035.548</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43790,37 +43790,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439.3</v>
+        <v>1439.2</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1439.28</v>
+        <v>1439.18</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1442.08</v>
+        <v>1441.98</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1444.1</v>
+        <v>1443.99</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1444.1</v>
+        <v>1443.99</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.86</v>
+        <v>1452.74</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1453.15</v>
+        <v>1453.01</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1454.2</v>
+        <v>1454.05</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1458.01</v>
+        <v>1457.84</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.84</v>
+        <v>1463.6</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1466.28</v>
+        <v>1466.08</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43907,52 +43907,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
     </row>
     <row r="18">
@@ -44024,52 +44024,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1413.94</v>
+        <v>1412.8</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1411.98</v>
+        <v>1410.62</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1413.94</v>
+        <v>1412.58</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1415.35</v>
+        <v>1413.98</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1415.35</v>
+        <v>1413.98</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1421.49</v>
+        <v>1420.11</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1421.69</v>
+        <v>1420.3</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1422.42</v>
+        <v>1421.03</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1425.09</v>
+        <v>1423.68</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1429.17</v>
+        <v>1427.71</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1430.88</v>
+        <v>1429.45</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1434.32</v>
+        <v>1433.03</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1444.25</v>
+        <v>1442.96</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1452.44</v>
+        <v>1451.15</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1455.71</v>
+        <v>1454.42</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1455.71</v>
+        <v>1454.42</v>
       </c>
     </row>
     <row r="19">
@@ -44141,52 +44141,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2569181.1</v>
+        <v>2567268.8</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2510538</v>
+        <v>2508293.6</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2438244.8</v>
+        <v>2436070.1</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2343557.4</v>
+        <v>2341471.8</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2343557.4</v>
+        <v>2341471.8</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1999410.7</v>
+        <v>1997646.1</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1855550.7</v>
+        <v>1853916.9</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1792839.2</v>
+        <v>1791263.7</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1541016.8</v>
+        <v>1539672.3</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1081420.4</v>
+        <v>1080493.6</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>843451.3</v>
+        <v>842724.3</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>619389.4</v>
+        <v>618832.3</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>371706.3</v>
+        <v>371374.3</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>264477.5</v>
+        <v>264242.6</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252952.7</v>
+        <v>252728.5</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52814.3</v>
+        <v>52767.5</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44201,19 +44201,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9106489.300000001</v>
+        <v>9104577</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9635897.6</v>
+        <v>9627307.300000001</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7188817.4</v>
+        <v>7182499</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2915967.4</v>
+        <v>2913424.5</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>570244.5</v>
+        <v>569738.6</v>
       </c>
     </row>
     <row r="20">
@@ -44285,52 +44285,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2447655.8</v>
+        <v>2445839.8</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2391824.6</v>
+        <v>2389692.7</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2374600.2</v>
+        <v>2372486.3</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2307249.8</v>
+        <v>2305199.5</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2307249.8</v>
+        <v>2305199.5</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1999410.7</v>
+        <v>1997646.1</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1855550.7</v>
+        <v>1853916.9</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1792839.2</v>
+        <v>1791263.7</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1541016.8</v>
+        <v>1539672.3</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1081420.4</v>
+        <v>1080493.6</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>843451.3</v>
+        <v>842724.3</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>619389.4</v>
+        <v>618832.3</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>371706.3</v>
+        <v>371374.3</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>264477.5</v>
+        <v>264242.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252952.7</v>
+        <v>252728.5</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52814.3</v>
+        <v>52767.5</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44345,19 +44345,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8615840.300000001</v>
+        <v>8614024.300000001</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9380924.4</v>
+        <v>9372578</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7188817.4</v>
+        <v>7182499</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2915967.4</v>
+        <v>2913424.5</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>570244.5</v>
+        <v>569738.6</v>
       </c>
     </row>
     <row r="21">
@@ -44429,52 +44429,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2131499.5</v>
+        <v>2129879</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2082300.2</v>
+        <v>2080406.6</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2061636.6</v>
+        <v>2059763.7</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1990847.1</v>
+        <v>1989040.3</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1990847.1</v>
+        <v>1989040.3</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1686447.2</v>
+        <v>1684923.5</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1542587.1</v>
+        <v>1541194.2</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1476436.5</v>
+        <v>1475104.6</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1226667.4</v>
+        <v>1225564.6</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>818096.3</v>
+        <v>817365.1</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>610263.2</v>
+        <v>609719.3</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>470531.7</v>
+        <v>470112</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>349400.9</v>
+        <v>349089.5</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>250173</v>
+        <v>249951.3</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252952.7</v>
+        <v>252728.5</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52814.3</v>
+        <v>52767.5</v>
       </c>
     </row>
     <row r="22">
@@ -44546,46 +44546,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>316156.2</v>
+        <v>315960.8</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>309524.4</v>
+        <v>309286.1</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312963.6</v>
+        <v>312722.6</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>316402.7</v>
+        <v>316159.1</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>316402.7</v>
+        <v>316159.1</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312963.6</v>
+        <v>312722.6</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312963.6</v>
+        <v>312722.6</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>316402.7</v>
+        <v>316159.1</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>314349.4</v>
+        <v>314107.7</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>263324.1</v>
+        <v>263128.4</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>233188.1</v>
+        <v>233005</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148857.7</v>
+        <v>148720.3</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22305.4</v>
+        <v>22284.8</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14304.5</v>
+        <v>14291.3</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44839,67 +44839,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1354.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1351.18)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1348.28)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
         <v/>
       </c>
     </row>
@@ -49506,43 +49506,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.404</v>
+        <v>46.528</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>45.894</v>
+        <v>46.017</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.404</v>
+        <v>46.528</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>46.914</v>
+        <v>47.039</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>46.914</v>
+        <v>47.039</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.404</v>
+        <v>46.528</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.404</v>
+        <v>46.528</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>46.914</v>
+        <v>47.039</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>46.914</v>
+        <v>47.039</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>45.894</v>
+        <v>46.017</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.109</v>
+        <v>31.189</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49561,7 +49561,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>496.169</v>
+        <v>497.491</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56700,10 +56700,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>496.169</v>
+        <v>497.491</v>
       </c>
       <c r="F197" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64250,7 +64250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21299억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3160억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21285억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20804억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3093억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20781억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3090억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 20575억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16849억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 16831억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15412억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 15395억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14751억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12256억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3141억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 12242억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3138억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39015억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39014억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41937억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41934억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45118억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45114억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48558억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48551억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52329억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52321억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 56217억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 56206억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 60331억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 60319억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 64722억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 64708억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39015억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 39014억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41937억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41934억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 45118억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 45114억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48558억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 48551억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52329억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 52321억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 56217억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 56206억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 60331억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 60319억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 64722억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 64708억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21299억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3160억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21285억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20804억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3093억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20781억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3090억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20598억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 20575억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19890억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16849억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 16831억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15412억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3127억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 15395억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14751억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3162억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12256억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3141억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 12242억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3138억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,306억(2026 4,206억 · 2027 12,543억 · 2028 12,557억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,206억 vs 688억 · 2027 12,543억 vs 29,126억 · 2028 12,557억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,280억(2026 4,204억 · 2027 12,531억 · 2028 12,545억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,204억 vs 688억 · 2027 12,531억 vs 29,126억 · 2028 12,545억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1364.3</v>
+        <v>1363.8</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.45</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="33">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2442</v>
+        <v>0.2441</v>
       </c>
     </row>
     <row r="34">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19720</v>
+        <v>19540</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19793.3</v>
+        <v>19735</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.010908918</v>
+        <v>-0.008699241999999999</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.001944965</v>
+        <v>-0.006711824</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.008914427000000001</v>
+        <v>0.002865272</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.001749548</v>
+        <v>0.001341747</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.005355309</v>
+        <v>0.000542462</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.006647515</v>
+        <v>0.003987192</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.000176559</v>
+        <v>-0.003407049</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.005316555</v>
+        <v>-0.00143424</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.001229607</v>
+        <v>0.008585100999999999</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.001187644</v>
+        <v>-0.000848897</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.010908918</v>
+        <v>-0.008699241999999999</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.001944965</v>
+        <v>-0.006711824</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.008914427000000001</v>
+        <v>0.002865272</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.001749548</v>
+        <v>0.001341747</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.005355309</v>
+        <v>0.000542462</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.006647515</v>
+        <v>0.003987192</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.000176559</v>
+        <v>-0.003407049</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.005316555</v>
+        <v>-0.00143424</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.001229607</v>
+        <v>0.008585100999999999</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.001187644</v>
+        <v>-0.000848897</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.133444262</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.119676624</v>
+        <v>0.119631698</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.111651652</v>
+        <v>0.111581232</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.109361664</v>
+        <v>0.109310755</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.106567999</v>
+        <v>0.106524725</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.105620669</v>
+        <v>0.105587084</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.098450853</v>
+        <v>0.098430856</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.094857469</v>
+        <v>0.094845595</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.092467902</v>
+        <v>0.092460705</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.086174192</v>
+        <v>0.08617298700000001</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.082222368</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.07722989399999999</v>
+        <v>0.07720062699999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.074890017</v>
+        <v>0.07484181299999999</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.07586250999999999</v>
+        <v>0.07582504800000001</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.076226618</v>
+        <v>0.07619242499999999</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.07767911800000001</v>
+        <v>0.07765034</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.074282971</v>
+        <v>0.074264289</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.07318219400000001</v>
+        <v>0.073168701</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.072779316</v>
+        <v>0.072769822</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.069070481</v>
+        <v>0.069066037</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>9999.694702999999</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>9999.704301</v>
+        <v>9999.6991</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>9999.769996000001</v>
+        <v>9999.769095</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>9999.619796000001</v>
+        <v>9999.618796000001</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>9999.691049999999</v>
+        <v>9999.690769000001</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>9999.704856</v>
+        <v>9999.70456</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>9999.806638</v>
+        <v>9999.802422000001</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>9999.698839999999</v>
+        <v>9999.703111000001</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>9999.765604</v>
+        <v>9999.7729</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>9999.701638</v>
+        <v>9999.708468000001</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.109264784</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.109501504</v>
+        <v>0.109506778</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.109506911</v>
+        <v>0.109506842</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.110644083</v>
+        <v>0.110649264</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.111217848</v>
+        <v>0.111217851</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.111217893</v>
+        <v>0.111217896</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.112086524</v>
+        <v>0.112086426</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.112086542</v>
+        <v>0.112086488</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.112086378</v>
+        <v>0.112086472</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.112086499</v>
+        <v>0.112086381</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13209,7 +13209,7 @@
         <v>0.109504618</v>
       </c>
       <c r="AG44" s="31" t="n">
-        <v>0.110644928</v>
+        <v>0.110653633</v>
       </c>
       <c r="AH44" s="31" t="n">
         <v>0.111219436</v>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>19720</v>
+        <v>19540</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,720원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,960원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200003187628856</v>
+        <v>0.2200000786307418</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463848392545808</v>
+        <v>0.04463847348901893</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229727986048935</v>
+        <v>0.01229715629018417</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576985615712875</v>
+        <v>0.05576884695824667</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42500,37 +42500,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.155</v>
+        <v>1817.262</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.152</v>
+        <v>1778.258</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.558</v>
+        <v>1724.665</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1655.938</v>
+        <v>1656.046</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1655.938</v>
+        <v>1656.046</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.684</v>
+        <v>1406.791</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.297</v>
+        <v>1305.404</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.539</v>
+        <v>1260.647</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.471</v>
+        <v>1081.579</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>756.799</v>
+        <v>756.905</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.546</v>
+        <v>589.6180000000001</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42560,16 +42560,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.42</v>
+        <v>6362.527</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6814.586</v>
+        <v>6815.015</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5053.991</v>
+        <v>5054.421</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.548</v>
+        <v>2035.726</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42644,37 +42644,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.02</v>
+        <v>1728.127</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1690.954</v>
+        <v>1691.06</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.39</v>
+        <v>1677.497</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.637</v>
+        <v>1628.745</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.637</v>
+        <v>1628.745</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.684</v>
+        <v>1406.791</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.297</v>
+        <v>1305.404</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.539</v>
+        <v>1260.647</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.471</v>
+        <v>1081.579</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>756.799</v>
+        <v>756.905</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.546</v>
+        <v>589.6180000000001</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42704,16 +42704,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6008.786</v>
+        <v>6008.893</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6625.618</v>
+        <v>6626.047</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5053.991</v>
+        <v>5054.421</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.548</v>
+        <v>2035.726</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43118,37 +43118,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>832.824</v>
+        <v>832.931</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.22</v>
+        <v>815.325</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>791.925</v>
+        <v>792.032</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.442</v>
+        <v>733.55</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.442</v>
+        <v>733.55</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.549</v>
+        <v>691.6559999999999</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>664.9829999999999</v>
+        <v>665.09</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.525</v>
+        <v>625.633</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>447.926</v>
+        <v>448.034</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.609</v>
+        <v>315.715</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.787</v>
+        <v>199.859</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43160,16 +43160,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.73</v>
+        <v>2583.837</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3074.029</v>
+        <v>3074.457</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2429.983</v>
+        <v>2430.413</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.562</v>
+        <v>595.74</v>
       </c>
     </row>
     <row r="11">
@@ -43430,37 +43430,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.02</v>
+        <v>1728.127</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1690.954</v>
+        <v>1691.06</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.39</v>
+        <v>1677.497</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.637</v>
+        <v>1628.745</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.637</v>
+        <v>1628.745</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.684</v>
+        <v>1406.791</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.297</v>
+        <v>1305.404</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.539</v>
+        <v>1260.647</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.471</v>
+        <v>1081.579</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>756.799</v>
+        <v>756.905</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.546</v>
+        <v>589.6180000000001</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43490,16 +43490,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5484.847</v>
+        <v>5484.954</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6625.618</v>
+        <v>6626.047</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5053.991</v>
+        <v>5054.421</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.548</v>
+        <v>2035.726</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43790,37 +43790,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439.2</v>
+        <v>1439.12</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1439.18</v>
+        <v>1439.09</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.98</v>
+        <v>1441.89</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.99</v>
+        <v>1443.89</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.99</v>
+        <v>1443.89</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.74</v>
+        <v>1452.63</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1453.01</v>
+        <v>1452.89</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1454.05</v>
+        <v>1453.93</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.84</v>
+        <v>1457.7</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.6</v>
+        <v>1463.4</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1466.08</v>
+        <v>1465.9</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43907,52 +43907,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
     </row>
     <row r="18">
@@ -44024,52 +44024,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1412.8</v>
+        <v>1411.81</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1410.62</v>
+        <v>1409</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1412.58</v>
+        <v>1410.95</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1413.98</v>
+        <v>1412.36</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1413.98</v>
+        <v>1412.36</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1420.11</v>
+        <v>1418.47</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1420.3</v>
+        <v>1418.66</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1421.03</v>
+        <v>1419.38</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1423.68</v>
+        <v>1422.02</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1427.71</v>
+        <v>1426.01</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1429.45</v>
+        <v>1427.76</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1433.03</v>
+        <v>1431.47</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1442.96</v>
+        <v>1441.4</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1451.15</v>
+        <v>1449.59</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1454.42</v>
+        <v>1452.86</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1454.42</v>
+        <v>1452.86</v>
       </c>
     </row>
     <row r="19">
@@ -44141,52 +44141,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2567268.8</v>
+        <v>2565622.1</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2508293.6</v>
+        <v>2505562.2</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2436070.1</v>
+        <v>2433422.8</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2341471.8</v>
+        <v>2338932</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2341471.8</v>
+        <v>2338932</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1997646.1</v>
+        <v>1995494.7</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1853916.9</v>
+        <v>1851923.6</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1791263.7</v>
+        <v>1789340.7</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1539672.3</v>
+        <v>1538028.6</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1080493.6</v>
+        <v>1079355.5</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>842724.3</v>
+        <v>841833.4</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>618832.3</v>
+        <v>618158.7</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>371374.3</v>
+        <v>370972.8</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>264242.6</v>
+        <v>263958.5</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252728.5</v>
+        <v>252457.4</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52767.5</v>
+        <v>52710.9</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44201,19 +44201,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9104577</v>
+        <v>9102930.300000001</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9627307.300000001</v>
+        <v>9616849</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7182499</v>
+        <v>7174787.6</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2913424.5</v>
+        <v>2910320.4</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>569738.6</v>
+        <v>569126.8</v>
       </c>
     </row>
     <row r="20">
@@ -44285,52 +44285,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2445839.8</v>
+        <v>2444276</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2389692.7</v>
+        <v>2387097.3</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2372486.3</v>
+        <v>2369912.6</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2305199.5</v>
+        <v>2302702.2</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2305199.5</v>
+        <v>2302702.2</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1997646.1</v>
+        <v>1995494.7</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1853916.9</v>
+        <v>1851923.6</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1791263.7</v>
+        <v>1789340.7</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1539672.3</v>
+        <v>1538028.6</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1080493.6</v>
+        <v>1079355.5</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>842724.3</v>
+        <v>841833.4</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>618832.3</v>
+        <v>618158.7</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>371374.3</v>
+        <v>370972.8</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>264242.6</v>
+        <v>263958.5</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252728.5</v>
+        <v>252457.4</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52767.5</v>
+        <v>52710.9</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44345,19 +44345,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8614024.300000001</v>
+        <v>8612460.5</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9372578</v>
+        <v>9362414.300000001</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7182499</v>
+        <v>7174787.6</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2913424.5</v>
+        <v>2910320.4</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>569738.6</v>
+        <v>569126.8</v>
       </c>
     </row>
     <row r="21">
@@ -44429,52 +44429,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2129879</v>
+        <v>2128483.5</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2080406.6</v>
+        <v>2078116.7</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2059763.7</v>
+        <v>2057498.8</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1989040.3</v>
+        <v>1986855.4</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1989040.3</v>
+        <v>1986855.4</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1684923.5</v>
+        <v>1683080.9</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1541194.2</v>
+        <v>1539509.8</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1475104.6</v>
+        <v>1473493.8</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1225564.6</v>
+        <v>1224230.9</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>817365.1</v>
+        <v>816480.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>609719.3</v>
+        <v>609061.6</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>470112</v>
+        <v>469604.5</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>349089.5</v>
+        <v>348712.9</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249951.3</v>
+        <v>249683.2</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252728.5</v>
+        <v>252457.4</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52767.5</v>
+        <v>52710.9</v>
       </c>
     </row>
     <row r="22">
@@ -44546,46 +44546,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315960.8</v>
+        <v>315792.5</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>309286.1</v>
+        <v>308980.6</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312722.6</v>
+        <v>312413.8</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>316159.1</v>
+        <v>315846.9</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>316159.1</v>
+        <v>315846.9</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312722.6</v>
+        <v>312413.8</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312722.6</v>
+        <v>312413.8</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>316159.1</v>
+        <v>315846.9</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>314107.7</v>
+        <v>313797.7</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>263128.4</v>
+        <v>262874.5</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>233005</v>
+        <v>232771.8</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148720.3</v>
+        <v>148554.2</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22284.8</v>
+        <v>22259.9</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14291.3</v>
+        <v>14275.4</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44839,67 +44839,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1351.18)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1348.08)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.98)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
         <v/>
       </c>
     </row>
@@ -49506,43 +49506,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.528</v>
+        <v>46.635</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.017</v>
+        <v>46.122</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.528</v>
+        <v>46.635</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.039</v>
+        <v>47.147</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.039</v>
+        <v>47.147</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.528</v>
+        <v>46.635</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.528</v>
+        <v>46.635</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.039</v>
+        <v>47.147</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.039</v>
+        <v>47.147</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.017</v>
+        <v>46.122</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.189</v>
+        <v>31.263</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49561,7 +49561,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>497.491</v>
+        <v>498.635</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56700,10 +56700,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>497.491</v>
+        <v>498.635</v>
       </c>
       <c r="F197" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64250,7 +64250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -2191,121 +2191,121 @@
     </comment>
     <comment ref="AC9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 97% × 코호트 15.0% + 등급없음 3% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 97% × 코호트 10.8% + 등급없음 3% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 15.0% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 10.8% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 15.0% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 10.8% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN9" authorId="0" shapeId="0">
       <text>
-        <t>추정: 매출액 × OPM(SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%))
+        <t>추정: 매출액 × OPM(SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%))
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AD10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AF10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 15.0% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.7%(코호트 모드 reference_anchor; 등급 비중 95% × 코호트 10.8% + 등급없음 5% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AG10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 97% × 코호트 15.0% + 등급없음 3% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 97% × 코호트 10.8% + 등급없음 3% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AH10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 15.0% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 10.8% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AI10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 14.9%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 15.0% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 98% × 코호트 10.8% + 등급없음 2% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AK10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AL10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AM10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
     <comment ref="AN10" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 코호트 타겟 15.0%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 15.0% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -3.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%)
+        <t>추정: SLS 코호트 타겟 10.8%(코호트 모드 reference_anchor; 등급 비중 100% × 코호트 10.8% + 등급없음 0% × 최근 4분기 실측 OPM 중위 9.7%) + 회사 캘리브레이션 -0.8%p(최근 4분기 실측−타겟 중위) — 신규수주 매출에도 같은 타겟 — 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%)
 [divide]</t>
       </text>
     </comment>
@@ -2317,55 +2317,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 36218억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 35966억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 39014억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41934억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41150억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 45114억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44011억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 48551억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47092억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 52321억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50471억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 56206억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 53933억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 60319억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57598억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 64708억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61509억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2377,55 +2377,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 36218억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 35966억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 39014억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 38502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41934억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41150억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 45114억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44011억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 48551억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47092억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 52321억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50471억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 56206억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 53933억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 60319억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57598억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 64708억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61509억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 15.0% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 14.72%→15.00%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,280억(2026 4,204억 · 2027 12,531억 · 2028 12,545억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,204억 vs 688억 · 2027 12,531억 vs 29,126억 · 2028 12,545억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,280억(2026 4,204억 · 2027 12,531억 · 2028 12,545억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,204억 vs 688억 · 2027 12,531억 vs 29,126억 · 2028 12,545억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1363.8</v>
+        <v>1234.7</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.33</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="32">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2441</v>
+        <v>0.221</v>
       </c>
     </row>
     <row r="34">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.71</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="35">
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15100</v>
+        <v>13700</v>
       </c>
     </row>
     <row r="36">
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.008699241999999999</v>
+        <v>-0.002946966</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.006711824</v>
+        <v>0.003964858</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.002865272</v>
+        <v>-0.009040717</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.001341747</v>
+        <v>0.006612437</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.000542462</v>
+        <v>0.002261545</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.003987192</v>
+        <v>5.104e-06</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.003407049</v>
+        <v>-0.004200418</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.00143424</v>
+        <v>0.00269112</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.008585100999999999</v>
+        <v>0.001507008</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.000848897</v>
+        <v>-0.006788747</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.008699241999999999</v>
+        <v>-0.002946966</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.006711824</v>
+        <v>0.003964858</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.002865272</v>
+        <v>-0.009040717</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.001341747</v>
+        <v>0.006612437</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.000542462</v>
+        <v>0.002261545</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.003987192</v>
+        <v>5.104e-06</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.003407049</v>
+        <v>-0.004200418</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.00143424</v>
+        <v>0.00269112</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.008585100999999999</v>
+        <v>0.001507008</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.000848897</v>
+        <v>-0.006788747</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11770,36 +11770,36 @@
         <v/>
       </c>
       <c r="AC33" s="31" t="n">
-        <v>0.133444262</v>
+        <v>0.121235518</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.119631698</v>
+        <v>0.109681061</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.111581232</v>
+        <v>0.103223111</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.109310755</v>
+        <v>0.101076186</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.106524725</v>
+        <v>0.098850941</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.105587084</v>
+        <v>0.098675913</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.098430856</v>
+        <v>0.09201411900000001</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.094845595</v>
+        <v>0.08918844400000001</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.092460705</v>
+        <v>0.087403175</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.08617298700000001</v>
+        <v>0.081839353</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11898,36 +11898,36 @@
         <v/>
       </c>
       <c r="AC34" s="31" t="n">
-        <v>0.082222368</v>
+        <v>0.074700172</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.07720062699999999</v>
+        <v>0.07050669499999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.07484181299999999</v>
+        <v>0.06878379799999999</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.07582504800000001</v>
+        <v>0.06952373000000001</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.07619242499999999</v>
+        <v>0.069998778</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.07765034</v>
+        <v>0.071758988</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.074264289</v>
+        <v>0.068594744</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.073168701</v>
+        <v>0.067945799</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.072769822</v>
+        <v>0.067909847</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.069066037</v>
+        <v>0.06474793700000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12922,42 +12922,42 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.109264784</v>
+        <v>0.09941024</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.109506778</v>
+        <v>0.099459066</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.109506842</v>
+        <v>0.099459058</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.110649264</v>
+        <v>0.09969014</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.111217851</v>
+        <v>0.09980499399999999</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.111217896</v>
+        <v>0.09980512</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.112086426</v>
+        <v>0.09998061599999999</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.112086488</v>
+        <v>0.099980687</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.112086472</v>
+        <v>0.099980625</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.112086381</v>
+        <v>0.099980652</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13196,42 +13196,42 @@
         <v/>
       </c>
       <c r="AC44" s="31" t="n">
-        <v>0.109260887</v>
+        <v>0.09940721299999999</v>
       </c>
       <c r="AD44" s="31" t="n">
-        <v>0.109504618</v>
+        <v>0.099459441</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE43/subQ!AE42,"")</f>
         <v/>
       </c>
       <c r="AF44" s="31" t="n">
-        <v>0.109504618</v>
+        <v>0.099459441</v>
       </c>
       <c r="AG44" s="31" t="n">
-        <v>0.110653633</v>
+        <v>0.099694466</v>
       </c>
       <c r="AH44" s="31" t="n">
-        <v>0.111219436</v>
+        <v>0.099807627</v>
       </c>
       <c r="AI44" s="31" t="n">
-        <v>0.111219436</v>
+        <v>0.099807627</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ43/subQ!AJ42,"")</f>
         <v/>
       </c>
       <c r="AK44" s="31" t="n">
-        <v>0.112089902</v>
+        <v>0.09998172</v>
       </c>
       <c r="AL44" s="31" t="n">
-        <v>0.112089902</v>
+        <v>0.09998172</v>
       </c>
       <c r="AM44" s="31" t="n">
-        <v>0.112089902</v>
+        <v>0.09998172</v>
       </c>
       <c r="AN44" s="31" t="n">
-        <v>0.112089902</v>
+        <v>0.09998172</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO43/subQ!AO42,"")</f>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200000786307418</v>
+        <v>0.2200000633240189</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229715629018417</v>
+        <v>0.01229665961540446</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576884695824667</v>
+        <v>0.0557670234890925</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25271,7 +25271,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42071,7 +42071,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>코호트 표(가정): ①적자 −5% ②BEP 0% ③중마진 5% ④호황 10% ⑤초호황 15% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 미적용</t>
+          <t>코호트 표(레퍼런스 실측 캘리브레이션): ①적자 −1.1% ②BEP 1% ③중마진 4.3% ④호황 5.4% ⑤초호황 10.8% — 회사별 캘리브레이션은 target_opm.basis 참조 · 코호트 모드 reference_anchor(대안 ledger_relative) · 잔고 캡 미적용</t>
         </is>
       </c>
     </row>
@@ -44606,109 +44606,109 @@
         </is>
       </c>
       <c r="E23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="G23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="H23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="I23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="J23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="K23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="L23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="M23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="N23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="O23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="P23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Q23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="R23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="S23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="T23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="U23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="V23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="W23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="X23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Y23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="Z23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AA23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AB23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AC23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AD23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AE23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AF23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AG23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AH23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AI23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AJ23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AK23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AL23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
       <c r="AM23" s="21" t="n">
-        <v>0.15</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="25">
@@ -56769,7 +56769,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 OPM 표 assumed 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 바꾸려면 --opm-table reference_calibrated(오너 결정 — 하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
+          <t>⚠ 코호트 OPM 표 reference_calibrated 적용. 레퍼런스 미포 SLS 셀 OPM 을 2023~2027 매출가중한 유효 표는 ①-1.1% ②1% ③4.3% ④5.4% ⑤10.8%(이전 가정 표 ①-5% ②0% ③5% ④10% ⑤15% 는 레퍼런스 2024~26 보다 +3.8~5.1%p 높다 — cohort_opm_calibration.by_year). 다음 분기 2026Q3 타겟: 가정 15.00% vs 캘리브레이션 10.80%. 다른 표는 --opm-table assumed (하류 섹션 각주·모델 백테스트가 cohort_opm_table 을 읽는다)</t>
         </is>
       </c>
     </row>

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,7 +1648,7 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21285억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 21276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3157억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
@@ -1666,19 +1666,19 @@
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16831억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 16830억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
@@ -1690,7 +1690,7 @@
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
@@ -2323,7 +2323,7 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2341,7 +2341,7 @@
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47092억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47091억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2359,7 +2359,7 @@
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57598억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57597억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,7 +2383,7 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 38502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 38501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2401,7 +2401,7 @@
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47092억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47091억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2419,7 +2419,7 @@
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57598억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57597억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,7 +4170,7 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21285억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 21276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3157억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -4188,19 +4188,19 @@
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19869억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16831억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 16830억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -4212,7 +4212,7 @@
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3158억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)
 [sls_link]</t>
       </text>
     </comment>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,280억(2026 4,204억 · 2027 12,531억 · 2028 12,545억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,204억 vs 688억 · 2027 12,531억 vs 29,126억 · 2028 12,545억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,280억(2026 4,203억 · 2027 12,532억 · 2028 12,546억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,203억 vs 688억 · 2027 12,532억 vs 29,126억 · 2028 12,546억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.83</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="33">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>19540</v>
+        <v>18890</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9736,7 +9736,7 @@
         <v>18440</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>19350</v>
+        <v>18800</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19735</v>
+        <v>19560</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.002946966</v>
+        <v>-0.003478913</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.003964858</v>
+        <v>-0.001485397</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.009040717</v>
+        <v>-0.001765401</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.006612437</v>
+        <v>0.004167238</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.002261545</v>
+        <v>6.4144e-05</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>5.104e-06</v>
+        <v>0.008159668</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.004200418</v>
+        <v>-0.007942183</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.00269112</v>
+        <v>0.009335932999999999</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.001507008</v>
+        <v>-0.001465706</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.006788747</v>
+        <v>-0.001567171</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.002946966</v>
+        <v>-0.003478913</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.003964858</v>
+        <v>-0.001485397</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.009040717</v>
+        <v>-0.001765401</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.006612437</v>
+        <v>0.004167238</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.002261545</v>
+        <v>6.4144e-05</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>5.104e-06</v>
+        <v>0.008159668</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.004200418</v>
+        <v>-0.007942183</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.00269112</v>
+        <v>0.009335932999999999</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.001507008</v>
+        <v>-0.001465706</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.006788747</v>
+        <v>-0.001567171</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.121235518</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.109681061</v>
+        <v>0.109652515</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.103223111</v>
+        <v>0.103224597</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.101076186</v>
+        <v>0.10107759</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098850941</v>
+        <v>0.098852262</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.098675913</v>
+        <v>0.09867719799999999</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.09201411900000001</v>
+        <v>0.092015229</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.08918844400000001</v>
+        <v>0.089189715</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.087403175</v>
+        <v>0.087404126</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.081839353</v>
+        <v>0.081840388</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.074700172</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.07050669499999999</v>
+        <v>0.07048834399999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.06878379799999999</v>
+        <v>0.068784198</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.06952373000000001</v>
+        <v>0.069523924</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.069998778</v>
+        <v>0.069999484</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.071758988</v>
+        <v>0.07175928099999999</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.068594744</v>
+        <v>0.068595421</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.067945799</v>
+        <v>0.06794626300000001</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.067909847</v>
+        <v>0.06791049</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.06474793700000001</v>
+        <v>0.06474851700000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>9999.694702999999</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>9999.6991</v>
+        <v>9999.702010000001</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>9999.769095</v>
+        <v>9999.765426</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>9999.618796000001</v>
+        <v>9999.620798</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>9999.690769000001</v>
+        <v>9999.688937000001</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>9999.70456</v>
+        <v>9999.702728</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>9999.802422000001</v>
+        <v>9999.80133</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>9999.703111000001</v>
+        <v>9999.694647</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>9999.7729</v>
+        <v>9999.77168</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>9999.708468000001</v>
+        <v>9999.709298</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.09941024</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099459066</v>
+        <v>0.09945911</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.099459058</v>
+        <v>0.09945905100000001</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.09969014</v>
+        <v>0.099690109</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.09980499399999999</v>
+        <v>0.09980493999999999</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.09980512</v>
+        <v>0.099805071</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.09998061599999999</v>
+        <v>0.099980662</v>
       </c>
       <c r="AL42" s="31" t="n">
         <v>0.099980687</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980625</v>
+        <v>0.099980584</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.099980652</v>
+        <v>0.099980712</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>19540</v>
+        <v>18890</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,960원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,700원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200000633240189</v>
+        <v>0.2199999756439437</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463847348901893</v>
+        <v>0.04463846471412587</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229665961540446</v>
+        <v>0.01229725690290061</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.0557670234890925</v>
+        <v>0.05576921540244233</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -42500,37 +42500,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.262</v>
+        <v>1817.327</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.258</v>
+        <v>1778.322</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.665</v>
+        <v>1724.73</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.046</v>
+        <v>1656.112</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.046</v>
+        <v>1656.112</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.791</v>
+        <v>1406.856</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.404</v>
+        <v>1305.469</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.647</v>
+        <v>1260.713</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.579</v>
+        <v>1081.645</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>756.905</v>
+        <v>756.97</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.6180000000001</v>
+        <v>589.6609999999999</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42560,16 +42560,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.527</v>
+        <v>6362.592</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.015</v>
+        <v>6815.276</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5054.421</v>
+        <v>5054.683</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.726</v>
+        <v>2035.834</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42644,37 +42644,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.127</v>
+        <v>1728.192</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.06</v>
+        <v>1691.124</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.497</v>
+        <v>1677.562</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.745</v>
+        <v>1628.811</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.745</v>
+        <v>1628.811</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.791</v>
+        <v>1406.856</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.404</v>
+        <v>1305.469</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.647</v>
+        <v>1260.713</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.579</v>
+        <v>1081.645</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>756.905</v>
+        <v>756.97</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.6180000000001</v>
+        <v>589.6609999999999</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42704,16 +42704,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6008.893</v>
+        <v>6008.958</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.047</v>
+        <v>6626.308</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5054.421</v>
+        <v>5054.683</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.726</v>
+        <v>2035.834</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43118,37 +43118,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>832.931</v>
+        <v>832.996</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.325</v>
+        <v>815.39</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.032</v>
+        <v>792.097</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.55</v>
+        <v>733.616</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.55</v>
+        <v>733.616</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.6559999999999</v>
+        <v>691.721</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.09</v>
+        <v>665.155</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.633</v>
+        <v>625.699</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.034</v>
+        <v>448.1</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.715</v>
+        <v>315.78</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.859</v>
+        <v>199.903</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43160,16 +43160,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.837</v>
+        <v>2583.902</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3074.457</v>
+        <v>3074.719</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2430.413</v>
+        <v>2430.675</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.74</v>
+        <v>595.849</v>
       </c>
     </row>
     <row r="11">
@@ -43430,37 +43430,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.127</v>
+        <v>1728.192</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.06</v>
+        <v>1691.124</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.497</v>
+        <v>1677.562</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.745</v>
+        <v>1628.811</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.745</v>
+        <v>1628.811</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.791</v>
+        <v>1406.856</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.404</v>
+        <v>1305.469</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.647</v>
+        <v>1260.713</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.579</v>
+        <v>1081.645</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>756.905</v>
+        <v>756.97</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.6180000000001</v>
+        <v>589.6609999999999</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43490,16 +43490,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5484.954</v>
+        <v>5485.019</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.047</v>
+        <v>6626.308</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5054.421</v>
+        <v>5054.683</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.726</v>
+        <v>2035.834</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43790,37 +43790,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439.12</v>
+        <v>1439.07</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1439.09</v>
+        <v>1439.04</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.89</v>
+        <v>1441.83</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.89</v>
+        <v>1443.84</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.89</v>
+        <v>1443.84</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.63</v>
+        <v>1452.56</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.89</v>
+        <v>1452.82</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.93</v>
+        <v>1453.85</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.7</v>
+        <v>1457.61</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.4</v>
+        <v>1463.27</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.9</v>
+        <v>1465.79</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43907,52 +43907,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
     </row>
     <row r="18">
@@ -44024,52 +44024,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1411.81</v>
+        <v>1411.21</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1409</v>
+        <v>1408.93</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1410.95</v>
+        <v>1410.89</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1412.36</v>
+        <v>1412.29</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1412.36</v>
+        <v>1412.29</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1418.47</v>
+        <v>1418.4</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1418.66</v>
+        <v>1418.58</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1419.38</v>
+        <v>1419.3</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1422.02</v>
+        <v>1421.93</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1426.01</v>
+        <v>1425.9</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1427.76</v>
+        <v>1427.66</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1431.47</v>
+        <v>1431.44</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1441.4</v>
+        <v>1441.38</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1449.59</v>
+        <v>1449.57</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1452.86</v>
+        <v>1452.83</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1452.86</v>
+        <v>1452.83</v>
       </c>
     </row>
     <row r="19">
@@ -44141,52 +44141,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2565622.1</v>
+        <v>2564623.4</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2505562.2</v>
+        <v>2505540</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2433422.8</v>
+        <v>2433402.3</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2338932</v>
+        <v>2338913.7</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2338932</v>
+        <v>2338913.7</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1995494.7</v>
+        <v>1995482.8</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1851923.6</v>
+        <v>1851914.4</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1789340.7</v>
+        <v>1789333.1</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1538028.6</v>
+        <v>1538025.8</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1079355.5</v>
+        <v>1079360.8</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>841833.4</v>
+        <v>841835</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>618158.7</v>
+        <v>618147</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>370972.8</v>
+        <v>370965.9</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>263958.5</v>
+        <v>263953.6</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252457.4</v>
+        <v>252452.7</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52710.9</v>
+        <v>52709.9</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44201,19 +44201,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9102930.300000001</v>
+        <v>9101931.6</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9616849</v>
+        <v>9616769.699999999</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7174787.6</v>
+        <v>7174756.1</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2910320.4</v>
+        <v>2910308.7</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>569126.8</v>
+        <v>569116.2</v>
       </c>
     </row>
     <row r="20">
@@ -44285,52 +44285,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2444276</v>
+        <v>2443327.6</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2387097.3</v>
+        <v>2387077.5</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2369912.6</v>
+        <v>2369893.4</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2302702.2</v>
+        <v>2302684.6</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2302702.2</v>
+        <v>2302684.6</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1995494.7</v>
+        <v>1995482.8</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1851923.6</v>
+        <v>1851914.4</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1789340.7</v>
+        <v>1789333.1</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1538028.6</v>
+        <v>1538025.8</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1079355.5</v>
+        <v>1079360.8</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>841833.4</v>
+        <v>841835</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>618158.7</v>
+        <v>618147</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>370972.8</v>
+        <v>370965.9</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>263958.5</v>
+        <v>263953.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252457.4</v>
+        <v>252452.7</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52710.9</v>
+        <v>52709.9</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44345,19 +44345,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8612460.5</v>
+        <v>8611512.1</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9362414.300000001</v>
+        <v>9362340.1</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7174787.6</v>
+        <v>7174756.1</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2910320.4</v>
+        <v>2910308.7</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>569126.8</v>
+        <v>569116.2</v>
       </c>
     </row>
     <row r="21">
@@ -44429,52 +44429,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2128483.5</v>
+        <v>2127637.2</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2078116.7</v>
+        <v>2078077</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2057498.8</v>
+        <v>2057459.6</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1986855.4</v>
+        <v>1986817.5</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1986855.4</v>
+        <v>1986817.5</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1683080.9</v>
+        <v>1683049</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1539509.8</v>
+        <v>1539480.7</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1473493.8</v>
+        <v>1473466</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1224230.9</v>
+        <v>1224207.8</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>816480.9</v>
+        <v>816465.6</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>609061.6</v>
+        <v>609050.2</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>469604.5</v>
+        <v>469595.7</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>348712.9</v>
+        <v>348706.4</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249683.2</v>
+        <v>249678.5</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252457.4</v>
+        <v>252452.7</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52710.9</v>
+        <v>52709.9</v>
       </c>
     </row>
     <row r="22">
@@ -44546,46 +44546,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315792.5</v>
+        <v>315690.4</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>308980.6</v>
+        <v>309000.4</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312413.8</v>
+        <v>312433.8</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>315846.9</v>
+        <v>315867.1</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>315846.9</v>
+        <v>315867.1</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312413.8</v>
+        <v>312433.8</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312413.8</v>
+        <v>312433.8</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>315846.9</v>
+        <v>315867.1</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>313797.7</v>
+        <v>313818</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>262874.5</v>
+        <v>262895.2</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>232771.8</v>
+        <v>232784.8</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148554.2</v>
+        <v>148551.3</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22259.9</v>
+        <v>22259.5</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14275.4</v>
+        <v>14275.1</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44839,67 +44839,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1348.08)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1346.2)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.78)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
         <v/>
       </c>
     </row>
@@ -49506,43 +49506,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.635</v>
+        <v>46.7</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.122</v>
+        <v>46.187</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.635</v>
+        <v>46.7</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.147</v>
+        <v>47.213</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.147</v>
+        <v>47.213</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.635</v>
+        <v>46.7</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.635</v>
+        <v>46.7</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.147</v>
+        <v>47.213</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.147</v>
+        <v>47.213</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.122</v>
+        <v>46.187</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.263</v>
+        <v>31.305</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49561,7 +49561,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>498.635</v>
+        <v>499.331</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56700,10 +56700,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>498.635</v>
+        <v>499.331</v>
       </c>
       <c r="F197" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -58477,7 +58477,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64250,7 +64250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1642,121 +1642,121 @@
     <comment ref="AC40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21603억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1046억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 22649억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 1046억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 21276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3157억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 24433억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20781억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3090억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 23871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3090억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 20575억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 23699억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 16830억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 19955억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15395억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 18519억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 17893억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 12242억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3138억 제외(패널 신규에 포함으로 봄)</t>
+SLS 해양 원화 15380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3138억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AF41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AH41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)</t>
+forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)</t>
       </text>
     </comment>
     <comment ref="AC42" authorId="0" shapeId="0">
@@ -2317,55 +2317,55 @@
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 35966억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 36047억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38779억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41150억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44011억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44398억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47091억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47437억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50471억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50740억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 53933억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54104억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57597억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57667억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61509억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61495억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2377,55 +2377,55 @@
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 35966억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 36047억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 38501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 38779억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41150억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44011억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44398억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47091억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47437억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50471억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50740억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 53933억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54104억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57597억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57667억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61509억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61495억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4164,61 +4164,61 @@
     </comment>
     <comment ref="AC38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21603억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 1046억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 22649억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 120931억) + 신규수주 매출 0억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 1046억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 21276억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 688억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3157억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 24433억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20781억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 2563억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3090억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 23871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3090억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 20575억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 5341억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 23699억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 8741억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19868억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 12481억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 16830억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 16400억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 19955억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15395억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 20325억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3124억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 18519억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 14735억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 24039억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3159억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 17893억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 12242억(sls.by_quarter.marine_hedged_krw_m_signed_by_origin(헤지 70% 적용; origin 2026Q2 이후 체결 7건 제외 — 패널 신규에 포함)) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 27324억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy) · origin 이후 공시 수주 SLS 3138억 제외(패널 신규에 포함으로 봄)
+        <t>추정: SLS 해양 원화 15380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3138억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -4234,61 +4234,61 @@
     </comment>
     <comment ref="AC39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AD39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AF39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AG39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN39" authorId="0" shapeId="0">
       <text>
-        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy — 매출조선에 포함(합산 금지)
+        <t>추정: forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 매출조선에 포함(합산 금지)
 [abs]</t>
       </text>
     </comment>
@@ -4919,152 +4919,152 @@
   <commentList>
     <comment ref="E12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P12" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel existing_only new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P18" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel conservative new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="F24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="H24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="I24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="J24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="K24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="M24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="N24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
     <comment ref="P24" authorId="0" shapeId="0">
       <text>
-        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100)</t>
+        <t>forecast_panel optimistic new_order_revenue(억원) — forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel)</t>
       </text>
     </comment>
   </commentList>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 통계 흐름, 공시 계약 개별 반영 아님). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
+          <t>· 신규수주 — forecast_panel base 시나리오를 매출조선신규 행에 포함(calibrated=False, status partial — 공시 계약은 체결 분기별로 패널 신규수주와 상계(SLS 일정 유지)). 보수/낙관/기존만 은 시나리오 시트에만(합산 안 함)</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base 신규수주 매출(new_order_revenue, 미보정 book-value proxy, status partial; FY합 117,902억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 패널 신규에 포함된 것으로 보아 기존 SLS 에서 제외 — 추정 창 SLS −29,280억(2026 4,203억 · 2027 12,532억 · 2028 12,546억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 제외 SLS vs 패널 base 신규 매출: 2026 4,203억 vs 688억 · 2027 12,532억 vs 29,126억 · 2028 12,546억 vs 88,088억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,203억 vs 54억 · 2027 12,532억 vs 16,454억 · 2028 12,546억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1234.7</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="32">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.221</v>
+        <v>0.2291</v>
       </c>
     </row>
     <row r="34">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="35">
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13700</v>
+        <v>14200</v>
       </c>
     </row>
     <row r="36">
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.003478913</v>
+        <v>-0.005525432</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.001485397</v>
+        <v>-0.010284369</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.001765401</v>
+        <v>0.0002603</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.004167238</v>
+        <v>0.002958888</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>6.4144e-05</v>
+        <v>-0.002353551</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.008159668</v>
+        <v>-0.001526557</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.007942183</v>
+        <v>-0.003184867</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.009335932999999999</v>
+        <v>0.003623298</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.001465706</v>
+        <v>-0.003856141</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.001567171</v>
+        <v>-0.00392748</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.003478913</v>
+        <v>-0.005525432</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.001485397</v>
+        <v>-0.010284369</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>-0.001765401</v>
+        <v>0.0002603</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.004167238</v>
+        <v>0.002958888</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>6.4144e-05</v>
+        <v>-0.002353551</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.008159668</v>
+        <v>-0.001526557</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.007942183</v>
+        <v>-0.003184867</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.009335932999999999</v>
+        <v>0.003623298</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.001465706</v>
+        <v>-0.003856141</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.001567171</v>
+        <v>-0.00392748</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11770,36 +11770,36 @@
         <v/>
       </c>
       <c r="AC33" s="31" t="n">
-        <v>0.121235518</v>
+        <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.109652515</v>
+        <v>0.117715082</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.103224597</v>
+        <v>0.105799242</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.10107759</v>
+        <v>0.10027493</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.098852262</v>
+        <v>0.09631724</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.09867719799999999</v>
+        <v>0.09548733500000001</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.092015229</v>
+        <v>0.08878535999999999</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.089189715</v>
+        <v>0.086365937</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.087404126</v>
+        <v>0.08539991600000001</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.081840388</v>
+        <v>0.080810124</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11898,36 +11898,36 @@
         <v/>
       </c>
       <c r="AC34" s="31" t="n">
-        <v>0.074700172</v>
+        <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.07048834399999999</v>
+        <v>0.07576588099999999</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.068784198</v>
+        <v>0.070752313</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.069523924</v>
+        <v>0.06925260900000001</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.069999484</v>
+        <v>0.068449251</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.07175928099999999</v>
+        <v>0.069629422</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.068595421</v>
+        <v>0.066307461</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.06794626300000001</v>
+        <v>0.065860061</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.06791049</v>
+        <v>0.066376659</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.06474851700000001</v>
+        <v>0.06392956299999999</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12621,36 +12621,36 @@
         <v/>
       </c>
       <c r="AC40" s="29" t="n">
-        <v>9999.694702999999</v>
+        <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>9999.702010000001</v>
+        <v>13156.60201</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>9999.765426</v>
+        <v>13089.775426</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>9999.620798</v>
+        <v>13123.960798</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>9999.688937000001</v>
+        <v>13158.358937</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>9999.702728</v>
+        <v>13158.372728</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>9999.80133</v>
+        <v>13124.14133</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>9999.694647</v>
+        <v>13124.034647</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>9999.77168</v>
+        <v>13158.44168</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>9999.709298</v>
+        <v>13137.889298</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12667,7 +12667,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>매출조선신규 (forecast_panel base 신규수주 매출, 억원 — 가정)</t>
+          <t>매출조선신규 (forecast_panel base · 공시 상계 신규수주 매출, 억원 — 가정)</t>
         </is>
       </c>
       <c r="E41" s="26">
@@ -12770,39 +12770,39 @@
         <v>0</v>
       </c>
       <c r="AD41" s="29" t="n">
-        <v>687.89</v>
+        <v>54.41</v>
       </c>
       <c r="AE41" s="30">
         <f>subQ!AE39</f>
         <v/>
       </c>
       <c r="AF41" s="29" t="n">
-        <v>2562.78</v>
+        <v>693.5700000000001</v>
       </c>
       <c r="AG41" s="29" t="n">
-        <v>5341.48</v>
+        <v>2393.86</v>
       </c>
       <c r="AH41" s="29" t="n">
-        <v>8740.809999999999</v>
+        <v>5034.28</v>
       </c>
       <c r="AI41" s="29" t="n">
-        <v>12480.75</v>
+        <v>8331.889999999999</v>
       </c>
       <c r="AJ41" s="30">
         <f>subQ!AJ39</f>
         <v/>
       </c>
       <c r="AK41" s="29" t="n">
-        <v>16399.95</v>
+        <v>12015.39</v>
       </c>
       <c r="AL41" s="29" t="n">
-        <v>20325.4</v>
+        <v>15897.92</v>
       </c>
       <c r="AM41" s="29" t="n">
-        <v>24039.28</v>
+        <v>19805.34</v>
       </c>
       <c r="AN41" s="29" t="n">
-        <v>27323.75</v>
+        <v>23529.12</v>
       </c>
       <c r="AO41" s="30">
         <f>subQ!AO39</f>
@@ -12922,42 +12922,42 @@
         <v/>
       </c>
       <c r="AC42" s="31" t="n">
-        <v>0.09941024</v>
+        <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.09945911</v>
+        <v>0.099458904</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.09945905100000001</v>
+        <v>0.099459063</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.099690109</v>
+        <v>0.09968990799999999</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.09980493999999999</v>
+        <v>0.09980491800000001</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.099805071</v>
+        <v>0.09980497300000001</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.099980662</v>
+        <v>0.099980605</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.099980687</v>
+        <v>0.09998066</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980584</v>
+        <v>0.099980712</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.099980712</v>
+        <v>0.099980556</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2199999756439437</v>
+        <v>0.2200001171455724</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463846471412587</v>
+        <v>0.04463851706803693</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229725690290061</v>
+        <v>0.01229708462849534</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576921540244233</v>
+        <v>0.05576840017629073</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17954,10 +17954,10 @@
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>13824.36</v>
+        <v>25215.05</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>13824.36</v>
+        <v>25215.05</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>34277.29</v>
@@ -17966,7 +17966,7 @@
         <v>30231.44</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>15789.6</v>
+        <v>19265.64</v>
       </c>
       <c r="J43" s="18" t="n">
         <v>56243.82</v>
@@ -18520,80 +18520,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>장기충당부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>78546.23</v>
+        <v>11390.69</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>78546.23</v>
+        <v>11390.69</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>55608.31</v>
+        <v>7813.22</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>55663.85</v>
+        <v>3406.07</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>26244.24</v>
+        <v>3476.04</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>28986.64</v>
+        <v>23643.99</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>28986.64</v>
+        <v>23643.99</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>29236.73</v>
+        <v>30397.06</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>24476.95</v>
+        <v>26102.37</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>26846.31</v>
+        <v>22944.46</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>29982.69</v>
+        <v>98825.3</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>29982.69</v>
+        <v>98825.3</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>32456.13</v>
+        <v>116821.81</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>37544.47</v>
+        <v>135361.8</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>36915.02</v>
+        <v>120208.56</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>41757.36</v>
+        <v>260361.99</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>41757.36</v>
+        <v>260361.99</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>50425.78</v>
+        <v>229263.33</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>50444.32</v>
+        <v>217866.14</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>55881.58</v>
+        <v>206144.41</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>63805.15</v>
+        <v>194567.72</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>63805.15</v>
+        <v>194567.72</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>68229.69</v>
+        <v>191617.06</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>79501.12</v>
+        <v>179711.06</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -18615,80 +18615,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>장기파생상품부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>417699.39</v>
+        <v>479880.42</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>417699.39</v>
+        <v>479880.42</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>395352.66</v>
+        <v>453740.98</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>786612.71</v>
+        <v>1000628.56</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>1279017.55</v>
+        <v>1492711.98</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>274626.53</v>
+        <v>516181.09</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>274626.53</v>
+        <v>516181.09</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>188154.52</v>
+        <v>441858.85</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>139650.81</v>
+        <v>390409.64</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>124205.26</v>
+        <v>374634.02</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>105724.86</v>
+        <v>391936.06</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>105724.86</v>
+        <v>391936.06</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>199974.85</v>
+        <v>376168.92</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>394904.27</v>
+        <v>589826.4300000001</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>121765.91</v>
+        <v>301279.1</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>914698.45</v>
+        <v>1237410.02</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>914698.45</v>
+        <v>1237410.02</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>864750.74</v>
+        <v>1159405.13</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>423500.26</v>
+        <v>706941.92</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>476332.47</v>
+        <v>748176.12</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>775354.91</v>
+        <v>1051863.9</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>775354.91</v>
+        <v>1051863.9</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>1467463.84</v>
+        <v>1741807.17</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>1564892.87</v>
+        <v>1827805.03</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -18710,80 +18710,80 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>장기충당부채</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>468489.73</v>
+        <v>78546.23</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>468489.73</v>
+        <v>78546.23</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>453740.98</v>
+        <v>55608.31</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>1000628.56</v>
+        <v>55663.85</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>1489235.94</v>
+        <v>26244.24</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>516181.09</v>
+        <v>28986.64</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>516181.09</v>
+        <v>28986.64</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>441858.85</v>
+        <v>29236.73</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>390409.64</v>
+        <v>24476.95</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>374634.02</v>
+        <v>26846.31</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>391936.06</v>
+        <v>29982.69</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>391936.06</v>
+        <v>29982.69</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>376168.92</v>
+        <v>32456.13</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>589826.4300000001</v>
+        <v>37544.47</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>301279.1</v>
+        <v>36915.02</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>1237410.02</v>
+        <v>41757.36</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>1237410.02</v>
+        <v>41757.36</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>1159405.13</v>
+        <v>50425.78</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>706941.92</v>
+        <v>50444.32</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>748176.12</v>
+        <v>55881.58</v>
       </c>
       <c r="Y51" s="18" t="n">
-        <v>1051863.9</v>
+        <v>63805.15</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>1051863.9</v>
+        <v>63805.15</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>1741807.17</v>
+        <v>68229.69</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>1827805.03</v>
+        <v>79501.12</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -18805,80 +18805,80 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>기타비유동금융부채</t>
+          <t>장기파생상품부채</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>50790.34</v>
+        <v>417699.39</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>50790.34</v>
+        <v>417699.39</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>50575.1</v>
+        <v>395352.66</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>210609.78</v>
+        <v>786612.71</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>210218.39</v>
+        <v>1279017.55</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>217910.57</v>
+        <v>274626.53</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>217910.57</v>
+        <v>274626.53</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>223307.27</v>
+        <v>188154.52</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>224656.46</v>
+        <v>139650.81</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>227484.3</v>
+        <v>124205.26</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>187385.9</v>
+        <v>105724.86</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>187385.9</v>
+        <v>105724.86</v>
       </c>
       <c r="Q52" s="18" t="n">
-        <v>59372.26</v>
+        <v>199974.85</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>59560.36</v>
+        <v>394904.27</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>59304.63</v>
+        <v>121765.91</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>62349.58</v>
+        <v>914698.45</v>
       </c>
       <c r="U52" s="37" t="n">
-        <v>62349.58</v>
+        <v>914698.45</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>65391.06</v>
+        <v>864750.74</v>
       </c>
       <c r="W52" s="18" t="n">
-        <v>65575.52</v>
+        <v>423500.26</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>65699.24000000001</v>
+        <v>476332.47</v>
       </c>
       <c r="Y52" s="18" t="n">
-        <v>81941.27</v>
+        <v>775354.91</v>
       </c>
       <c r="Z52" s="37" t="n">
-        <v>81941.27</v>
+        <v>775354.91</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>82726.27</v>
+        <v>1467463.84</v>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>83201.10000000001</v>
+        <v>1564892.87</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -18900,67 +18900,81 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>이연법인세부채</t>
+          <t>기타비유동금융부채</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>27179.19</v>
+        <v>50790.34</v>
       </c>
       <c r="F53" s="37" t="n">
-        <v>27179.19</v>
+        <v>50790.34</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>28165.52</v>
+        <v>50575.1</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>29960.34</v>
+        <v>210609.78</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>33253.84</v>
+        <v>210218.39</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>21861.69</v>
+        <v>217910.57</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>21861.69</v>
+        <v>217910.57</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>18007.91</v>
+        <v>223307.27</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>17697.11</v>
+        <v>224656.46</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>14050.09</v>
+        <v>227484.3</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>14086.42</v>
+        <v>187385.9</v>
       </c>
       <c r="P53" s="37" t="n">
-        <v>14086.42</v>
+        <v>187385.9</v>
       </c>
       <c r="Q53" s="18" t="n">
-        <v>0</v>
+        <v>59372.26</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>0</v>
+        <v>59560.36</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>0</v>
+        <v>59304.63</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>0</v>
+        <v>62349.58</v>
       </c>
       <c r="U53" s="37" t="n">
-        <v>0</v>
+        <v>62349.58</v>
+      </c>
+      <c r="V53" s="18" t="n">
+        <v>65391.06</v>
+      </c>
+      <c r="W53" s="18" t="n">
+        <v>65575.52</v>
+      </c>
+      <c r="X53" s="18" t="n">
+        <v>65699.24000000001</v>
       </c>
       <c r="Y53" s="18" t="n">
-        <v>0</v>
+        <v>81941.27</v>
       </c>
       <c r="Z53" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="5" t="n"/>
+        <v>81941.27</v>
+      </c>
+      <c r="AA53" s="18" t="n">
+        <v>82726.27</v>
+      </c>
+      <c r="AB53" s="19" t="n">
+        <v>83201.10000000001</v>
+      </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
@@ -18981,81 +18995,67 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>이연법인세부채</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
-        <v>8041328.86</v>
+        <v>27179.19</v>
       </c>
       <c r="F54" s="37" t="n">
-        <v>8041328.86</v>
+        <v>27179.19</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>8253315.24</v>
+        <v>28165.52</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>9570294.279999999</v>
+        <v>29960.34</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>12369442.93</v>
+        <v>33253.84</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>10919760.59</v>
+        <v>21861.69</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>10919760.59</v>
+        <v>21861.69</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>10931420.36</v>
+        <v>18007.91</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>11272755.19</v>
+        <v>17697.11</v>
       </c>
       <c r="N54" s="18" t="n">
-        <v>12727072.7</v>
+        <v>14050.09</v>
       </c>
       <c r="O54" s="18" t="n">
-        <v>12184181.55</v>
+        <v>14086.42</v>
       </c>
       <c r="P54" s="37" t="n">
-        <v>12184181.55</v>
+        <v>14086.42</v>
       </c>
       <c r="Q54" s="18" t="n">
-        <v>12687134.45</v>
+        <v>0</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>12859746.37</v>
+        <v>0</v>
       </c>
       <c r="S54" s="18" t="n">
-        <v>11344791.93</v>
+        <v>0</v>
       </c>
       <c r="T54" s="18" t="n">
-        <v>13445186.02</v>
+        <v>0</v>
       </c>
       <c r="U54" s="37" t="n">
-        <v>13445186.02</v>
-      </c>
-      <c r="V54" s="18" t="n">
-        <v>12473197.52</v>
-      </c>
-      <c r="W54" s="18" t="n">
-        <v>10332762.13</v>
-      </c>
-      <c r="X54" s="18" t="n">
-        <v>10594103.78</v>
+        <v>0</v>
       </c>
       <c r="Y54" s="18" t="n">
-        <v>10853831.16</v>
+        <v>0</v>
       </c>
       <c r="Z54" s="37" t="n">
-        <v>10853831.16</v>
-      </c>
-      <c r="AA54" s="18" t="n">
-        <v>12113230.2</v>
-      </c>
-      <c r="AB54" s="19" t="n">
-        <v>13249028.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB54" s="5" t="n"/>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
       <c r="AE54" s="11" t="n"/>
@@ -19076,80 +19076,80 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E55" s="18" t="n">
-        <v>4111043.96</v>
+        <v>8041328.86</v>
       </c>
       <c r="F55" s="37" t="n">
-        <v>4111043.96</v>
+        <v>8041328.86</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>4048489.67</v>
+        <v>8253315.24</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>4244211.22</v>
+        <v>9570294.279999999</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>4514542.26</v>
+        <v>12369442.93</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>3594491.08</v>
+        <v>10919760.59</v>
       </c>
       <c r="K55" s="37" t="n">
-        <v>3594491.08</v>
+        <v>10919760.59</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>3745865.3</v>
+        <v>10931420.36</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>3736371.86</v>
+        <v>11272755.19</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>3903339.23</v>
+        <v>12727072.7</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>3439345</v>
+        <v>12184181.55</v>
       </c>
       <c r="P55" s="37" t="n">
-        <v>3439345</v>
+        <v>12184181.55</v>
       </c>
       <c r="Q55" s="18" t="n">
-        <v>3705485.47</v>
+        <v>12687134.45</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>3955772.1</v>
+        <v>12859746.37</v>
       </c>
       <c r="S55" s="18" t="n">
-        <v>3769079.35</v>
+        <v>11344791.93</v>
       </c>
       <c r="T55" s="18" t="n">
-        <v>3794592.95</v>
+        <v>13445186.02</v>
       </c>
       <c r="U55" s="37" t="n">
-        <v>3794592.95</v>
+        <v>13445186.02</v>
       </c>
       <c r="V55" s="18" t="n">
-        <v>3854995.33</v>
+        <v>12473197.52</v>
       </c>
       <c r="W55" s="18" t="n">
-        <v>3654160.42</v>
+        <v>10332762.13</v>
       </c>
       <c r="X55" s="18" t="n">
-        <v>3993852.28</v>
+        <v>10594103.78</v>
       </c>
       <c r="Y55" s="18" t="n">
-        <v>4148939.31</v>
+        <v>10853831.16</v>
       </c>
       <c r="Z55" s="37" t="n">
-        <v>4148939.31</v>
+        <v>10853831.16</v>
       </c>
       <c r="AA55" s="18" t="n">
-        <v>4513941.76</v>
+        <v>12113230.2</v>
       </c>
       <c r="AB55" s="19" t="n">
-        <v>4771398.4</v>
+        <v>13249028.8</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -19171,80 +19171,80 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E56" s="18" t="n">
-        <v>880114.84</v>
+        <v>4111043.96</v>
       </c>
       <c r="F56" s="37" t="n">
-        <v>880114.84</v>
+        <v>4111043.96</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>880114.84</v>
+        <v>4048489.67</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>880114.84</v>
+        <v>4244211.22</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>880114.84</v>
+        <v>4514542.26</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3594491.08</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>880114.84</v>
+        <v>3594491.08</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3745865.3</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3736371.86</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3903339.23</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3439345</v>
       </c>
       <c r="P56" s="37" t="n">
-        <v>880114.84</v>
+        <v>3439345</v>
       </c>
       <c r="Q56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3705485.47</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3955772.1</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3769079.35</v>
       </c>
       <c r="T56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3794592.95</v>
       </c>
       <c r="U56" s="37" t="n">
-        <v>880114.84</v>
+        <v>3794592.95</v>
       </c>
       <c r="V56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3854995.33</v>
       </c>
       <c r="W56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3654160.42</v>
       </c>
       <c r="X56" s="18" t="n">
-        <v>880114.84</v>
+        <v>3993852.28</v>
       </c>
       <c r="Y56" s="18" t="n">
-        <v>880114.84</v>
+        <v>4148939.31</v>
       </c>
       <c r="Z56" s="37" t="n">
-        <v>880114.84</v>
+        <v>4148939.31</v>
       </c>
       <c r="AA56" s="18" t="n">
-        <v>880114.84</v>
+        <v>4513941.76</v>
       </c>
       <c r="AB56" s="19" t="n">
-        <v>880114.84</v>
+        <v>4771398.4</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -19266,80 +19266,80 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>보통주자본금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="F57" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="I57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="K57" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="W57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -19361,80 +19361,80 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>우선주자본금</t>
+          <t>보통주자본금</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="F58" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="K58" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -19456,80 +19456,80 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>우선주자본금</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="F59" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -19551,80 +19551,80 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>1060330.62</v>
+        <v>1969727.2</v>
       </c>
       <c r="F60" s="37" t="n">
-        <v>1060330.62</v>
+        <v>1969727.2</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>1100811.83</v>
+        <v>1969727.2</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>1333501.06</v>
+        <v>1969727.2</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>1802788.05</v>
+        <v>1969727.2</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>1147530.94</v>
+        <v>1969727.2</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>1147530.94</v>
+        <v>1969727.2</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>1287480.88</v>
+        <v>1969727.2</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>1252379.35</v>
+        <v>1969727.2</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>1381235.89</v>
+        <v>1969727.2</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>1202135.76</v>
+        <v>1969727.2</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>1202135.76</v>
+        <v>1969727.2</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>1458329.32</v>
+        <v>1969727.2</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1632059.61</v>
+        <v>1969727.2</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>1371387.3</v>
+        <v>1969727.2</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>1524732.98</v>
+        <v>1969727.2</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>1524732.98</v>
+        <v>1969727.2</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>1493039.63</v>
+        <v>1969727.2</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>1078085.44</v>
+        <v>1969727.2</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>1273381.84</v>
+        <v>1969727.2</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>1345897.38</v>
+        <v>1969727.2</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>1345897.38</v>
+        <v>1969727.2</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>1609315.95</v>
+        <v>1969727.2</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>1642439.97</v>
+        <v>1969727.2</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -19646,80 +19646,80 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1060330.62</v>
       </c>
       <c r="F61" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1060330.62</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1100811.83</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1333501.06</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1802788.05</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1147530.94</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1147530.94</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1287480.88</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1252379.35</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1381235.89</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1202135.76</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1202135.76</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1458329.32</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1632059.61</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1371387.3</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1524732.98</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1524732.98</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1493039.63</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1078085.44</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1273381.84</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1345897.38</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1345897.38</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1609315.95</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>1556045.05</v>
+        <v>1642439.97</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -19741,80 +19741,80 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-1355173.76</v>
+        <v>1556045.05</v>
       </c>
       <c r="F62" s="37" t="n">
-        <v>-1355173.76</v>
+        <v>1556045.05</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-1458209.26</v>
+        <v>1556045.05</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-1495176.94</v>
+        <v>1556045.05</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-1694132.89</v>
+        <v>1556045.05</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-1958926.96</v>
+        <v>1556045.05</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>-1958926.96</v>
+        <v>1556045.05</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-1947502.68</v>
+        <v>1556045.05</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-1921894.59</v>
+        <v>1556045.05</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-1883783.76</v>
+        <v>1556045.05</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-2168677.85</v>
+        <v>1556045.05</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>-2168677.85</v>
+        <v>1556045.05</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>-2158730.94</v>
+        <v>1556045.05</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>-2082174.61</v>
+        <v>1556045.05</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>-2008195.05</v>
+        <v>1556045.05</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>-2136027.13</v>
+        <v>1556045.05</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>-2136027.13</v>
+        <v>1556045.05</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>-2043931.41</v>
+        <v>1556045.05</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>-1829812.12</v>
+        <v>1556045.05</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>-1685416.66</v>
+        <v>1556045.05</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>-1602845.17</v>
+        <v>1556045.05</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>-1602845.17</v>
+        <v>1556045.05</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>-1501261.29</v>
+        <v>1556045.05</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>-1276928.67</v>
+        <v>1556045.05</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -19836,80 +19836,80 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>비지배주주지분</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>-13776.85</v>
+        <v>-1355173.76</v>
       </c>
       <c r="F63" s="37" t="n">
-        <v>-13776.85</v>
+        <v>-1355173.76</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>-14925.61</v>
+        <v>-1458209.26</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>-18056.08</v>
+        <v>-1495176.94</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-22924.9</v>
+        <v>-1694132.89</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>-22553.68</v>
+        <v>-1958926.96</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>-22553.68</v>
+        <v>-1958926.96</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-25397.45</v>
+        <v>-1947502.68</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-27945.27</v>
+        <v>-1921894.59</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-31213.01</v>
+        <v>-1883783.76</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>-30137.4</v>
+        <v>-2168677.85</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>-30137.4</v>
+        <v>-2168677.85</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>-33614.48</v>
+        <v>-2158730.94</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>-37270.51</v>
+        <v>-2082174.61</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>-37902.17</v>
+        <v>-2008195.05</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>-45141.84</v>
+        <v>-2136027.13</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>-45141.84</v>
+        <v>-2136027.13</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>-47036.82</v>
+        <v>-2043931.41</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>-45203.09</v>
+        <v>-1829812.12</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>-48506.35</v>
+        <v>-1685416.66</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>-53899.37</v>
+        <v>-1602845.17</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>-53899.37</v>
+        <v>-1602845.17</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>-58448.98</v>
+        <v>-1501261.29</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>-61044.99</v>
+        <v>-1276928.67</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -19931,80 +19931,80 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>비지배주주지분</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4097267.11</v>
+        <v>-13776.85</v>
       </c>
       <c r="F64" s="37" t="n">
-        <v>4097267.11</v>
+        <v>-13776.85</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>4033564.06</v>
+        <v>-14925.61</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>4226155.14</v>
+        <v>-18056.08</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>4491617.36</v>
+        <v>-22924.9</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>3571937.4</v>
+        <v>-22553.68</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>3571937.4</v>
+        <v>-22553.68</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>3720467.85</v>
+        <v>-25397.45</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>3708426.59</v>
+        <v>-27945.27</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>3872126.22</v>
+        <v>-31213.01</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>3409207.6</v>
+        <v>-30137.4</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>3409207.6</v>
+        <v>-30137.4</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>3671870.99</v>
+        <v>-33614.48</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>3918501.59</v>
+        <v>-37270.51</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>3731177.19</v>
+        <v>-37902.17</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>3749451.11</v>
+        <v>-45141.84</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>3749451.11</v>
+        <v>-45141.84</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>3807958.51</v>
+        <v>-47036.82</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>3608957.33</v>
+        <v>-45203.09</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>3945345.92</v>
+        <v>-48506.35</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>4095039.94</v>
+        <v>-53899.37</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>4095039.94</v>
+        <v>-53899.37</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>4455492.78</v>
+        <v>-58448.98</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>4710353.4</v>
+        <v>-61044.99</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -20026,80 +20026,80 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>12138595.96</v>
+        <v>4097267.11</v>
       </c>
       <c r="F65" s="37" t="n">
-        <v>12138595.96</v>
+        <v>4097267.11</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>12286879.3</v>
+        <v>4033564.06</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>13796449.42</v>
+        <v>4226155.14</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>16861060.29</v>
+        <v>4491617.36</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>14491697.98</v>
+        <v>3571937.4</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>14491697.98</v>
+        <v>3571937.4</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>14651888.21</v>
+        <v>3720467.85</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>14981181.78</v>
+        <v>3708426.59</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>16599198.92</v>
+        <v>3872126.22</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>15593389.15</v>
+        <v>3409207.6</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>15593389.15</v>
+        <v>3409207.6</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>16359005.44</v>
+        <v>3671870.99</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>16778247.96</v>
+        <v>3918501.59</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>15075969.11</v>
+        <v>3731177.19</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>17194637.13</v>
+        <v>3749451.11</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>17194637.13</v>
+        <v>3749451.11</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>16281156.02</v>
+        <v>3807958.51</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>13941719.46</v>
+        <v>3608957.33</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>14539449.71</v>
+        <v>3945345.92</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>14948871.09</v>
+        <v>4095039.94</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>14948871.09</v>
+        <v>4095039.94</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>16568722.98</v>
+        <v>4455492.78</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>17959382.2</v>
+        <v>4710353.4</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -20121,80 +20121,80 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>2247063.78</v>
+        <v>12138595.96</v>
       </c>
       <c r="F66" s="37" t="n">
-        <v>2247063.78</v>
+        <v>12138595.96</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>2133513.58</v>
+        <v>12286879.3</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>2139053.68</v>
+        <v>13796449.42</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>3037361.36</v>
+        <v>16861060.29</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>3063381.34</v>
+        <v>14491697.98</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>3063381.34</v>
+        <v>14491697.98</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>2831768.51</v>
+        <v>14651888.21</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>3165213.52</v>
+        <v>14981181.78</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>3348103.32</v>
+        <v>16599198.92</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>3551161.25</v>
+        <v>15593389.15</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>3551161.25</v>
+        <v>15593389.15</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>3573130.58</v>
+        <v>16359005.44</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>3617735.85</v>
+        <v>16778247.96</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>3811952.19</v>
+        <v>15075969.11</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>3218241.49</v>
+        <v>17194637.13</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>3218241.49</v>
+        <v>17194637.13</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>3105959.59</v>
+        <v>16281156.02</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>2728837.49</v>
+        <v>13941719.46</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>2459777.99</v>
+        <v>14539449.71</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>2047792.26</v>
+        <v>14948871.09</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>2047792.26</v>
+        <v>14948871.09</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>1195828.85</v>
+        <v>16568722.98</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>1102144.31</v>
+        <v>17959382.2</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -20216,80 +20216,80 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>638535.3100000001</v>
+        <v>2247063.78</v>
       </c>
       <c r="F67" s="37" t="n">
-        <v>638535.3100000001</v>
+        <v>2247063.78</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>572071.46</v>
+        <v>2133513.58</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-901843.1</v>
+        <v>2139053.68</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-1495396.7</v>
+        <v>3037361.36</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>117286.3</v>
+        <v>3063381.34</v>
       </c>
       <c r="K67" s="37" t="n">
-        <v>117286.3</v>
+        <v>3063381.34</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>143361.33</v>
+        <v>2831768.51</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>290561.91</v>
+        <v>3165213.52</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>60148.1</v>
+        <v>3348103.32</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>1433002.02</v>
+        <v>3551161.25</v>
       </c>
       <c r="P67" s="37" t="n">
-        <v>1433002.02</v>
+        <v>3551161.25</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>696904.6899999999</v>
+        <v>3573130.58</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>804142.46</v>
+        <v>3617735.85</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>1673625.43</v>
+        <v>3811952.19</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>163338.39</v>
+        <v>3218241.49</v>
       </c>
       <c r="U67" s="37" t="n">
-        <v>163338.39</v>
+        <v>3218241.49</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>744420.65</v>
+        <v>3105959.59</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>999625.55</v>
+        <v>2728837.49</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>-102309.85</v>
+        <v>2459777.99</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>-81690.17999999999</v>
+        <v>2047792.26</v>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>-81690.17999999999</v>
+        <v>2047792.26</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>-1899206.73</v>
+        <v>1195828.85</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>-2062046.7</v>
+        <v>1102144.31</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -20311,80 +20311,80 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>1654204.2</v>
+        <v>638535.3100000001</v>
       </c>
       <c r="F68" s="37" t="n">
-        <v>1654204.2</v>
+        <v>638535.3100000001</v>
       </c>
       <c r="G68" s="18" t="n">
-        <v>1607873.38</v>
+        <v>572071.46</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>3087254.38</v>
+        <v>-901843.1</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>4578758.4</v>
+        <v>-1495396.7</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>3031841.04</v>
+        <v>117286.3</v>
       </c>
       <c r="K68" s="37" t="n">
-        <v>3031841.04</v>
+        <v>117286.3</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>2774179.54</v>
+        <v>143361.33</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>2960649.59</v>
+        <v>290561.91</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>3373879.62</v>
+        <v>60148.1</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>2205461.33</v>
+        <v>1433002.02</v>
       </c>
       <c r="P68" s="37" t="n">
-        <v>2205461.33</v>
+        <v>1433002.02</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>2963817.11</v>
+        <v>696904.6899999999</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>2901054.48</v>
+        <v>804142.46</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>2226751.34</v>
+        <v>1673625.43</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>3157244.54</v>
+        <v>163338.39</v>
       </c>
       <c r="U68" s="37" t="n">
-        <v>3157244.54</v>
+        <v>163338.39</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>2481499.01</v>
+        <v>744420.65</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>1849195.26</v>
+        <v>999625.55</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>2738983</v>
+        <v>-102309.85</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>2297860.74</v>
+        <v>-81690.17999999999</v>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>2297860.74</v>
+        <v>-81690.17999999999</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>3260818.8</v>
+        <v>-1899206.73</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>3346629.22</v>
+        <v>-2062046.7</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -20406,72 +20406,80 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="n">
+        <v>1654204.2</v>
+      </c>
+      <c r="F69" s="37" t="n">
+        <v>1654204.2</v>
+      </c>
       <c r="G69" s="18" t="n">
-        <v>7813.22</v>
+        <v>1607873.38</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>3406.07</v>
+        <v>3087254.38</v>
+      </c>
+      <c r="I69" s="18" t="n">
+        <v>4578758.4</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>23643.99</v>
+        <v>3031841.04</v>
       </c>
       <c r="K69" s="37" t="n">
-        <v>23643.99</v>
+        <v>3031841.04</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>30397.06</v>
+        <v>2774179.54</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>26102.37</v>
+        <v>2960649.59</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>22944.46</v>
+        <v>3373879.62</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>98825.3</v>
+        <v>2205461.33</v>
       </c>
       <c r="P69" s="37" t="n">
-        <v>98825.3</v>
+        <v>2205461.33</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>116821.81</v>
+        <v>2963817.11</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>135361.8</v>
+        <v>2901054.48</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>120208.56</v>
+        <v>2226751.34</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>260361.99</v>
+        <v>3157244.54</v>
       </c>
       <c r="U69" s="37" t="n">
-        <v>260361.99</v>
+        <v>3157244.54</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>229263.33</v>
+        <v>2481499.01</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>217866.14</v>
+        <v>1849195.26</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>206144.41</v>
+        <v>2738983</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>194567.72</v>
+        <v>2297860.74</v>
       </c>
       <c r="Z69" s="37" t="n">
-        <v>194567.72</v>
+        <v>2297860.74</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>191617.06</v>
+        <v>3260818.8</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>179711.06</v>
+        <v>3346629.22</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -25271,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28857,10 +28865,10 @@
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>13435.1</v>
+        <v>24825.79</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>13435.1</v>
+        <v>24825.79</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>24817.38</v>
@@ -28869,7 +28877,7 @@
         <v>20143.71</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>15516.04</v>
+        <v>18992.08</v>
       </c>
       <c r="J41" s="18" t="n">
         <v>56027.95</v>
@@ -29418,80 +29426,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>장기충당부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>61798.56</v>
+        <v>11390.69</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>61798.56</v>
+        <v>11390.69</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>39429.58</v>
+        <v>7813.22</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>38828.65</v>
+        <v>3406.07</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>26244.24</v>
+        <v>3476.04</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>28986.64</v>
+        <v>23643.99</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>28986.64</v>
+        <v>23643.99</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>19466.9</v>
+        <v>30397.06</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>23514.47</v>
+        <v>26102.37</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>26846.31</v>
+        <v>22944.46</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>29982.69</v>
+        <v>98825.3</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>29982.69</v>
+        <v>98825.3</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>32456.13</v>
+        <v>116821.81</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>37544.47</v>
+        <v>135361.8</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>36915.02</v>
+        <v>120208.56</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>41757.36</v>
+        <v>260361.99</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>41757.36</v>
+        <v>260361.99</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>50425.78</v>
+        <v>229263.33</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>50444.32</v>
+        <v>217866.14</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>55319.83</v>
+        <v>206144.41</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>63230.31</v>
+        <v>194567.72</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>63230.31</v>
+        <v>194567.72</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>67623.39999999999</v>
+        <v>191617.06</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>78883.57000000001</v>
+        <v>179711.06</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -29513,80 +29521,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>장기파생상품부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>417699.39</v>
+        <v>479089.84</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>417699.39</v>
+        <v>479089.84</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>395352.66</v>
+        <v>452918.94</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>786612.71</v>
+        <v>839257.29</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>1279017.55</v>
+        <v>1330963.56</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>274626.53</v>
+        <v>347495.09</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>274626.53</v>
+        <v>347495.09</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>188154.52</v>
+        <v>268670.88</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>139650.81</v>
+        <v>215812.93</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>124205.26</v>
+        <v>196576.95</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>105724.86</v>
+        <v>262487.58</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>105724.86</v>
+        <v>262487.58</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>199974.85</v>
+        <v>375087.08</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>394904.27</v>
+        <v>588591.04</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>121765.91</v>
+        <v>300027.7</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>914698.45</v>
+        <v>1235598.03</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>914698.45</v>
+        <v>1235598.03</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>864750.74</v>
+        <v>1157555.27</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>423500.26</v>
+        <v>704888.55</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>476332.47</v>
+        <v>746038.3</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>775354.91</v>
+        <v>1048424.18</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>775354.91</v>
+        <v>1048424.18</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>1467463.84</v>
+        <v>1737565</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>1564892.87</v>
+        <v>1823299.3</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -29608,80 +29616,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>장기충당부채</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>467699.15</v>
+        <v>61798.56</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>467699.15</v>
+        <v>61798.56</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>452918.94</v>
+        <v>39429.58</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>839257.29</v>
+        <v>38828.65</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>1327487.52</v>
+        <v>26244.24</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>347495.09</v>
+        <v>28986.64</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>347495.09</v>
+        <v>28986.64</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>268670.88</v>
+        <v>19466.9</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>215812.93</v>
+        <v>23514.47</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>196576.95</v>
+        <v>26846.31</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>262487.58</v>
+        <v>29982.69</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>262487.58</v>
+        <v>29982.69</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>375087.08</v>
+        <v>32456.13</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>588591.04</v>
+        <v>37544.47</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>300027.7</v>
+        <v>36915.02</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>1235598.03</v>
+        <v>41757.36</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>1235598.03</v>
+        <v>41757.36</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>1157555.27</v>
+        <v>50425.78</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>704888.55</v>
+        <v>50444.32</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>746038.3</v>
+        <v>55319.83</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>1048424.18</v>
+        <v>63230.31</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>1048424.18</v>
+        <v>63230.31</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>1737565</v>
+        <v>67623.39999999999</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>1823299.3</v>
+        <v>78883.57000000001</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -29703,80 +29711,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>기타비유동금융부채</t>
+          <t>장기파생상품부채</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>49999.76</v>
+        <v>417699.39</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>49999.76</v>
+        <v>417699.39</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>49753.06</v>
+        <v>395352.66</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>49238.51</v>
+        <v>786612.71</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>48469.97</v>
+        <v>1279017.55</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>49224.57</v>
+        <v>274626.53</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>49224.57</v>
+        <v>274626.53</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>50119.3</v>
+        <v>188154.52</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>50059.75</v>
+        <v>139650.81</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>49427.23</v>
+        <v>124205.26</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>57937.42</v>
+        <v>105724.86</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>57937.42</v>
+        <v>105724.86</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>58290.42</v>
+        <v>199974.85</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>58324.97</v>
+        <v>394904.27</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>58053.23</v>
+        <v>121765.91</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>60537.59</v>
+        <v>914698.45</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>60537.59</v>
+        <v>914698.45</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>63541.2</v>
+        <v>864750.74</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>63522.15</v>
+        <v>423500.26</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>63561.42</v>
+        <v>476332.47</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>78501.55</v>
+        <v>775354.91</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>78501.55</v>
+        <v>775354.91</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>78484.10000000001</v>
+        <v>1467463.84</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>78695.37</v>
+        <v>1564892.87</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -29798,80 +29806,80 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>기타비유동금융부채</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>7669432.61</v>
+        <v>49999.76</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>7669432.61</v>
+        <v>49999.76</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>7890281.19</v>
+        <v>49753.06</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>9821190.220000001</v>
+        <v>49238.51</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>12698813.3</v>
+        <v>48469.97</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>11186551.2</v>
+        <v>49224.57</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>11186551.2</v>
+        <v>49224.57</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>11136315.97</v>
+        <v>50119.3</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>11479477.72</v>
+        <v>50059.75</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>12970907.76</v>
+        <v>49427.23</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>12448525.75</v>
+        <v>57937.42</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>12448525.75</v>
+        <v>57937.42</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>12710795.72</v>
+        <v>58290.42</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>12849616.54</v>
+        <v>58324.97</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>11328558.26</v>
+        <v>58053.23</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>13275009.33</v>
+        <v>60537.59</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>13275009.33</v>
+        <v>60537.59</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>12322672.78</v>
+        <v>63541.2</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>10210365.18</v>
+        <v>63522.15</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>10446071.19</v>
+        <v>63561.42</v>
       </c>
       <c r="Y51" s="18" t="n">
-        <v>10706551.83</v>
+        <v>78501.55</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>10706551.83</v>
+        <v>78501.55</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>12003580.5</v>
+        <v>78484.10000000001</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>13115989.99</v>
+        <v>78695.37</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -29893,80 +29901,80 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>880114.84</v>
+        <v>7669432.61</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>880114.84</v>
+        <v>7669432.61</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>880114.84</v>
+        <v>7890281.19</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>880114.84</v>
+        <v>9821190.220000001</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12698813.3</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>880114.84</v>
+        <v>11186551.2</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>880114.84</v>
+        <v>11186551.2</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>880114.84</v>
+        <v>11136315.97</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>880114.84</v>
+        <v>11479477.72</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12970907.76</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12448525.75</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>880114.84</v>
+        <v>12448525.75</v>
       </c>
       <c r="Q52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12710795.72</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12849616.54</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>880114.84</v>
+        <v>11328558.26</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>880114.84</v>
+        <v>13275009.33</v>
       </c>
       <c r="U52" s="37" t="n">
-        <v>880114.84</v>
+        <v>13275009.33</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12322672.78</v>
       </c>
       <c r="W52" s="18" t="n">
-        <v>880114.84</v>
+        <v>10210365.18</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>880114.84</v>
+        <v>10446071.19</v>
       </c>
       <c r="Y52" s="18" t="n">
-        <v>880114.84</v>
+        <v>10706551.83</v>
       </c>
       <c r="Z52" s="37" t="n">
-        <v>880114.84</v>
+        <v>10706551.83</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>880114.84</v>
+        <v>12003580.5</v>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>880114.84</v>
+        <v>13115989.99</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -29988,80 +29996,80 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>보통주자본금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="F53" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="P53" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="Q53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="U53" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="V53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="W53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="X53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="Y53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="Z53" s="37" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="AA53" s="18" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="AB53" s="19" t="n">
-        <v>880000</v>
+        <v>880114.84</v>
       </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -30083,80 +30091,80 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>우선주자본금</t>
+          <t>보통주자본금</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="F54" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="N54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="O54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="P54" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="Q54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="S54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="T54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="U54" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="V54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="W54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="X54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="Y54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="Z54" s="37" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="AA54" s="18" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="AB54" s="19" t="n">
-        <v>114.84</v>
+        <v>880000</v>
       </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
@@ -30178,80 +30186,80 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>우선주자본금</t>
         </is>
       </c>
       <c r="E55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="F55" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="K55" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="P55" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="Q55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="R55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="S55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="T55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="U55" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="V55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="W55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="X55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="Y55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="Z55" s="37" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="AA55" s="18" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="AB55" s="19" t="n">
-        <v>1969727.2</v>
+        <v>114.84</v>
       </c>
       <c r="AC55" s="10" t="n"/>
       <c r="AD55" s="10" t="n"/>
@@ -30273,80 +30281,80 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E56" s="18" t="n">
-        <v>1173140.79</v>
+        <v>1969727.2</v>
       </c>
       <c r="F56" s="37" t="n">
-        <v>1173140.79</v>
+        <v>1969727.2</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>1208455.35</v>
+        <v>1969727.2</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>1427756.67</v>
+        <v>1969727.2</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>1875453.65</v>
+        <v>1969727.2</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>1267458.63</v>
+        <v>1969727.2</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>1267458.63</v>
+        <v>1969727.2</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>1390770.61</v>
+        <v>1969727.2</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>1370585.95</v>
+        <v>1969727.2</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>1518179.33</v>
+        <v>1969727.2</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>1308612.03</v>
+        <v>1969727.2</v>
       </c>
       <c r="P56" s="37" t="n">
-        <v>1308612.03</v>
+        <v>1969727.2</v>
       </c>
       <c r="Q56" s="18" t="n">
-        <v>1561439.31</v>
+        <v>1969727.2</v>
       </c>
       <c r="R56" s="18" t="n">
-        <v>1729108.56</v>
+        <v>1969727.2</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>1454060.34</v>
+        <v>1969727.2</v>
       </c>
       <c r="T56" s="18" t="n">
-        <v>1603542.16</v>
+        <v>1969727.2</v>
       </c>
       <c r="U56" s="37" t="n">
-        <v>1603542.16</v>
+        <v>1969727.2</v>
       </c>
       <c r="V56" s="18" t="n">
-        <v>1570252.52</v>
+        <v>1969727.2</v>
       </c>
       <c r="W56" s="18" t="n">
-        <v>1167907.04</v>
+        <v>1969727.2</v>
       </c>
       <c r="X56" s="18" t="n">
-        <v>1356493.11</v>
+        <v>1969727.2</v>
       </c>
       <c r="Y56" s="18" t="n">
-        <v>1420867.53</v>
+        <v>1969727.2</v>
       </c>
       <c r="Z56" s="37" t="n">
-        <v>1420867.53</v>
+        <v>1969727.2</v>
       </c>
       <c r="AA56" s="18" t="n">
-        <v>1669663</v>
+        <v>1969727.2</v>
       </c>
       <c r="AB56" s="19" t="n">
-        <v>1694099.07</v>
+        <v>1969727.2</v>
       </c>
       <c r="AC56" s="10" t="n"/>
       <c r="AD56" s="10" t="n"/>
@@ -30368,80 +30376,80 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1173140.79</v>
       </c>
       <c r="F57" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1173140.79</v>
       </c>
       <c r="G57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1208455.35</v>
       </c>
       <c r="H57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1427756.67</v>
       </c>
       <c r="I57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1875453.65</v>
       </c>
       <c r="J57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1267458.63</v>
       </c>
       <c r="K57" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1267458.63</v>
       </c>
       <c r="L57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1390770.61</v>
       </c>
       <c r="M57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1370585.95</v>
       </c>
       <c r="N57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1518179.33</v>
       </c>
       <c r="O57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1308612.03</v>
       </c>
       <c r="P57" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1308612.03</v>
       </c>
       <c r="Q57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1561439.31</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1729108.56</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1454060.34</v>
       </c>
       <c r="T57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1603542.16</v>
       </c>
       <c r="U57" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1603542.16</v>
       </c>
       <c r="V57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1570252.52</v>
       </c>
       <c r="W57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1167907.04</v>
       </c>
       <c r="X57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1356493.11</v>
       </c>
       <c r="Y57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1420867.53</v>
       </c>
       <c r="Z57" s="37" t="n">
-        <v>1556045.05</v>
+        <v>1420867.53</v>
       </c>
       <c r="AA57" s="18" t="n">
-        <v>1556045.05</v>
+        <v>1669663</v>
       </c>
       <c r="AB57" s="19" t="n">
-        <v>1556045.05</v>
+        <v>1694099.07</v>
       </c>
       <c r="AC57" s="10" t="n"/>
       <c r="AD57" s="10" t="n"/>
@@ -30463,80 +30471,80 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-1356322.93</v>
+        <v>1556045.05</v>
       </c>
       <c r="F58" s="37" t="n">
-        <v>-1356322.93</v>
+        <v>1556045.05</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-1441919.24</v>
+        <v>1556045.05</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-1693475.44</v>
+        <v>1556045.05</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-1918015.28</v>
+        <v>1556045.05</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-2120523.2</v>
+        <v>1556045.05</v>
       </c>
       <c r="K58" s="37" t="n">
-        <v>-2120523.2</v>
+        <v>1556045.05</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-2049465.42</v>
+        <v>1556045.05</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-1989763.65</v>
+        <v>1556045.05</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-1967528.89</v>
+        <v>1556045.05</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-2271046.14</v>
+        <v>1556045.05</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>-2271046.14</v>
+        <v>1556045.05</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>-2337263.75</v>
+        <v>1556045.05</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>-2276935.88</v>
+        <v>1556045.05</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>-2200158.91</v>
+        <v>1556045.05</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>-2286584.91</v>
+        <v>1556045.05</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>-2286584.91</v>
+        <v>1556045.05</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>-2184703.03</v>
+        <v>1556045.05</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>-1966242.59</v>
+        <v>1556045.05</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>-1820555.79</v>
+        <v>1556045.05</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>-1758618.09</v>
+        <v>1556045.05</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>-1758618.09</v>
+        <v>1556045.05</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>-1643215.54</v>
+        <v>1556045.05</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>-1417785.06</v>
+        <v>1556045.05</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -30558,80 +30566,80 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>4222704.96</v>
+        <v>-1356322.93</v>
       </c>
       <c r="F59" s="37" t="n">
-        <v>4222704.96</v>
+        <v>-1356322.93</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>4172423.21</v>
+        <v>-1441919.24</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>4140168.34</v>
+        <v>-1693475.44</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>4363325.47</v>
+        <v>-1918015.28</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>3552822.52</v>
+        <v>-2120523.2</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>3552822.52</v>
+        <v>-2120523.2</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>3747192.29</v>
+        <v>-2049465.42</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>3786709.4</v>
+        <v>-1989763.65</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>3956537.54</v>
+        <v>-1967528.89</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>3443452.99</v>
+        <v>-2271046.14</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>3443452.99</v>
+        <v>-2271046.14</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>3630062.66</v>
+        <v>-2337263.75</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>3858059.77</v>
+        <v>-2276935.88</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>3659788.53</v>
+        <v>-2200158.91</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>3722844.35</v>
+        <v>-2286584.91</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>3722844.35</v>
+        <v>-2286584.91</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>3791436.59</v>
+        <v>-2184703.03</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>3607551.55</v>
+        <v>-1966242.59</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>3941824.42</v>
+        <v>-1820555.79</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>4068136.54</v>
+        <v>-1758618.09</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>4068136.54</v>
+        <v>-1758618.09</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>4432334.56</v>
+        <v>-1643215.54</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>4682201.11</v>
+        <v>-1417785.06</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -30653,80 +30661,80 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>11892137.57</v>
+        <v>4222704.96</v>
       </c>
       <c r="F60" s="37" t="n">
-        <v>11892137.57</v>
+        <v>4222704.96</v>
       </c>
       <c r="G60" s="18" t="n">
-        <v>12062704.4</v>
+        <v>4172423.21</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>13961358.56</v>
+        <v>4140168.34</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>17062138.77</v>
+        <v>4363325.47</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>14739373.72</v>
+        <v>3552822.52</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>14739373.72</v>
+        <v>3552822.52</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>14883508.26</v>
+        <v>3747192.29</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>15266187.11</v>
+        <v>3786709.4</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>16927445.3</v>
+        <v>3956537.54</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>15891978.74</v>
+        <v>3443452.99</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>15891978.74</v>
+        <v>3443452.99</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>16340858.38</v>
+        <v>3630062.66</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>16707676.31</v>
+        <v>3858059.77</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>14988346.79</v>
+        <v>3659788.53</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>16997853.68</v>
+        <v>3722844.35</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>16997853.68</v>
+        <v>3722844.35</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>16114109.37</v>
+        <v>3791436.59</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>13817916.73</v>
+        <v>3607551.55</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>14387895.61</v>
+        <v>3941824.42</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>14774688.37</v>
+        <v>4068136.54</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>14774688.37</v>
+        <v>4068136.54</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>16435915.06</v>
+        <v>4432334.56</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>17798191.1</v>
+        <v>4682201.11</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -30748,80 +30756,80 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>4222704.96</v>
+        <v>11892137.57</v>
       </c>
       <c r="F61" s="37" t="n">
-        <v>4222704.96</v>
+        <v>11892137.57</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>4172423.21</v>
+        <v>12062704.4</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>4140168.34</v>
+        <v>13961358.56</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>4363325.47</v>
+        <v>17062138.77</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>3552822.52</v>
+        <v>14739373.72</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>3552822.52</v>
+        <v>14739373.72</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>3747192.29</v>
+        <v>14883508.26</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>3786709.4</v>
+        <v>15266187.11</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>3956537.54</v>
+        <v>16927445.3</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>3443452.99</v>
+        <v>15891978.74</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>3443452.99</v>
+        <v>15891978.74</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>3630062.66</v>
+        <v>16340858.38</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>3858059.77</v>
+        <v>16707676.31</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>3659788.53</v>
+        <v>14988346.79</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>3722844.35</v>
+        <v>16997853.68</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>3722844.35</v>
+        <v>16997853.68</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>3791436.59</v>
+        <v>16114109.37</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>3607551.55</v>
+        <v>13817916.73</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>3941824.42</v>
+        <v>14387895.61</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>4068136.54</v>
+        <v>14774688.37</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>4068136.54</v>
+        <v>14774688.37</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>4432334.56</v>
+        <v>16435915.06</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>4682201.11</v>
+        <v>17798191.1</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -30843,80 +30851,80 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>2126684.13</v>
+        <v>4222704.96</v>
       </c>
       <c r="F62" s="37" t="n">
-        <v>2126684.13</v>
+        <v>4222704.96</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>2022845.2</v>
+        <v>4172423.21</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>2751734.18</v>
+        <v>4140168.34</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>3605868.78</v>
+        <v>4363325.47</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>3658829.22</v>
+        <v>3552822.52</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>3658829.22</v>
+        <v>3552822.52</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>3441273.32</v>
+        <v>3747192.29</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>3959458.77</v>
+        <v>3786709.4</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>4206833.43</v>
+        <v>3956537.54</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>4439375.92</v>
+        <v>3443452.99</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>4439375.92</v>
+        <v>3443452.99</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>3912757.9</v>
+        <v>3630062.66</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>3741791.38</v>
+        <v>3858059.77</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>3932747.73</v>
+        <v>3659788.53</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>3077891.94</v>
+        <v>3722844.35</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>3077891.94</v>
+        <v>3722844.35</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>2987072.74</v>
+        <v>3791436.59</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>2636246.14</v>
+        <v>3607551.55</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>2345905.64</v>
+        <v>3941824.42</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>1919683.76</v>
+        <v>4068136.54</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>1919683.76</v>
+        <v>4068136.54</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>1110049.47</v>
+        <v>4432334.56</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>1006203.6</v>
+        <v>4682201.11</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -30938,80 +30946,80 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>605419.52</v>
+        <v>2126684.13</v>
       </c>
       <c r="F63" s="37" t="n">
-        <v>605419.52</v>
+        <v>2126684.13</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>550320.9399999999</v>
+        <v>2022845.2</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>169615.1</v>
+        <v>2751734.18</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-476850.85</v>
+        <v>3605868.78</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>1150323.56</v>
+        <v>3658829.22</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>1150323.56</v>
+        <v>3658829.22</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>855007.42</v>
+        <v>3441273.32</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>1166956.65</v>
+        <v>3959458.77</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>1044933.02</v>
+        <v>4206833.43</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>2408393.48</v>
+        <v>4439375.92</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>2408393.48</v>
+        <v>4439375.92</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>1067273.73</v>
+        <v>3912757.9</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1011954.2</v>
+        <v>3741791.38</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>1875956.45</v>
+        <v>3932747.73</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>107411.89</v>
+        <v>3077891.94</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>107411.89</v>
+        <v>3077891.94</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>683280.5600000001</v>
+        <v>2987072.74</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>970250.91</v>
+        <v>2636246.14</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>-130465.89</v>
+        <v>2345905.64</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>-98414.38</v>
+        <v>1919683.76</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>-98414.38</v>
+        <v>1919683.76</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>-1930189.71</v>
+        <v>1110049.47</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>-2099373.79</v>
+        <v>1006203.6</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -31033,80 +31041,80 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>1566672.49</v>
+        <v>605419.52</v>
       </c>
       <c r="F64" s="37" t="n">
-        <v>1566672.49</v>
+        <v>605419.52</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>1518735.18</v>
+        <v>550320.9399999999</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>2628181.78</v>
+        <v>169615.1</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>4128421.65</v>
+        <v>-476850.85</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>2594022.34</v>
+        <v>1150323.56</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>2594022.34</v>
+        <v>1150323.56</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>2671805.94</v>
+        <v>855007.42</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>2878279.1</v>
+        <v>1166956.65</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>3247611.83</v>
+        <v>1044933.02</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>2117902.78</v>
+        <v>2408393.48</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>2117902.78</v>
+        <v>2408393.48</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>2932683.36</v>
+        <v>1067273.73</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>2837881.92</v>
+        <v>1011954.2</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>2164730.54</v>
+        <v>1875956.45</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>3094541.87</v>
+        <v>107411.89</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>3094541.87</v>
+        <v>107411.89</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>2445422.25</v>
+        <v>683280.5600000001</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>1839930.69</v>
+        <v>970250.91</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>2709048.35</v>
+        <v>-130465.89</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>2241560.73</v>
+        <v>-98414.38</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>2241560.73</v>
+        <v>-98414.38</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>3264242.14</v>
+        <v>-1930189.71</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>3345350.7</v>
+        <v>-2099373.79</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -31128,75 +31136,80 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>사용권자산</t>
-        </is>
-      </c>
-      <c r="F65" s="9" t="n"/>
+          <t>이자발생자산</t>
+        </is>
+      </c>
+      <c r="E65" s="18" t="n">
+        <v>1566672.49</v>
+      </c>
+      <c r="F65" s="37" t="n">
+        <v>1566672.49</v>
+      </c>
       <c r="G65" s="18" t="n">
-        <v>6872.69</v>
+        <v>1518735.18</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>5705.09</v>
+        <v>2628181.78</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>7436.78</v>
+        <v>4128421.65</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>47000.66</v>
+        <v>2594022.34</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>47000.66</v>
+        <v>2594022.34</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>74199.03</v>
+        <v>2671805.94</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>66576.89999999999</v>
+        <v>2878279.1</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>57470.06</v>
+        <v>3247611.83</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>127772.18</v>
+        <v>2117902.78</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>127772.18</v>
+        <v>2117902.78</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>195986.43</v>
+        <v>2932683.36</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>210758.81</v>
+        <v>2837881.92</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>188268.89</v>
+        <v>2164730.54</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>211609.24</v>
+        <v>3094541.87</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>211609.24</v>
+        <v>3094541.87</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>195180.18</v>
+        <v>2445422.25</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>176638.97</v>
+        <v>1839930.69</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>165683.35</v>
+        <v>2709048.35</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>145255.68</v>
+        <v>2241560.73</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>145255.68</v>
+        <v>2241560.73</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>149095.69</v>
+        <v>3264242.14</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>124052.11</v>
+        <v>3345350.7</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -31218,72 +31231,75 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>사용권자산</t>
         </is>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>7813.22</v>
+        <v>6872.69</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>3406.07</v>
+        <v>5705.09</v>
+      </c>
+      <c r="I66" s="18" t="n">
+        <v>7436.78</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>23643.99</v>
+        <v>47000.66</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>23643.99</v>
+        <v>47000.66</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>30397.06</v>
+        <v>74199.03</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>26102.37</v>
+        <v>66576.89999999999</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>22944.46</v>
+        <v>57470.06</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>98825.3</v>
+        <v>127772.18</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>98825.3</v>
+        <v>127772.18</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>116821.81</v>
+        <v>195986.43</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>135361.8</v>
+        <v>210758.81</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>120208.56</v>
+        <v>188268.89</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>260361.99</v>
+        <v>211609.24</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>260361.99</v>
+        <v>211609.24</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>229263.33</v>
+        <v>195180.18</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>217866.14</v>
+        <v>176638.97</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>206144.41</v>
+        <v>165683.35</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>194567.72</v>
+        <v>145255.68</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>194567.72</v>
+        <v>145255.68</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>191617.06</v>
+        <v>149095.69</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>179711.06</v>
+        <v>124052.11</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -40689,7 +40705,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(조선해양) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(조선해양) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18" t="n"/>
@@ -56904,7 +56920,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님</t>
+          <t>출처: forecast_panel.json.gz scenarios.{conservative,base,optimistic}.quarterly[].new_order_revenue (KRW_million → 억원 ÷100) — 공시 수주 체결 분기별 상계 후(net_panel) · calibrated=False · 행(subQ)에 포함된 시나리오: base. 보수/낙관/기존만 은 합산하지 않는다. 모델 산출값 — 목표주가·추천 아님</t>
         </is>
       </c>
     </row>
@@ -57688,39 +57704,39 @@
         <v>0</v>
       </c>
       <c r="F18" s="34" t="n">
-        <v>338.54</v>
+        <v>0</v>
       </c>
       <c r="G18" s="20">
         <f>SUM(E18:F18)</f>
         <v/>
       </c>
       <c r="H18" s="34" t="n">
-        <v>1269.27</v>
+        <v>202.96</v>
       </c>
       <c r="I18" s="34" t="n">
-        <v>2664.86</v>
+        <v>896.53</v>
       </c>
       <c r="J18" s="34" t="n">
-        <v>4397.96</v>
+        <v>2105.95</v>
       </c>
       <c r="K18" s="34" t="n">
-        <v>6341.88</v>
+        <v>3703.88</v>
       </c>
       <c r="L18" s="20">
         <f>SUM(H18:K18)</f>
         <v/>
       </c>
       <c r="M18" s="34" t="n">
-        <v>8394.040000000001</v>
+        <v>5563.38</v>
       </c>
       <c r="N18" s="34" t="n">
-        <v>10449.47</v>
+        <v>7572.18</v>
       </c>
       <c r="O18" s="34" t="n">
-        <v>12394.12</v>
+        <v>9626.299999999999</v>
       </c>
       <c r="P18" s="34" t="n">
-        <v>14113.92</v>
+        <v>11615.32</v>
       </c>
       <c r="Q18" s="20">
         <f>SUM(M18:P18)</f>
@@ -57994,39 +58010,39 @@
         <v>0</v>
       </c>
       <c r="F24" s="34" t="n">
-        <v>1106.18</v>
+        <v>381.61</v>
       </c>
       <c r="G24" s="20">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
       <c r="H24" s="34" t="n">
-        <v>4057.61</v>
+        <v>1961.25</v>
       </c>
       <c r="I24" s="34" t="n">
-        <v>8303.59</v>
+        <v>5087.17</v>
       </c>
       <c r="J24" s="34" t="n">
-        <v>13293.43</v>
+        <v>9398.879999999999</v>
       </c>
       <c r="K24" s="34" t="n">
-        <v>18488.76</v>
+        <v>14349.92</v>
       </c>
       <c r="L24" s="20">
         <f>SUM(H24:K24)</f>
         <v/>
       </c>
       <c r="M24" s="34" t="n">
-        <v>23813.75</v>
+        <v>19559.68</v>
       </c>
       <c r="N24" s="34" t="n">
-        <v>29147.25</v>
+        <v>24868.49</v>
       </c>
       <c r="O24" s="34" t="n">
-        <v>34193.29</v>
+        <v>30101.56</v>
       </c>
       <c r="P24" s="34" t="n">
-        <v>38655.89</v>
+        <v>34988.72</v>
       </c>
       <c r="Q24" s="20">
         <f>SUM(M24:P24)</f>
@@ -63075,7 +63091,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(조선해양) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(조선해양) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18">
@@ -65824,7 +65840,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>매출 조선·해양(조선해양) 신규수주(forecast_panel base — 매출조선에 포함)</t>
+          <t>매출 조선·해양(조선해양) 신규수주(forecast_panel base(공시 상계) — 매출조선에 포함)</t>
         </is>
       </c>
       <c r="E39" s="18">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="SLS" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="시나리오" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="분기" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="연간예상" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="외화" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 24433억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 24431억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3090억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23895억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3093억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23699억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23723억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19955억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19975억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18519억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18538억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17893억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 17911억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3138억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15396억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3141억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38779억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38778억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41524억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44398억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44401억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47437억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47442억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50740억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50747억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54104억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54113억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57667억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57678억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61495억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61507억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 38779억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 38778억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41524억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44398억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44401억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47437억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47442억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50740억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50747억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 54104억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54113억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57667억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57678억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61495억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61507억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 24433억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 24431억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23871억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3090억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23895억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3093억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23699억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23723억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23027억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19955억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19975억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18519억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3124억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18538억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17893억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3159억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 17911억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15380억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3138억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15396억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3141억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,203억 vs 54억 · 2027 12,532억 vs 16,454억 · 2028 12,546억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,203억 vs 54억 · 2027 12,545억 vs 16,454억 · 2028 12,559억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1280</v>
+        <v>1280.4</v>
       </c>
     </row>
     <row r="30">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2291</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="34">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18890</v>
+        <v>18900</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19560</v>
+        <v>19562</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005525432</v>
+        <v>-0.005267365</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.010284369</v>
+        <v>-0.009146474999999999</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.0002603</v>
+        <v>0.000349108</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.002958888</v>
+        <v>5.5327e-05</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.002353551</v>
+        <v>0.00273027</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.001526557</v>
+        <v>0.0005186429999999999</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.003184867</v>
+        <v>0.001719344</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.003623298</v>
+        <v>-0.004266916</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.003856141</v>
+        <v>0.005383531</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.00392748</v>
+        <v>0.004102383</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.005525432</v>
+        <v>-0.005267365</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.010284369</v>
+        <v>-0.009146474999999999</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.0002603</v>
+        <v>0.000349108</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.002958888</v>
+        <v>5.5327e-05</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.002353551</v>
+        <v>0.00273027</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.001526557</v>
+        <v>0.0005186429999999999</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.003184867</v>
+        <v>0.001719344</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.003623298</v>
+        <v>-0.004266916</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.003856141</v>
+        <v>0.005383531</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.00392748</v>
+        <v>0.004102383</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.117715082</v>
+        <v>0.117707324</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.105799242</v>
+        <v>0.105872472</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.10027493</v>
+        <v>0.100334541</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.09631724</v>
+        <v>0.096364306</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.09548733500000001</v>
+        <v>0.09552529899999999</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.08878535999999999</v>
+        <v>0.088810351</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.086365937</v>
+        <v>0.086383321</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.08539991600000001</v>
+        <v>0.085412396</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.080810124</v>
+        <v>0.08081609300000001</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.07576588099999999</v>
+        <v>0.075760888</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.070752313</v>
+        <v>0.07080112199999999</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.06925260900000001</v>
+        <v>0.069295049</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.068449251</v>
+        <v>0.068484947</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.069629422</v>
+        <v>0.069660055</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.066307461</v>
+        <v>0.066329333</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.065860061</v>
+        <v>0.065876849</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.066376659</v>
+        <v>0.06638957500000001</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.06392956299999999</v>
+        <v>0.063937511</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>13156.60201</v>
+        <v>13156.352722</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>13089.775426</v>
+        <v>13093.029906</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>13123.960798</v>
+        <v>13127.254696</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>13158.358937</v>
+        <v>13161.686022</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>13158.372728</v>
+        <v>13161.699827</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>13124.14133</v>
+        <v>13127.439217</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13124.034647</v>
+        <v>13127.323267</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>13158.44168</v>
+        <v>13161.766333</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>13137.889298</v>
+        <v>13141.195321</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099458904</v>
+        <v>0.099458926</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.099459063</v>
+        <v>0.099458979</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.09968990799999999</v>
+        <v>0.099689921</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.09980491800000001</v>
+        <v>0.099805116</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.09980497300000001</v>
+        <v>0.09980491399999999</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.099980605</v>
+        <v>0.099980614</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.09998066</v>
+        <v>0.099980579</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980712</v>
+        <v>0.099980719</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.099980556</v>
+        <v>0.099980685</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>18890</v>
+        <v>18900</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,700원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,540원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200001171455724</v>
+        <v>0.2199997462877507</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463851706803693</v>
+        <v>0.04463843968357698</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229708462849534</v>
+        <v>0.01229747721816401</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576840017629073</v>
+        <v>0.0557700431890551</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -42516,37 +42516,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.327</v>
+        <v>1817.343</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.322</v>
+        <v>1778.338</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.73</v>
+        <v>1724.746</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.112</v>
+        <v>1656.128</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.112</v>
+        <v>1656.128</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.856</v>
+        <v>1406.872</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.469</v>
+        <v>1305.485</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.713</v>
+        <v>1260.729</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.645</v>
+        <v>1081.661</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>756.97</v>
+        <v>756.985</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.6609999999999</v>
+        <v>589.672</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42576,16 +42576,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.592</v>
+        <v>6362.608</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.276</v>
+        <v>6815.34</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5054.683</v>
+        <v>5054.747</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.834</v>
+        <v>2035.86</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42660,37 +42660,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.192</v>
+        <v>1728.208</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.124</v>
+        <v>1691.14</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.562</v>
+        <v>1677.578</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.811</v>
+        <v>1628.827</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.811</v>
+        <v>1628.827</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.856</v>
+        <v>1406.872</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.469</v>
+        <v>1305.485</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.713</v>
+        <v>1260.729</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.645</v>
+        <v>1081.661</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>756.97</v>
+        <v>756.985</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.6609999999999</v>
+        <v>589.672</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42720,16 +42720,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6008.958</v>
+        <v>6008.974</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.308</v>
+        <v>6626.372</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5054.683</v>
+        <v>5054.747</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.834</v>
+        <v>2035.86</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43134,37 +43134,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>832.996</v>
+        <v>833.0119999999999</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.39</v>
+        <v>815.4059999999999</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.097</v>
+        <v>792.1130000000001</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.616</v>
+        <v>733.6319999999999</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.616</v>
+        <v>733.6319999999999</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.721</v>
+        <v>691.737</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.155</v>
+        <v>665.171</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.699</v>
+        <v>625.715</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.1</v>
+        <v>448.116</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.78</v>
+        <v>315.795</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.903</v>
+        <v>199.913</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43176,16 +43176,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.902</v>
+        <v>2583.918</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3074.719</v>
+        <v>3074.783</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2430.675</v>
+        <v>2430.739</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.849</v>
+        <v>595.874</v>
       </c>
     </row>
     <row r="11">
@@ -43446,37 +43446,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.192</v>
+        <v>1728.208</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.124</v>
+        <v>1691.14</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.562</v>
+        <v>1677.578</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.811</v>
+        <v>1628.827</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.811</v>
+        <v>1628.827</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.856</v>
+        <v>1406.872</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.469</v>
+        <v>1305.485</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.713</v>
+        <v>1260.729</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.645</v>
+        <v>1081.661</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>756.97</v>
+        <v>756.985</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.6609999999999</v>
+        <v>589.672</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43506,16 +43506,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5485.019</v>
+        <v>5485.035</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.308</v>
+        <v>6626.372</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5054.683</v>
+        <v>5054.747</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.834</v>
+        <v>2035.86</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43806,37 +43806,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439.07</v>
+        <v>1439.05</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1439.04</v>
+        <v>1439.03</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.83</v>
+        <v>1441.82</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.84</v>
+        <v>1443.82</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.84</v>
+        <v>1443.82</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.56</v>
+        <v>1452.54</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.82</v>
+        <v>1452.8</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.85</v>
+        <v>1453.83</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.61</v>
+        <v>1457.59</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.27</v>
+        <v>1463.24</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.79</v>
+        <v>1465.76</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43923,52 +43923,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
     </row>
     <row r="18">
@@ -44040,52 +44040,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1411.21</v>
+        <v>1411.06</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1408.93</v>
+        <v>1410.36</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1410.89</v>
+        <v>1412.31</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1412.29</v>
+        <v>1413.71</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1412.29</v>
+        <v>1413.71</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1418.4</v>
+        <v>1419.82</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1418.58</v>
+        <v>1420</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1419.3</v>
+        <v>1420.72</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1421.93</v>
+        <v>1423.35</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1425.9</v>
+        <v>1427.31</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1427.66</v>
+        <v>1429.07</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1431.44</v>
+        <v>1432.88</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1441.38</v>
+        <v>1442.81</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1449.57</v>
+        <v>1451</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1452.83</v>
+        <v>1454.26</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1452.83</v>
+        <v>1454.26</v>
       </c>
     </row>
     <row r="19">
@@ -44157,52 +44157,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2564623.4</v>
+        <v>2564379.1</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2505540</v>
+        <v>2508091.2</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2433402.3</v>
+        <v>2435876.9</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2338913.7</v>
+        <v>2341290.1</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2338913.7</v>
+        <v>2341290.1</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1995482.8</v>
+        <v>1997502.5</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1851914.4</v>
+        <v>1853789</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1789333.1</v>
+        <v>1791143.7</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1538025.8</v>
+        <v>1539580.2</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1079360.8</v>
+        <v>1080450.5</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>841835</v>
+        <v>842683.2</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>618147</v>
+        <v>618765</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>370965.9</v>
+        <v>371334.2</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>263953.6</v>
+        <v>264214.2</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252452.7</v>
+        <v>252701.4</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52709.9</v>
+        <v>52761.8</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44217,19 +44217,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9101931.6</v>
+        <v>9101687.300000001</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9616769.699999999</v>
+        <v>9626548.300000001</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7174756.1</v>
+        <v>7182015.4</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2910308.7</v>
+        <v>2913232.9</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>569116.2</v>
+        <v>569677.4</v>
       </c>
     </row>
     <row r="20">
@@ -44301,52 +44301,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2443327.6</v>
+        <v>2443095.6</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2387077.5</v>
+        <v>2389503.9</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2369893.4</v>
+        <v>2372300.5</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2302684.6</v>
+        <v>2305022</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2302684.6</v>
+        <v>2305022</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1995482.8</v>
+        <v>1997502.5</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1851914.4</v>
+        <v>1853789</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1789333.1</v>
+        <v>1791143.7</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1538025.8</v>
+        <v>1539580.2</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1079360.8</v>
+        <v>1080450.5</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>841835</v>
+        <v>842683.2</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>618147</v>
+        <v>618765</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>370965.9</v>
+        <v>371334.2</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>263953.6</v>
+        <v>264214.2</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252452.7</v>
+        <v>252701.4</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52709.9</v>
+        <v>52761.8</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44361,19 +44361,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8611512.1</v>
+        <v>8611280.1</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9362340.1</v>
+        <v>9371848.4</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7174756.1</v>
+        <v>7182015.4</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2910308.7</v>
+        <v>2913232.9</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>569116.2</v>
+        <v>569677.4</v>
       </c>
     </row>
     <row r="21">
@@ -44445,52 +44445,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2127637.2</v>
+        <v>2127430.1</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2078077</v>
+        <v>2080177.6</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2057459.6</v>
+        <v>2059537.2</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1986817.5</v>
+        <v>1988821.8</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1986817.5</v>
+        <v>1988821.8</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1683049</v>
+        <v>1684739.3</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1539480.7</v>
+        <v>1541025.8</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1473466</v>
+        <v>1474943.5</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1224207.8</v>
+        <v>1225431.2</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>816465.6</v>
+        <v>817276.7</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>609050.2</v>
+        <v>609653.6</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>469595.7</v>
+        <v>470061.3</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>348706.4</v>
+        <v>349051.9</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249678.5</v>
+        <v>249924.4</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252452.7</v>
+        <v>252701.4</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52709.9</v>
+        <v>52761.8</v>
       </c>
     </row>
     <row r="22">
@@ -44562,46 +44562,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315690.4</v>
+        <v>315665.4</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>309000.4</v>
+        <v>309326.3</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312433.8</v>
+        <v>312763.2</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>315867.1</v>
+        <v>316200.2</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>315867.1</v>
+        <v>316200.2</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312433.8</v>
+        <v>312763.2</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312433.8</v>
+        <v>312763.2</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>315867.1</v>
+        <v>316200.2</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>313818</v>
+        <v>314149</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>262895.2</v>
+        <v>263173.7</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>232784.8</v>
+        <v>233029.6</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148551.3</v>
+        <v>148703.7</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22259.5</v>
+        <v>22282.3</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14275.1</v>
+        <v>14289.7</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44855,67 +44855,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1346.2)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1345.74)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1338.69)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
         <v/>
       </c>
     </row>
@@ -49522,43 +49522,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.7</v>
+        <v>46.716</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.187</v>
+        <v>46.203</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.7</v>
+        <v>46.716</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.213</v>
+        <v>47.229</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.213</v>
+        <v>47.229</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.7</v>
+        <v>46.716</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.7</v>
+        <v>46.716</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.213</v>
+        <v>47.229</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.213</v>
+        <v>47.229</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.187</v>
+        <v>46.203</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.305</v>
+        <v>31.316</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49577,7 +49577,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>499.331</v>
+        <v>499.502</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56716,10 +56716,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>499.331</v>
+        <v>499.502</v>
       </c>
       <c r="F197" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 24431억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 24428억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23895억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3093억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23723억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19975억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18538억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17911억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15396억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3141억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15389억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2329,43 +2329,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41524억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41523억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44401억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44400억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47442억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47440억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50747억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50744억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54113억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54109억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57678억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61507억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2389,43 +2389,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41524억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41523억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44401억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44400억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47442억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47440억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50747억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50744억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 54113억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54109억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57678억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61507억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 24431억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3157억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 24428억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23895억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3093억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23723억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23050억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19975억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18538억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3128억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17911억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3162억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15396억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3141억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15389억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,203억 vs 54억 · 2027 12,545억 vs 16,454억 · 2028 12,559억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,203억 vs 54억 · 2027 12,540억 vs 16,454억 · 2028 12,554억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1280.4</v>
+        <v>1280.1</v>
       </c>
     </row>
     <row r="30">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2292</v>
+        <v>0.2291</v>
       </c>
     </row>
     <row r="34">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005267365</v>
+        <v>-0.005896407</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.009146474999999999</v>
+        <v>-0.004079818</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.000349108</v>
+        <v>0.004218953</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>5.5327e-05</v>
+        <v>-0.008234640999999999</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.00273027</v>
+        <v>-0.002103201</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.0005186429999999999</v>
+        <v>0.001307811</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.001719344</v>
+        <v>0.00178583</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.004266916</v>
+        <v>-0.009358874</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.005383531</v>
+        <v>0.00404136</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.004102383</v>
+        <v>-0.003248432</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.005267365</v>
+        <v>-0.005896407</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.009146474999999999</v>
+        <v>-0.004079818</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.000349108</v>
+        <v>0.004218953</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>5.5327e-05</v>
+        <v>-0.008234640999999999</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.00273027</v>
+        <v>-0.002103201</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.0005186429999999999</v>
+        <v>0.001307811</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.001719344</v>
+        <v>0.00178583</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.004266916</v>
+        <v>-0.009358874</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.005383531</v>
+        <v>0.00404136</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.004102383</v>
+        <v>-0.003248432</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.117707324</v>
+        <v>0.117696979</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.105872472</v>
+        <v>0.105844145</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.100334541</v>
+        <v>0.10031119</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.096364306</v>
+        <v>0.096345942</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.09552529899999999</v>
+        <v>0.095510867</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.088810351</v>
+        <v>0.08880083900000001</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.086383321</v>
+        <v>0.086376723</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.085412396</v>
+        <v>0.08540807</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.08081609300000001</v>
+        <v>0.08081408299999999</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.075760888</v>
+        <v>0.075754507</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.07080112199999999</v>
+        <v>0.07078142799999999</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.069295049</v>
+        <v>0.069278432</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.068484947</v>
+        <v>0.06847078500000001</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.069660055</v>
+        <v>0.069647946</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.066329333</v>
+        <v>0.066320798</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.065876849</v>
+        <v>0.065870348</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.06638957500000001</v>
+        <v>0.066384733</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.063937511</v>
+        <v>0.063934693</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>13156.352722</v>
+        <v>13156.023651</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>13093.029906</v>
+        <v>13091.795142</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>13127.254696</v>
+        <v>13126.005182</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>13161.686022</v>
+        <v>13160.423704</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>13161.699827</v>
+        <v>13160.437503</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>13127.439217</v>
+        <v>13126.189754</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13127.323267</v>
+        <v>13126.074654</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>13161.766333</v>
+        <v>13160.508521</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>13141.195321</v>
+        <v>13139.937928</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099458926</v>
+        <v>0.099458965</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.099458979</v>
+        <v>0.099459142</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.099689921</v>
+        <v>0.09968992</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.099805116</v>
+        <v>0.09980491</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.09980491399999999</v>
+        <v>0.09980496599999999</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.099980614</v>
+        <v>0.099980682</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.099980579</v>
+        <v>0.09998064299999999</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980719</v>
+        <v>0.099980633</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.099980685</v>
+        <v>0.099980703</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2199997462877507</v>
+        <v>0.2200000341595637</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463843968357698</v>
+        <v>0.04463848141516285</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229747721816401</v>
+        <v>0.01229700690146045</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.0557700431890551</v>
+        <v>0.05576846454460622</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42516,37 +42516,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.343</v>
+        <v>1817.364</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.338</v>
+        <v>1778.359</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.746</v>
+        <v>1724.767</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.128</v>
+        <v>1656.15</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.128</v>
+        <v>1656.15</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.872</v>
+        <v>1406.893</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.485</v>
+        <v>1305.506</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.729</v>
+        <v>1260.75</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.661</v>
+        <v>1081.682</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>756.985</v>
+        <v>757.006</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.672</v>
+        <v>589.686</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42576,16 +42576,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.608</v>
+        <v>6362.629</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.34</v>
+        <v>6815.426</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5054.747</v>
+        <v>5054.831</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.86</v>
+        <v>2035.895</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42660,37 +42660,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.208</v>
+        <v>1728.228</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.14</v>
+        <v>1691.161</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.578</v>
+        <v>1677.599</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.827</v>
+        <v>1628.848</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.827</v>
+        <v>1628.848</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.872</v>
+        <v>1406.893</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.485</v>
+        <v>1305.506</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.729</v>
+        <v>1260.75</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.661</v>
+        <v>1081.682</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>756.985</v>
+        <v>757.006</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.672</v>
+        <v>589.686</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42720,16 +42720,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6008.974</v>
+        <v>6008.994</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.372</v>
+        <v>6626.456</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5054.747</v>
+        <v>5054.831</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.86</v>
+        <v>2035.895</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43134,37 +43134,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>833.0119999999999</v>
+        <v>833.033</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.4059999999999</v>
+        <v>815.426</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.1130000000001</v>
+        <v>792.134</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.6319999999999</v>
+        <v>733.653</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.6319999999999</v>
+        <v>733.653</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.737</v>
+        <v>691.758</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.171</v>
+        <v>665.192</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.715</v>
+        <v>625.736</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.116</v>
+        <v>448.137</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.795</v>
+        <v>315.816</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.913</v>
+        <v>199.927</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43176,16 +43176,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.918</v>
+        <v>2583.939</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3074.783</v>
+        <v>3074.866</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2430.739</v>
+        <v>2430.823</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.874</v>
+        <v>595.909</v>
       </c>
     </row>
     <row r="11">
@@ -43446,37 +43446,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.208</v>
+        <v>1728.228</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.14</v>
+        <v>1691.161</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.578</v>
+        <v>1677.599</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.827</v>
+        <v>1628.848</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.827</v>
+        <v>1628.848</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.872</v>
+        <v>1406.893</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.485</v>
+        <v>1305.506</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.729</v>
+        <v>1260.75</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.661</v>
+        <v>1081.682</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>756.985</v>
+        <v>757.006</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.672</v>
+        <v>589.686</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43506,16 +43506,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5485.035</v>
+        <v>5485.055</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.372</v>
+        <v>6626.456</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5054.747</v>
+        <v>5054.831</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.86</v>
+        <v>2035.895</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43806,37 +43806,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439.05</v>
+        <v>1439.04</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1439.03</v>
+        <v>1439.01</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.82</v>
+        <v>1441.8</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.82</v>
+        <v>1443.8</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.82</v>
+        <v>1443.8</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.54</v>
+        <v>1452.52</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.8</v>
+        <v>1452.78</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.83</v>
+        <v>1453.81</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.59</v>
+        <v>1457.56</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.24</v>
+        <v>1463.2</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.76</v>
+        <v>1465.73</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43923,52 +43923,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
     </row>
     <row r="18">
@@ -44040,52 +44040,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1411.06</v>
+        <v>1410.87</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1410.36</v>
+        <v>1409.75</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1412.31</v>
+        <v>1411.71</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1413.71</v>
+        <v>1413.11</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1413.71</v>
+        <v>1413.11</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1419.82</v>
+        <v>1419.21</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1420</v>
+        <v>1419.39</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1420.72</v>
+        <v>1420.11</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1423.35</v>
+        <v>1422.74</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1427.31</v>
+        <v>1426.69</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1429.07</v>
+        <v>1428.46</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1432.88</v>
+        <v>1432.28</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1442.81</v>
+        <v>1442.22</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1451</v>
+        <v>1450.41</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1454.26</v>
+        <v>1453.67</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1454.26</v>
+        <v>1453.67</v>
       </c>
     </row>
     <row r="19">
@@ -44157,52 +44157,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2564379.1</v>
+        <v>2564060.4</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2508091.2</v>
+        <v>2507048.5</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2435876.9</v>
+        <v>2434866</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2341290.1</v>
+        <v>2340319.8</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2341290.1</v>
+        <v>2340319.8</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1997502.5</v>
+        <v>1996679.4</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1853789</v>
+        <v>1853025.9</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1791143.7</v>
+        <v>1790407.1</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1539580.2</v>
+        <v>1538949.4</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1080450.5</v>
+        <v>1080011.4</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>842683.2</v>
+        <v>842340.3</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>618765</v>
+        <v>618509.7</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>371334.2</v>
+        <v>371182.1</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>264214.2</v>
+        <v>264106.6</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252701.4</v>
+        <v>252598.7</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52761.8</v>
+        <v>52740.4</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44217,19 +44217,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9101687.300000001</v>
+        <v>9101368.6</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9626548.300000001</v>
+        <v>9622554.1</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7182015.4</v>
+        <v>7179061.8</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2913232.9</v>
+        <v>2912043.5</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>569677.4</v>
+        <v>569445.7</v>
       </c>
     </row>
     <row r="20">
@@ -44301,52 +44301,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2443095.6</v>
+        <v>2442792.9</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2389503.9</v>
+        <v>2388512.7</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2372300.5</v>
+        <v>2371317.4</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2305022</v>
+        <v>2304067.9</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2305022</v>
+        <v>2304067.9</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1997502.5</v>
+        <v>1996679.4</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1853789</v>
+        <v>1853025.9</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1791143.7</v>
+        <v>1790407.1</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1539580.2</v>
+        <v>1538949.4</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1080450.5</v>
+        <v>1080011.4</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>842683.2</v>
+        <v>842340.3</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>618765</v>
+        <v>618509.7</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>371334.2</v>
+        <v>371182.1</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>264214.2</v>
+        <v>264106.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252701.4</v>
+        <v>252598.7</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52761.8</v>
+        <v>52740.4</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44361,19 +44361,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8611280.1</v>
+        <v>8610977.4</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9371848.4</v>
+        <v>9367965.9</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7182015.4</v>
+        <v>7179061.8</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2913232.9</v>
+        <v>2912043.5</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>569677.4</v>
+        <v>569445.7</v>
       </c>
     </row>
     <row r="21">
@@ -44445,52 +44445,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2127430.1</v>
+        <v>2127160</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2080177.6</v>
+        <v>2079310.1</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2059537.2</v>
+        <v>2058679.2</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1988821.8</v>
+        <v>1987994.1</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1988821.8</v>
+        <v>1987994.1</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1684739.3</v>
+        <v>1684041.2</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1541025.8</v>
+        <v>1540387.7</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1474943.5</v>
+        <v>1474333.3</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1225431.2</v>
+        <v>1224926</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>817276.7</v>
+        <v>816941.8</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>609653.6</v>
+        <v>609404.4</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>470061.3</v>
+        <v>469869</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>349051.9</v>
+        <v>348909.2</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249924.4</v>
+        <v>249822.9</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252701.4</v>
+        <v>252598.7</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52761.8</v>
+        <v>52740.4</v>
       </c>
     </row>
     <row r="22">
@@ -44562,46 +44562,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315665.4</v>
+        <v>315632.9</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>309326.3</v>
+        <v>309202.7</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312763.2</v>
+        <v>312638.2</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>316200.2</v>
+        <v>316073.8</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>316200.2</v>
+        <v>316073.8</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312763.2</v>
+        <v>312638.2</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312763.2</v>
+        <v>312638.2</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>316200.2</v>
+        <v>316073.8</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>314149</v>
+        <v>314023.5</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>263173.7</v>
+        <v>263069.7</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>233029.6</v>
+        <v>232935.9</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148703.7</v>
+        <v>148640.7</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22282.3</v>
+        <v>22272.9</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14289.7</v>
+        <v>14283.7</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44855,67 +44855,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1345.74)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1345.14)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1343.46)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
         <v/>
       </c>
     </row>
@@ -49522,43 +49522,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.716</v>
+        <v>46.737</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.203</v>
+        <v>46.223</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.716</v>
+        <v>46.737</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.229</v>
+        <v>47.25</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.229</v>
+        <v>47.25</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.716</v>
+        <v>46.737</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.716</v>
+        <v>46.737</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.229</v>
+        <v>47.25</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.229</v>
+        <v>47.25</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.203</v>
+        <v>46.223</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.316</v>
+        <v>31.331</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49577,7 +49577,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>499.502</v>
+        <v>499.725</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56716,10 +56716,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>499.502</v>
+        <v>499.725</v>
       </c>
       <c r="F197" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.76</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="33">
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18900</v>
+        <v>17970</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9736,7 +9736,7 @@
         <v>18440</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>18800</v>
+        <v>17910</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19562</v>
+        <v>19296.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -13302,7 +13302,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>18900</v>
+        <v>17970</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -58493,7 +58493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64266,7 +64266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 24428억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 24420억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23843억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3087억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23671억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19932억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18498억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 17873억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15389억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15362억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3135억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2329,43 +2329,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41523억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41519억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44400억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44392억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47440억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47429억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50744억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50730억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54109억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54093억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57654억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61480억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2389,43 +2389,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41523억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41519억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44400억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44392억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47440억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47429억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50744억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50730억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 54109억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54093억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57654억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61502억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61480억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 24428억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 24420억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23843억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3087억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23671억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19932억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3126억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18498억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 17873억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15389억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15362억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3135억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,203억 vs 54억 · 2027 12,540억 vs 16,454억 · 2028 12,554억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,202억 vs 54억 · 2027 12,518억 vs 16,454억 · 2028 12,532억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1280.1</v>
+        <v>1279.3</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.04</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="33">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2291</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="34">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="35">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>17970</v>
+        <v>18340</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9736,7 +9736,7 @@
         <v>18440</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17910</v>
+        <v>17210</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19296.7</v>
+        <v>19147.1</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005896407</v>
+        <v>-0.002317991</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.004079818</v>
+        <v>0.004377922</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.004218953</v>
+        <v>0.004394855</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.008234640999999999</v>
+        <v>-0.002714699</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.002103201</v>
+        <v>0.008965828</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.001307811</v>
+        <v>0.004649385</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.00178583</v>
+        <v>-0.001609489</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.009358874</v>
+        <v>-0.006824645</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.00404136</v>
+        <v>0.013848928</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.003248432</v>
+        <v>-0.006572539</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.005896407</v>
+        <v>-0.002317991</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.004079818</v>
+        <v>0.004377922</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.004218953</v>
+        <v>0.004394854</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.008234640999999999</v>
+        <v>-0.002714698</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>-0.002103201</v>
+        <v>0.008965828</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.001307811</v>
+        <v>0.004649385</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.00178583</v>
+        <v>-0.001609489</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.009358874</v>
+        <v>-0.006824645</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.00404136</v>
+        <v>0.013848928</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.003248432</v>
+        <v>-0.006572539</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.117696979</v>
+        <v>0.11767155</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.105844145</v>
+        <v>0.105719681</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.10031119</v>
+        <v>0.100210371</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.096345942</v>
+        <v>0.096266372</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095510867</v>
+        <v>0.095446659</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.08880083900000001</v>
+        <v>0.088759266</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.086376723</v>
+        <v>0.086348412</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.08540807</v>
+        <v>0.085388135</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.08081408299999999</v>
+        <v>0.080805296</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.075754507</v>
+        <v>0.07573814</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.07078142799999999</v>
+        <v>0.07069766199999999</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.069278432</v>
+        <v>0.069205665</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.06847078500000001</v>
+        <v>0.06840998500000001</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.069647946</v>
+        <v>0.06959569</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.066320798</v>
+        <v>0.066283725</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.065870348</v>
+        <v>0.065842365</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.066384733</v>
+        <v>0.06636299399999999</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.063934693</v>
+        <v>0.063921856</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>13156.023651</v>
+        <v>13155.200989</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>13091.795142</v>
+        <v>13086.375995</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>13126.005182</v>
+        <v>13120.532029</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>13160.423704</v>
+        <v>13154.889404</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>13160.437503</v>
+        <v>13154.893177</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>13126.189754</v>
+        <v>13120.714482</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13126.074654</v>
+        <v>13120.604632</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>13160.508521</v>
+        <v>13154.967999</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>13139.937928</v>
+        <v>13134.442038</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099458965</v>
+        <v>0.099459194</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.099459142</v>
+        <v>0.099459086</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.09968992</v>
+        <v>0.099690002</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.09980491</v>
+        <v>0.099805042</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.09980496599999999</v>
+        <v>0.099805112</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.099980682</v>
+        <v>0.099980523</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.09998064299999999</v>
+        <v>0.099980583</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980633</v>
+        <v>0.099980746</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.099980703</v>
+        <v>0.09998056900000001</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>17970</v>
+        <v>18340</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 19,540원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,860원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200000341595637</v>
+        <v>0.219999423742024</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463848141516285</v>
+        <v>0.04463846693893195</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229700690146045</v>
+        <v>0.01229650830929219</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576846454460622</v>
+        <v>0.05576622541852579</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42516,37 +42516,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.364</v>
+        <v>1817.417</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.359</v>
+        <v>1778.411</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.767</v>
+        <v>1724.819</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.15</v>
+        <v>1656.203</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.15</v>
+        <v>1656.203</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.893</v>
+        <v>1406.946</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.506</v>
+        <v>1305.559</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.75</v>
+        <v>1260.803</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.682</v>
+        <v>1081.735</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>757.006</v>
+        <v>757.058</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.686</v>
+        <v>589.721</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42576,16 +42576,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.629</v>
+        <v>6362.682</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.426</v>
+        <v>6815.636</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5054.831</v>
+        <v>5055.043</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.895</v>
+        <v>2035.982</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42660,37 +42660,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.228</v>
+        <v>1728.281</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.161</v>
+        <v>1691.213</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.599</v>
+        <v>1677.651</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.848</v>
+        <v>1628.902</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.848</v>
+        <v>1628.902</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.893</v>
+        <v>1406.946</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.506</v>
+        <v>1305.559</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.75</v>
+        <v>1260.803</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.682</v>
+        <v>1081.735</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>757.006</v>
+        <v>757.058</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.686</v>
+        <v>589.721</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42720,16 +42720,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6008.994</v>
+        <v>6009.047</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.456</v>
+        <v>6626.668</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5054.831</v>
+        <v>5055.043</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.895</v>
+        <v>2035.982</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43134,37 +43134,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>833.033</v>
+        <v>833.086</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.426</v>
+        <v>815.478</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.134</v>
+        <v>792.186</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.653</v>
+        <v>733.706</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.653</v>
+        <v>733.706</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.758</v>
+        <v>691.8099999999999</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.192</v>
+        <v>665.245</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.736</v>
+        <v>625.789</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.137</v>
+        <v>448.19</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.816</v>
+        <v>315.868</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.927</v>
+        <v>199.963</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43176,16 +43176,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.939</v>
+        <v>2583.992</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3074.866</v>
+        <v>3075.076</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2430.823</v>
+        <v>2431.034</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.909</v>
+        <v>595.997</v>
       </c>
     </row>
     <row r="11">
@@ -43446,37 +43446,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.228</v>
+        <v>1728.281</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.161</v>
+        <v>1691.213</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.599</v>
+        <v>1677.651</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.848</v>
+        <v>1628.902</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.848</v>
+        <v>1628.902</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.893</v>
+        <v>1406.946</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.506</v>
+        <v>1305.559</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.75</v>
+        <v>1260.803</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.682</v>
+        <v>1081.735</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>757.006</v>
+        <v>757.058</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.686</v>
+        <v>589.721</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43506,16 +43506,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5485.055</v>
+        <v>5485.108</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.456</v>
+        <v>6626.668</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5054.831</v>
+        <v>5055.043</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.895</v>
+        <v>2035.982</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43806,37 +43806,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439.04</v>
+        <v>1439</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1439.01</v>
+        <v>1438.97</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.8</v>
+        <v>1441.76</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.8</v>
+        <v>1443.76</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.8</v>
+        <v>1443.76</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.52</v>
+        <v>1452.47</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.78</v>
+        <v>1452.72</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.81</v>
+        <v>1453.75</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.56</v>
+        <v>1457.49</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.2</v>
+        <v>1463.1</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.73</v>
+        <v>1465.64</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43923,52 +43923,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
     </row>
     <row r="18">
@@ -44040,52 +44040,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1410.87</v>
+        <v>1410.39</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1409.75</v>
+        <v>1407.2</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1411.71</v>
+        <v>1409.16</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1413.11</v>
+        <v>1410.56</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1413.11</v>
+        <v>1410.56</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1419.21</v>
+        <v>1416.65</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1419.39</v>
+        <v>1416.83</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1420.11</v>
+        <v>1417.55</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1422.74</v>
+        <v>1420.17</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1426.69</v>
+        <v>1424.1</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1428.46</v>
+        <v>1425.87</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1432.28</v>
+        <v>1429.76</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1442.22</v>
+        <v>1439.7</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1450.41</v>
+        <v>1447.89</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1453.67</v>
+        <v>1451.15</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1453.67</v>
+        <v>1451.15</v>
       </c>
     </row>
     <row r="19">
@@ -44157,52 +44157,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2564060.4</v>
+        <v>2563258.4</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2507048.5</v>
+        <v>2502587.9</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2434866</v>
+        <v>2430540.6</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2340319.8</v>
+        <v>2336167.6</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2340319.8</v>
+        <v>2336167.6</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1996679.4</v>
+        <v>1993155.1</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1853025.9</v>
+        <v>1849757.1</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1790407.1</v>
+        <v>1787251.3</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1538949.4</v>
+        <v>1536244.9</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1080011.4</v>
+        <v>1078124.6</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>842340.3</v>
+        <v>840868.4</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>618509.7</v>
+        <v>617421.5</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>371182.1</v>
+        <v>370533.5</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>264106.6</v>
+        <v>263647.7</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252598.7</v>
+        <v>252160.8</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52740.4</v>
+        <v>52649</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44217,19 +44217,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9101368.6</v>
+        <v>9100566.6</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9622554.1</v>
+        <v>9605463.699999999</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7179061.8</v>
+        <v>7166408.4</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2912043.5</v>
+        <v>2906948</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>569445.7</v>
+        <v>568457.5</v>
       </c>
     </row>
     <row r="20">
@@ -44301,52 +44301,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2442792.9</v>
+        <v>2442031.2</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2388512.7</v>
+        <v>2384271.8</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2371317.4</v>
+        <v>2367110.9</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2304067.9</v>
+        <v>2299984.5</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2304067.9</v>
+        <v>2299984.5</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1996679.4</v>
+        <v>1993155.1</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1853025.9</v>
+        <v>1849757.1</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1790407.1</v>
+        <v>1787251.3</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1538949.4</v>
+        <v>1536244.9</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1080011.4</v>
+        <v>1078124.6</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>842340.3</v>
+        <v>840868.4</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>618509.7</v>
+        <v>617421.5</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>371182.1</v>
+        <v>370533.5</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>264106.6</v>
+        <v>263647.7</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252598.7</v>
+        <v>252160.8</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52740.4</v>
+        <v>52649</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44361,19 +44361,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8610977.4</v>
+        <v>8610215.699999999</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9367965.9</v>
+        <v>9351351.699999999</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7179061.8</v>
+        <v>7166408.4</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2912043.5</v>
+        <v>2906948</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>569445.7</v>
+        <v>568457.5</v>
       </c>
     </row>
     <row r="21">
@@ -44445,52 +44445,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2127160</v>
+        <v>2126480.3</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2079310.1</v>
+        <v>2075611</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2058679.2</v>
+        <v>2055020.5</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1987994.1</v>
+        <v>1984464.5</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1987994.1</v>
+        <v>1984464.5</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1684041.2</v>
+        <v>1681064.7</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1540387.7</v>
+        <v>1537666.7</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1474333.3</v>
+        <v>1471731.3</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1224926</v>
+        <v>1222771.5</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>816941.8</v>
+        <v>815513.4</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>609404.4</v>
+        <v>608341.9</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>469869</v>
+        <v>469049.2</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>348909.2</v>
+        <v>348300.8</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249822.9</v>
+        <v>249389.8</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252598.7</v>
+        <v>252160.8</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52740.4</v>
+        <v>52649</v>
       </c>
     </row>
     <row r="22">
@@ -44562,46 +44562,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315632.9</v>
+        <v>315551</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>309202.7</v>
+        <v>308660.9</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312638.2</v>
+        <v>312090.4</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>316073.8</v>
+        <v>315520</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>316073.8</v>
+        <v>315520</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312638.2</v>
+        <v>312090.4</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312638.2</v>
+        <v>312090.4</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>316073.8</v>
+        <v>315520</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>314023.5</v>
+        <v>313473.3</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>263069.7</v>
+        <v>262611.2</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>232935.9</v>
+        <v>232526.5</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148640.7</v>
+        <v>148372.3</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22272.9</v>
+        <v>22232.7</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14283.7</v>
+        <v>14257.9</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44855,67 +44855,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1345.14)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.63)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.49)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
         <v/>
       </c>
     </row>
@@ -49522,43 +49522,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.737</v>
+        <v>46.789</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.223</v>
+        <v>46.275</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.737</v>
+        <v>46.789</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.25</v>
+        <v>47.304</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.25</v>
+        <v>47.304</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.737</v>
+        <v>46.789</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.737</v>
+        <v>46.789</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.25</v>
+        <v>47.304</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.25</v>
+        <v>47.304</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.223</v>
+        <v>46.275</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.331</v>
+        <v>31.365</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49577,7 +49577,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>499.725</v>
+        <v>500.287</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56716,10 +56716,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>499.725</v>
+        <v>500.287</v>
       </c>
       <c r="F197" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64266,7 +64266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 24420억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 24419억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23843억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3087억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23671억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19932억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18498억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17873억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15362억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3135억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15390억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38778억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38777억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41519억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44392억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44399억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47429억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47439억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50730억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50743억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54093억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54108억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57654억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61480억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 38778억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 38777억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41519억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44392억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44399억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47429억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47439억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50730억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50743억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 54093억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54108억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57654억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61480억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 24420억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3156억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 24419억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23843억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3087억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23671억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23000억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19932억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18498억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3121억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17873억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15362억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3135억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15390억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,202억 vs 54억 · 2027 12,518억 vs 16,454억 · 2028 12,532억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,202억 vs 54억 · 2027 12,541억 vs 16,454억 · 2028 12,555억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1279.3</v>
+        <v>1280.1</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.34</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.28</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="33">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.229</v>
+        <v>0.2291</v>
       </c>
     </row>
     <row r="34">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="35">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18340</v>
+        <v>18950</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19147.1</v>
+        <v>19126.2</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.002317991</v>
+        <v>-0.005775192</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.004377922</v>
+        <v>-0.010283237</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.004394855</v>
+        <v>0.00289783</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.002714699</v>
+        <v>-0.001649152</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.008965828</v>
+        <v>0.004577501</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.004649385</v>
+        <v>-0.001913895</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.001609489</v>
+        <v>0.008717664</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.006824645</v>
+        <v>-0.002319941</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.013848928</v>
+        <v>0.00122935</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.006572539</v>
+        <v>0.004090058</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.002317991</v>
+        <v>-0.005775192</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>0.004377922</v>
+        <v>-0.010283238</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.004394854</v>
+        <v>0.002897831</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.002714698</v>
+        <v>-0.001649152</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.008965828</v>
+        <v>0.004577501</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>0.004649385</v>
+        <v>-0.001913895</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.001609489</v>
+        <v>0.008717664</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.006824645</v>
+        <v>-0.002319941</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.013848928</v>
+        <v>0.00122935</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>-0.006572539</v>
+        <v>0.004090058</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.11767155</v>
+        <v>0.117667671</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.105719681</v>
+        <v>0.105846535</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.100210371</v>
+        <v>0.100313952</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.096266372</v>
+        <v>0.09634801899999999</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095446659</v>
+        <v>0.095512744</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.088759266</v>
+        <v>0.088802433</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.086348412</v>
+        <v>0.086378389</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.085388135</v>
+        <v>0.085409346</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.080805296</v>
+        <v>0.080815606</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.07573814</v>
+        <v>0.075735366</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.07069766199999999</v>
+        <v>0.070782945</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.069205665</v>
+        <v>0.069279566</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.06840998500000001</v>
+        <v>0.068471834</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.06959569</v>
+        <v>0.069648944</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.066283725</v>
+        <v>0.066321883</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.065842365</v>
+        <v>0.065871349</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.06636299399999999</v>
+        <v>0.066385493</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.063921856</v>
+        <v>0.063935379</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>13155.200989</v>
+        <v>13155.07136</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>13086.375995</v>
+        <v>13092.011288</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>13120.532029</v>
+        <v>13126.219405</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>13154.889404</v>
+        <v>13160.641779</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>13154.893177</v>
+        <v>13160.655577</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>13120.714482</v>
+        <v>13126.411491</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13120.604632</v>
+        <v>13126.294226</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>13154.967999</v>
+        <v>13160.732423</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>13134.442038</v>
+        <v>13140.160519</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099459194</v>
+        <v>0.099458913</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.099459086</v>
+        <v>0.09945902700000001</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.099690002</v>
+        <v>0.099690086</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.099805042</v>
+        <v>0.099805041</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.099805112</v>
+        <v>0.099805087</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.099980523</v>
+        <v>0.09998073</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.099980583</v>
+        <v>0.099980665</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980746</v>
+        <v>0.099980633</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.09998056900000001</v>
+        <v>0.099980662</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>18340</v>
+        <v>18950</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,860원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,010원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.219999423742024</v>
+        <v>0.2200002049616331</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463846693893195</v>
+        <v>0.04463845400700116</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229650830929219</v>
+        <v>0.01229724507167632</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576622541852579</v>
+        <v>0.05576886836051728</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42516,37 +42516,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.417</v>
+        <v>1817.425</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.411</v>
+        <v>1778.419</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.819</v>
+        <v>1724.827</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.203</v>
+        <v>1656.211</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.203</v>
+        <v>1656.211</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.946</v>
+        <v>1406.954</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.559</v>
+        <v>1305.567</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.803</v>
+        <v>1260.811</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.735</v>
+        <v>1081.744</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>757.058</v>
+        <v>757.066</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.721</v>
+        <v>589.727</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42576,16 +42576,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.682</v>
+        <v>6362.69</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.636</v>
+        <v>6815.668</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5055.043</v>
+        <v>5055.076</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.982</v>
+        <v>2035.996</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42660,37 +42660,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.281</v>
+        <v>1728.289</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.213</v>
+        <v>1691.221</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.651</v>
+        <v>1677.66</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.902</v>
+        <v>1628.91</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.902</v>
+        <v>1628.91</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.946</v>
+        <v>1406.954</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.559</v>
+        <v>1305.567</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.803</v>
+        <v>1260.811</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.735</v>
+        <v>1081.744</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>757.058</v>
+        <v>757.066</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.721</v>
+        <v>589.727</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42720,16 +42720,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6009.047</v>
+        <v>6009.055</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.668</v>
+        <v>6626.701</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5055.043</v>
+        <v>5055.076</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.982</v>
+        <v>2035.996</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43134,37 +43134,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>833.086</v>
+        <v>833.0940000000001</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.478</v>
+        <v>815.486</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.186</v>
+        <v>792.1950000000001</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.706</v>
+        <v>733.715</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.706</v>
+        <v>733.715</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.8099999999999</v>
+        <v>691.819</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.245</v>
+        <v>665.253</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.789</v>
+        <v>625.797</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.19</v>
+        <v>448.199</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.868</v>
+        <v>315.876</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.963</v>
+        <v>199.968</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43176,16 +43176,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2583.992</v>
+        <v>2584</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3075.076</v>
+        <v>3075.111</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2431.034</v>
+        <v>2431.068</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>595.997</v>
+        <v>596.01</v>
       </c>
     </row>
     <row r="11">
@@ -43446,37 +43446,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.281</v>
+        <v>1728.289</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.213</v>
+        <v>1691.221</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.651</v>
+        <v>1677.66</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.902</v>
+        <v>1628.91</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.902</v>
+        <v>1628.91</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.946</v>
+        <v>1406.954</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.559</v>
+        <v>1305.567</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.803</v>
+        <v>1260.811</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.735</v>
+        <v>1081.744</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>757.058</v>
+        <v>757.066</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.721</v>
+        <v>589.727</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43506,16 +43506,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5485.108</v>
+        <v>5485.116</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.668</v>
+        <v>6626.701</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5055.043</v>
+        <v>5055.076</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.982</v>
+        <v>2035.996</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43806,37 +43806,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1439</v>
+        <v>1438.99</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1438.97</v>
+        <v>1438.96</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.76</v>
+        <v>1441.75</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.76</v>
+        <v>1443.75</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.76</v>
+        <v>1443.75</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.47</v>
+        <v>1452.46</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.72</v>
+        <v>1452.71</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.75</v>
+        <v>1453.74</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.49</v>
+        <v>1457.47</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.1</v>
+        <v>1463.09</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.64</v>
+        <v>1465.63</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43923,52 +43923,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
     </row>
     <row r="18">
@@ -44040,52 +44040,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1410.39</v>
+        <v>1410.31</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1407.2</v>
+        <v>1409.71</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1409.16</v>
+        <v>1411.66</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1410.56</v>
+        <v>1413.06</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1410.56</v>
+        <v>1413.06</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1416.65</v>
+        <v>1419.16</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1416.83</v>
+        <v>1419.33</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1417.55</v>
+        <v>1420.05</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1420.17</v>
+        <v>1422.67</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1424.1</v>
+        <v>1426.59</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1425.87</v>
+        <v>1428.37</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1429.76</v>
+        <v>1432.27</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1439.7</v>
+        <v>1442.21</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1447.89</v>
+        <v>1450.39</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1451.15</v>
+        <v>1453.66</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1451.15</v>
+        <v>1453.66</v>
       </c>
     </row>
     <row r="19">
@@ -44157,52 +44157,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2563258.4</v>
+        <v>2563130.9</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2502587.9</v>
+        <v>2507051.4</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2430540.6</v>
+        <v>2434869.8</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2336167.6</v>
+        <v>2340324.7</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2336167.6</v>
+        <v>2340324.7</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1993155.1</v>
+        <v>1996687.1</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1849757.1</v>
+        <v>1853034.7</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1787251.3</v>
+        <v>1790416.7</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1536244.9</v>
+        <v>1538961.2</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1078124.6</v>
+        <v>1080026.6</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>840868.4</v>
+        <v>842349.7</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>617421.5</v>
+        <v>618504.6</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>370533.5</v>
+        <v>371179</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>263647.7</v>
+        <v>264104.4</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252160.8</v>
+        <v>252596.6</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52649</v>
+        <v>52740</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44217,19 +44217,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9100566.6</v>
+        <v>9100439.1</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9605463.699999999</v>
+        <v>9622570.6</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7166408.4</v>
+        <v>7179099.7</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2906948</v>
+        <v>2912059.9</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>568457.5</v>
+        <v>569441</v>
       </c>
     </row>
     <row r="20">
@@ -44301,52 +44301,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2442031.2</v>
+        <v>2441910.1</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2384271.8</v>
+        <v>2388516.7</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2367110.9</v>
+        <v>2371321.8</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2299984.5</v>
+        <v>2304073.1</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2299984.5</v>
+        <v>2304073.1</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1993155.1</v>
+        <v>1996687.1</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1849757.1</v>
+        <v>1853034.7</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1787251.3</v>
+        <v>1790416.7</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1536244.9</v>
+        <v>1538961.2</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1078124.6</v>
+        <v>1080026.6</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>840868.4</v>
+        <v>842349.7</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>617421.5</v>
+        <v>618504.6</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>370533.5</v>
+        <v>371179</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>263647.7</v>
+        <v>264104.4</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252160.8</v>
+        <v>252596.6</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52649</v>
+        <v>52740</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44361,19 +44361,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8610215.699999999</v>
+        <v>8610094.6</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9351351.699999999</v>
+        <v>9367984.699999999</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7166408.4</v>
+        <v>7179099.7</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2906948</v>
+        <v>2912059.9</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>568457.5</v>
+        <v>569441</v>
       </c>
     </row>
     <row r="21">
@@ -44445,52 +44445,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2126480.3</v>
+        <v>2126372.3</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2075611</v>
+        <v>2079292.5</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2055020.5</v>
+        <v>2058661.8</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1984464.5</v>
+        <v>1987977.2</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1984464.5</v>
+        <v>1987977.2</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1681064.7</v>
+        <v>1684027</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1537666.7</v>
+        <v>1540374.7</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1471731.3</v>
+        <v>1474320.9</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1222771.5</v>
+        <v>1224915.7</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>815513.4</v>
+        <v>816934.9</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>608341.9</v>
+        <v>609399.3</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>469049.2</v>
+        <v>469865.1</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>348300.8</v>
+        <v>348906.3</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249389.8</v>
+        <v>249820.8</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252160.8</v>
+        <v>252596.6</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52649</v>
+        <v>52740</v>
       </c>
     </row>
     <row r="22">
@@ -44562,46 +44562,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315551</v>
+        <v>315537.9</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>308660.9</v>
+        <v>309224.2</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312090.4</v>
+        <v>312660</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>315520</v>
+        <v>316095.9</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>315520</v>
+        <v>316095.9</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312090.4</v>
+        <v>312660</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312090.4</v>
+        <v>312660</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>315520</v>
+        <v>316095.9</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>313473.3</v>
+        <v>314045.5</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>262611.2</v>
+        <v>263091.6</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>232526.5</v>
+        <v>232950.3</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148372.3</v>
+        <v>148639.5</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22232.7</v>
+        <v>22272.7</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14257.9</v>
+        <v>14283.6</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44855,67 +44855,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.63)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.39)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1333.09)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
         <v/>
       </c>
     </row>
@@ -49522,43 +49522,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.789</v>
+        <v>46.798</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.275</v>
+        <v>46.283</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.789</v>
+        <v>46.798</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.304</v>
+        <v>47.312</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.304</v>
+        <v>47.312</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.789</v>
+        <v>46.798</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.789</v>
+        <v>46.798</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.304</v>
+        <v>47.312</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.304</v>
+        <v>47.312</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.275</v>
+        <v>46.283</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.365</v>
+        <v>31.37</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49577,7 +49577,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>500.287</v>
+        <v>500.376</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56716,10 +56716,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>500.287</v>
+        <v>500.376</v>
       </c>
       <c r="F197" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64266,7 +64266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 24419억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 24413억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23838억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3086억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23666억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19928억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18494억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 17869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15390억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15359억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3134억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2329,43 +2329,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41518억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44399억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44391억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47439억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47428억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50743억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50728억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54108억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54090억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57652억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61477억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2389,43 +2389,43 @@
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41522억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41518억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44399억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44391억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47439억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47428억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50743억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50728억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 54108억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54090억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57673억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57652억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61501억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61477억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 24419억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 24413억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23885억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3092억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23838억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3086억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23713억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23666억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23041억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19967억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19928억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18530억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3127억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18494억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17904억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3161억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 17869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15390억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3140억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15359억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3134억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,202억 vs 54억 · 2027 12,541억 vs 16,454억 · 2028 12,555억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,201억 vs 54억 · 2027 12,516억 vs 16,454억 · 2028 12,530억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1280.1</v>
+        <v>1279.2</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.8</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.39</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="33">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2291</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="34">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="35">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18950</v>
+        <v>18300</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>19126.2</v>
+        <v>18892.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005775192</v>
+        <v>-0.00437145</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.010283237</v>
+        <v>-0.008110109000000001</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.00289783</v>
+        <v>0.006996103</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>-0.001649152</v>
+        <v>0.00698306</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.004577501</v>
+        <v>0.005801761</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.001913895</v>
+        <v>-0.007028072</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.008717664</v>
+        <v>-0.00143717</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>-0.002319941</v>
+        <v>0.006252531</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.00122935</v>
+        <v>-0.003588791</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.004090058</v>
+        <v>0.002485498</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.005775192</v>
+        <v>-0.00437145</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.010283238</v>
+        <v>-0.008110109000000001</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.002897831</v>
+        <v>0.006996103</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>-0.001649152</v>
+        <v>0.00698306</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.004577501</v>
+        <v>0.005801761</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.001913895</v>
+        <v>-0.007028072</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>0.008717664</v>
+        <v>-0.00143717</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>-0.002319941</v>
+        <v>0.006252531</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>0.00122935</v>
+        <v>-0.003588791</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.004090058</v>
+        <v>0.002485498</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.117667671</v>
+        <v>0.117646121</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.105846535</v>
+        <v>0.105707432</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.100313952</v>
+        <v>0.100200857</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.09634801899999999</v>
+        <v>0.096259049</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095512744</v>
+        <v>0.095440652</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.088802433</v>
+        <v>0.088755933</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.086378389</v>
+        <v>0.086346121</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.085409346</v>
+        <v>0.08538699399999999</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.080815606</v>
+        <v>0.08080527899999999</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.075735366</v>
+        <v>0.075721495</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.070782945</v>
+        <v>0.070689214</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.069279566</v>
+        <v>0.06919837</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.068471834</v>
+        <v>0.068403715</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.069648944</v>
+        <v>0.069590609</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.066321883</v>
+        <v>0.066280122</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.065871349</v>
+        <v>0.065840098</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.066385493</v>
+        <v>0.066361038</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.063935379</v>
+        <v>0.06392103</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>13155.07136</v>
+        <v>13154.383342</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>13092.011288</v>
+        <v>13085.925631</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>13126.219405</v>
+        <v>13120.06405</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>13160.641779</v>
+        <v>13154.419254</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>13160.655577</v>
+        <v>13154.433024</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>13126.411491</v>
+        <v>13120.252468</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13126.294226</v>
+        <v>13120.141522</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>13160.732423</v>
+        <v>13154.504581</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>13140.160519</v>
+        <v>13133.981165</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099458913</v>
+        <v>0.099458957</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.09945902700000001</v>
+        <v>0.09945904</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.099690086</v>
+        <v>0.099690182</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.099805041</v>
+        <v>0.099805097</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.099805087</v>
+        <v>0.099804897</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.09998073</v>
+        <v>0.099980688</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.099980665</v>
+        <v>0.09998074</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980633</v>
+        <v>0.099980597</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.099980662</v>
+        <v>0.09998056800000001</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>18950</v>
+        <v>18300</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,010원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,170원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2200002049616331</v>
+        <v>0.219999960927751</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463845400700116</v>
+        <v>0.04463848126112946</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229724507167632</v>
+        <v>0.01229708144005519</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576886836051728</v>
+        <v>0.05576809408005337</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42516,37 +42516,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.425</v>
+        <v>1817.47</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.419</v>
+        <v>1778.463</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.827</v>
+        <v>1724.872</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.211</v>
+        <v>1656.256</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.211</v>
+        <v>1656.256</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.954</v>
+        <v>1406.999</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.567</v>
+        <v>1305.612</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.811</v>
+        <v>1260.857</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.744</v>
+        <v>1081.789</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>757.066</v>
+        <v>757.11</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.727</v>
+        <v>589.7569999999999</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42576,16 +42576,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.69</v>
+        <v>6362.735</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.668</v>
+        <v>6815.847</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5055.076</v>
+        <v>5055.257</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2035.996</v>
+        <v>2036.07</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42660,37 +42660,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.289</v>
+        <v>1728.334</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.221</v>
+        <v>1691.265</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.66</v>
+        <v>1677.704</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.91</v>
+        <v>1628.955</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.91</v>
+        <v>1628.955</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.954</v>
+        <v>1406.999</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.567</v>
+        <v>1305.612</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.811</v>
+        <v>1260.857</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.744</v>
+        <v>1081.789</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>757.066</v>
+        <v>757.11</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.727</v>
+        <v>589.7569999999999</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42720,16 +42720,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6009.055</v>
+        <v>6009.1</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.701</v>
+        <v>6626.879</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5055.076</v>
+        <v>5055.257</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2035.996</v>
+        <v>2036.07</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43134,37 +43134,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>833.0940000000001</v>
+        <v>833.139</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.486</v>
+        <v>815.5309999999999</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.1950000000001</v>
+        <v>792.239</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.715</v>
+        <v>733.76</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.715</v>
+        <v>733.76</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.819</v>
+        <v>691.8630000000001</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.253</v>
+        <v>665.298</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.797</v>
+        <v>625.842</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.199</v>
+        <v>448.244</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.876</v>
+        <v>315.92</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.968</v>
+        <v>199.998</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43176,16 +43176,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2584</v>
+        <v>2584.045</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3075.111</v>
+        <v>3075.29</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2431.068</v>
+        <v>2431.247</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>596.01</v>
+        <v>596.0839999999999</v>
       </c>
     </row>
     <row r="11">
@@ -43446,37 +43446,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.289</v>
+        <v>1728.334</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.221</v>
+        <v>1691.265</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.66</v>
+        <v>1677.704</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.91</v>
+        <v>1628.955</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.91</v>
+        <v>1628.955</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.954</v>
+        <v>1406.999</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.567</v>
+        <v>1305.612</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.811</v>
+        <v>1260.857</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.744</v>
+        <v>1081.789</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>757.066</v>
+        <v>757.11</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.727</v>
+        <v>589.7569999999999</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43506,16 +43506,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5485.116</v>
+        <v>5485.161</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.701</v>
+        <v>6626.879</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5055.076</v>
+        <v>5055.257</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2035.996</v>
+        <v>2036.07</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43806,37 +43806,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1438.99</v>
+        <v>1438.95</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1438.96</v>
+        <v>1438.93</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.75</v>
+        <v>1441.71</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.75</v>
+        <v>1443.71</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.75</v>
+        <v>1443.71</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.46</v>
+        <v>1452.41</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.71</v>
+        <v>1452.66</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.74</v>
+        <v>1453.69</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.47</v>
+        <v>1457.41</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463.09</v>
+        <v>1463</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.63</v>
+        <v>1465.55</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43923,52 +43923,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
     </row>
     <row r="18">
@@ -44040,52 +44040,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1410.31</v>
+        <v>1409.9</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1409.71</v>
+        <v>1406.88</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1411.66</v>
+        <v>1408.83</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1413.06</v>
+        <v>1410.23</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1413.06</v>
+        <v>1410.23</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1419.16</v>
+        <v>1416.32</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1419.33</v>
+        <v>1416.49</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1420.05</v>
+        <v>1417.21</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1422.67</v>
+        <v>1419.82</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1426.59</v>
+        <v>1423.73</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1428.37</v>
+        <v>1425.52</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1432.27</v>
+        <v>1429.47</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1442.21</v>
+        <v>1439.4</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1450.39</v>
+        <v>1447.59</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1453.66</v>
+        <v>1450.86</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1453.66</v>
+        <v>1450.86</v>
       </c>
     </row>
     <row r="19">
@@ -44157,52 +44157,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2563130.9</v>
+        <v>2562450.9</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2507051.4</v>
+        <v>2502080.6</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2434869.8</v>
+        <v>2430049.5</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2340324.7</v>
+        <v>2335697.1</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2340324.7</v>
+        <v>2335697.1</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1996687.1</v>
+        <v>1992758.4</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1853034.7</v>
+        <v>1849390.4</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1790416.7</v>
+        <v>1786898.2</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1538961.2</v>
+        <v>1535944.9</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1080026.6</v>
+        <v>1077920.6</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>842349.7</v>
+        <v>840707.4</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>618504.6</v>
+        <v>617293.3</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>371179</v>
+        <v>370457.1</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>264104.4</v>
+        <v>263593.6</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252596.6</v>
+        <v>252109.2</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52740</v>
+        <v>52638.2</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44217,19 +44217,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9100439.1</v>
+        <v>9099759.1</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9622570.6</v>
+        <v>9603524.300000001</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7179099.7</v>
+        <v>7164991.9</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2912059.9</v>
+        <v>2906378.4</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>569441</v>
+        <v>568341</v>
       </c>
     </row>
     <row r="20">
@@ -44301,52 +44301,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2441910.1</v>
+        <v>2441264.4</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2388516.7</v>
+        <v>2383790.4</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2371321.8</v>
+        <v>2366633.8</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2304073.1</v>
+        <v>2299522</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2304073.1</v>
+        <v>2299522</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1996687.1</v>
+        <v>1992758.4</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1853034.7</v>
+        <v>1849390.4</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1790416.7</v>
+        <v>1786898.2</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1538961.2</v>
+        <v>1535944.9</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1080026.6</v>
+        <v>1077920.6</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>842349.7</v>
+        <v>840707.4</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>618504.6</v>
+        <v>617293.3</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>371179</v>
+        <v>370457.1</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>264104.4</v>
+        <v>263593.6</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252596.6</v>
+        <v>252109.2</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52740</v>
+        <v>52638.2</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44361,19 +44361,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8610094.6</v>
+        <v>8609448.9</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9367984.699999999</v>
+        <v>9349468.199999999</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7179099.7</v>
+        <v>7164991.9</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2912059.9</v>
+        <v>2906378.4</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>569441</v>
+        <v>568341</v>
       </c>
     </row>
     <row r="21">
@@ -44445,52 +44445,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2126372.3</v>
+        <v>2125796.1</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2079292.5</v>
+        <v>2075175</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2058661.8</v>
+        <v>2054589.3</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1987977.2</v>
+        <v>1984048.5</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1987977.2</v>
+        <v>1984048.5</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1684027</v>
+        <v>1680713.9</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1540374.7</v>
+        <v>1537346</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1474320.9</v>
+        <v>1471424.7</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1224915.7</v>
+        <v>1222517.6</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>816934.9</v>
+        <v>815345.1</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>609399.3</v>
+        <v>608216.7</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>469865.1</v>
+        <v>468952.5</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>348906.3</v>
+        <v>348229.1</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249820.8</v>
+        <v>249338.8</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252596.6</v>
+        <v>252109.2</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52740</v>
+        <v>52638.2</v>
       </c>
     </row>
     <row r="22">
@@ -44562,46 +44562,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315537.9</v>
+        <v>315468.4</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>309224.2</v>
+        <v>308615.4</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312660</v>
+        <v>312044.5</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>316095.9</v>
+        <v>315473.5</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>316095.9</v>
+        <v>315473.5</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312660</v>
+        <v>312044.5</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312660</v>
+        <v>312044.5</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>316095.9</v>
+        <v>315473.5</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>314045.5</v>
+        <v>313427.3</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>263091.6</v>
+        <v>262575.5</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>232950.3</v>
+        <v>232490.7</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148639.5</v>
+        <v>148340.7</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22272.7</v>
+        <v>22227.9</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14283.6</v>
+        <v>14254.9</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44855,67 +44855,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1343.39)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1342.11)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1341.45)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1332.1)</f>
         <v/>
       </c>
     </row>
@@ -49522,43 +49522,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.798</v>
+        <v>46.842</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.283</v>
+        <v>46.328</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.798</v>
+        <v>46.842</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.312</v>
+        <v>47.357</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.312</v>
+        <v>47.357</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.798</v>
+        <v>46.842</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.798</v>
+        <v>46.842</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.312</v>
+        <v>47.357</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.312</v>
+        <v>47.357</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.283</v>
+        <v>46.328</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.37</v>
+        <v>31.401</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49577,7 +49577,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>500.376</v>
+        <v>500.853</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -56716,10 +56716,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>500.376</v>
+        <v>500.853</v>
       </c>
       <c r="F197" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -58493,7 +58493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64266,7 +64266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/010140_model.xlsx
+++ b/argus/kship/models/010140_model.xlsx
@@ -1648,55 +1648,55 @@
     <comment ref="AD40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 24413억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 24389억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3152억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AF40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23838억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3086억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23800억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3082억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AG40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 23666억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 23628억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3116억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AH40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 22958억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3150억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AI40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 22958억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3150억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AK40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 19928억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 19896억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3116억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AL40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 18494억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 18465억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3116억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AM40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 17869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 17841억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3150억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AN40" authorId="0" shapeId="0">
       <text>
         <t>역산: 모델 매출조선 − SLS 재구성 원화/100 − 매출조선신규 (모델 runoff_per_q 9999.72; 계약 스케줄 소수 3자리 반올림 차 포함)
-SLS 해양 원화 15359억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3134억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
+SLS 해양 원화 15335억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3130억 유지(패널 신규수주 체결 분기별 상계, net_panel)</t>
       </text>
     </comment>
     <comment ref="AC41" authorId="0" shapeId="0">
@@ -2323,49 +2323,49 @@
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38777억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 38775억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41518억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 41513억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44391억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 44383억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47428억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 47417억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50728억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 50715억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54090억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 54074억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57652억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 57633억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61477억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 -0.01억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 61457억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2383,49 +2383,49 @@
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 38777억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 38775억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 41518억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 41513억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 44391억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 44383억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 47428억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 47417억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 50728억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 50715억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 54090억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 54074억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 57652억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 57633억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 61477억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
+        <t>추정: 이자발생자산 61457억 × 1.23%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 11021억 × 5.58%(주석 이자비용 ÷ 평균 총차입금(2025Q3~2026Q2)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4170,55 +4170,55 @@
     </comment>
     <comment ref="AD38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 24413억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 24389억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 110931억) + 신규수주 매출 54억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3152억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AF38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23838억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3086억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23800억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 100931억) + 신규수주 매출 694억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3082억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AG38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 23666억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 23628억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 90931억) + 신규수주 매출 2394억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3116억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AH38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 22958억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 80932억) + 신규수주 매출 5034억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3150억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AI38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 22995억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 22958억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 70932억) + 신규수주 매출 8332억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3150억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AK38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 19928억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 19896억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 60932억) + 신규수주 매출 12015억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3116억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AL38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 18494억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3120억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 18465억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 50933억) + 신규수주 매출 15898억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3116억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AM38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 17869억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3155억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 17841억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 40933억) + 신규수주 매출 19805억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3150억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
     <comment ref="AN38" authorId="0" shapeId="0">
       <text>
-        <t>추정: SLS 해양 원화 15359억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3134억 유지(패널 신규수주 체결 분기별 상계, net_panel)
+        <t>추정: SLS 해양 원화 15335억(sls.by_quarter.marine_hedged_krw_m(헤지 70% 적용; origin 2026Q2 이후 체결 7건 SLS 유지 — 패널 신규수주와 체결 분기별 상계(net_panel))) + 원장 밖 잔고 소진 10000억(최근 4분기 '부문매출−SLS' 중위 10000억/분기, 잔여 30933억) + 신규수주 매출 23529억(forecast_panel.json.gz scenarios.base new_order_revenue(KRW_million÷100), status partial, calibrated=false, book-value proxy; 출처 사슬 new_order_revenue→covered_scope_new_revenue→ledger_signing_rate; origin 이후 공시 수주 체결 분기별 상계(net_panel: 2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억)) · origin 이후 공시 수주 SLS 3130억 유지(패널 신규수주 체결 분기별 상계, net_panel)
 [sls_link]</t>
       </text>
     </comment>
@@ -5376,7 +5376,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,201억 vs 54억 · 2027 12,516억 vs 16,454억 · 2028 12,530억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 2022Q1 조선 부문 매출(14972억) &gt; 연결 매출(14838억) — 부문표/파서 문제(yards 레인 확인) / 2025Q2 조선 부문 매출(31509억) &gt; 연결 매출(26830억) — 부문표/파서 문제(yards 레인 확인) / OPM 경로: 코호트 경로 없음 → 실측 중위 고정(원 타겟 전 분기 10.8% 상수(코호트 모드 reference_anchor); 경로 변화는 등급 없는 비중의 실측 중위 9.7% 채움에서만, 추정 구간 타겟 10.74%→10.80%) / 추정 매출조선 = 2026Q2 기준 잔고 소진분 + forecast_panel base new_order_revenue 신규수주 매출(미보정 book-value proxy, status partial; FY합 87,756억) — 보수/낙관은 scenarios 블록(합산 안 함) / origin 이후 공시 수주 7건 36,582억은 SLS 일정으로 전부 유지, 패널 신규수주에서 체결 분기별 상계(2026Q3 패널 32,424억 − 공시 29,860억 = 2,564억 · 2026Q4 패널 32,424억 − 공시 6,722억 = 25,702억) — 패널 base 신규 매출 −30,146억(2026 633억 · 2027 12,672억 · 2028 16,841억) · 패널 new_order_revenue 정의 불확실 — order_basis=positive_part_of_empirical_net_replenishment; includes_unseparated_FX_cancellations(경험적 순보충 분위의 통계 흐름, 공시 계약을 개별 반영하지 않음) · new_order_arrival=quarter_end; first_recognition_next_quarter · progress_curve=R1_smoothstep_unfitted; contract_period_not_actual_build_stage; 패널 기존잔고는 origin 이후 공시 8건을 제외(industry_axes.schedule_exclusions.not_known_at_origin); 2026Q3 공시 수주 29,860억 vs 패널 base 신규수주 32,424억(92%); 2026Q4 공시 수주 6,722억 vs 패널 base 신규수주 32,424억(21%). 공시 수주의 인식 시점·진행률(선형, 체결 분기부터)은 패널 가정과 다르다(calibrated=false) — FY 유지 SLS(공시) vs 패널 base 신규 매출(상계 후): 2026 4,199억 vs 54억 · 2027 12,498억 vs 16,454억 · 2028 12,512억 vs 71,248억 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 금융손익 실적→추정 단절: 최근 4분기 실적 -907/-773/-1348/-294(중위 -840억) → 추정 2026Q3 -51억(차 +789억, +94%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1279.2</v>
+        <v>1278.3</v>
       </c>
     </row>
     <row r="30">
@@ -6012,7 +6012,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.31</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="32">
@@ -6022,7 +6022,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.28</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="33">
@@ -6032,7 +6032,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.229</v>
+        <v>0.2288</v>
       </c>
     </row>
     <row r="34">
@@ -8586,35 +8586,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -8705,35 +8705,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -8824,35 +8824,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -8943,35 +8943,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -9062,35 +9062,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -9181,35 +9181,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -9300,35 +9300,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -9419,35 +9419,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9554,7 +9554,7 @@
         <v>19840</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>18300</v>
+        <v>16230</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -9736,7 +9736,7 @@
         <v>18440</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>17210</v>
+        <v>16230</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -9827,7 +9827,7 @@
         <v>21422.3</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>18892.7</v>
+        <v>18303.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -11386,36 +11386,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.00437145</v>
+        <v>-0.005932587</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.008110109000000001</v>
+        <v>-0.009156113</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.006996103</v>
+        <v>-0.002638186</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>0.00698306</v>
+        <v>0.005957914</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.005801761</v>
+        <v>-0.006374798</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.007028072</v>
+        <v>0.001810573</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.00143717</v>
+        <v>0.002828276</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>0.006252531</v>
+        <v>-0.005889397</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.003588791</v>
+        <v>-0.005333014</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.002485498</v>
+        <v>0.003123286</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -11514,36 +11514,36 @@
         <v/>
       </c>
       <c r="AC31" s="29" t="n">
-        <v>-0.00437145</v>
+        <v>-0.005932587</v>
       </c>
       <c r="AD31" s="29" t="n">
-        <v>-0.008110109000000001</v>
+        <v>-0.009156113</v>
       </c>
       <c r="AE31" s="30" t="n"/>
       <c r="AF31" s="29" t="n">
-        <v>0.006996103</v>
+        <v>-0.002638186</v>
       </c>
       <c r="AG31" s="29" t="n">
-        <v>0.00698306</v>
+        <v>0.005957914</v>
       </c>
       <c r="AH31" s="29" t="n">
-        <v>0.005801761</v>
+        <v>-0.006374798</v>
       </c>
       <c r="AI31" s="29" t="n">
-        <v>-0.007028072</v>
+        <v>0.001810573</v>
       </c>
       <c r="AJ31" s="30" t="n"/>
       <c r="AK31" s="29" t="n">
-        <v>-0.00143717</v>
+        <v>0.002828276</v>
       </c>
       <c r="AL31" s="29" t="n">
-        <v>0.006252531</v>
+        <v>-0.005889397</v>
       </c>
       <c r="AM31" s="29" t="n">
-        <v>-0.003588791</v>
+        <v>-0.005333014</v>
       </c>
       <c r="AN31" s="29" t="n">
-        <v>0.002485498</v>
+        <v>0.003123286</v>
       </c>
       <c r="AO31" s="30" t="n"/>
     </row>
@@ -11773,33 +11773,33 @@
         <v>0.125169959</v>
       </c>
       <c r="AD33" s="31" t="n">
-        <v>0.117646121</v>
+        <v>0.117568109</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="31" t="n">
-        <v>0.105707432</v>
+        <v>0.105600269</v>
       </c>
       <c r="AG33" s="31" t="n">
-        <v>0.100200857</v>
+        <v>0.10011466</v>
       </c>
       <c r="AH33" s="31" t="n">
-        <v>0.096259049</v>
+        <v>0.096191323</v>
       </c>
       <c r="AI33" s="31" t="n">
-        <v>0.095440652</v>
+        <v>0.095386637</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="31" t="n">
-        <v>0.088755933</v>
+        <v>0.08872153300000001</v>
       </c>
       <c r="AL33" s="31" t="n">
-        <v>0.086346121</v>
+        <v>0.086323095</v>
       </c>
       <c r="AM33" s="31" t="n">
-        <v>0.08538699399999999</v>
+        <v>0.085371683</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>0.08080527899999999</v>
+        <v>0.08079976899999999</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -11901,33 +11901,33 @@
         <v>0.07712440299999999</v>
       </c>
       <c r="AD34" s="31" t="n">
-        <v>0.075721495</v>
+        <v>0.075671561</v>
       </c>
       <c r="AE34" s="25" t="n"/>
       <c r="AF34" s="31" t="n">
-        <v>0.070689214</v>
+        <v>0.0706159</v>
       </c>
       <c r="AG34" s="31" t="n">
-        <v>0.06919837</v>
+        <v>0.06913501900000001</v>
       </c>
       <c r="AH34" s="31" t="n">
-        <v>0.068403715</v>
+        <v>0.06835073899999999</v>
       </c>
       <c r="AI34" s="31" t="n">
-        <v>0.069590609</v>
+        <v>0.069545232</v>
       </c>
       <c r="AJ34" s="25" t="n"/>
       <c r="AK34" s="31" t="n">
-        <v>0.066280122</v>
+        <v>0.066248667</v>
       </c>
       <c r="AL34" s="31" t="n">
-        <v>0.065840098</v>
+        <v>0.065816478</v>
       </c>
       <c r="AM34" s="31" t="n">
-        <v>0.066361038</v>
+        <v>0.066343266</v>
       </c>
       <c r="AN34" s="31" t="n">
-        <v>0.06392103</v>
+        <v>0.06391084700000001</v>
       </c>
       <c r="AO34" s="25" t="n"/>
     </row>
@@ -12624,33 +12624,33 @@
         <v>11046.034703</v>
       </c>
       <c r="AD40" s="29" t="n">
-        <v>13154.383342</v>
+        <v>13151.870493</v>
       </c>
       <c r="AE40" s="30" t="n"/>
       <c r="AF40" s="29" t="n">
-        <v>13085.925631</v>
+        <v>13081.433729</v>
       </c>
       <c r="AG40" s="29" t="n">
-        <v>13120.06405</v>
+        <v>13115.524214</v>
       </c>
       <c r="AH40" s="29" t="n">
-        <v>13154.419254</v>
+        <v>13149.833552</v>
       </c>
       <c r="AI40" s="29" t="n">
-        <v>13154.433024</v>
+        <v>13149.847299</v>
       </c>
       <c r="AJ40" s="30" t="n"/>
       <c r="AK40" s="29" t="n">
-        <v>13120.252468</v>
+        <v>13115.709631</v>
       </c>
       <c r="AL40" s="29" t="n">
-        <v>13120.141522</v>
+        <v>13115.602037</v>
       </c>
       <c r="AM40" s="29" t="n">
-        <v>13154.504581</v>
+        <v>13149.910892</v>
       </c>
       <c r="AN40" s="29" t="n">
-        <v>13133.981165</v>
+        <v>13129.421694</v>
       </c>
       <c r="AO40" s="30" t="n"/>
     </row>
@@ -12925,39 +12925,39 @@
         <v>0.099410028</v>
       </c>
       <c r="AD42" s="31" t="n">
-        <v>0.099458957</v>
+        <v>0.09945891</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE38,"")</f>
         <v/>
       </c>
       <c r="AF42" s="31" t="n">
-        <v>0.09945904</v>
+        <v>0.099458963</v>
       </c>
       <c r="AG42" s="31" t="n">
-        <v>0.099690182</v>
+        <v>0.099690023</v>
       </c>
       <c r="AH42" s="31" t="n">
-        <v>0.099805097</v>
+        <v>0.099804988</v>
       </c>
       <c r="AI42" s="31" t="n">
-        <v>0.099804897</v>
+        <v>0.099805038</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ38,"")</f>
         <v/>
       </c>
       <c r="AK42" s="31" t="n">
-        <v>0.099980688</v>
+        <v>0.099980554</v>
       </c>
       <c r="AL42" s="31" t="n">
-        <v>0.09998074</v>
+        <v>0.099980547</v>
       </c>
       <c r="AM42" s="31" t="n">
-        <v>0.099980597</v>
+        <v>0.09998056499999999</v>
       </c>
       <c r="AN42" s="31" t="n">
-        <v>0.09998056800000001</v>
+        <v>0.09998072199999999</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO38,"")</f>
@@ -13302,11 +13302,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>18300</v>
+        <v>16230</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 18,170원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 17,320원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -13342,7 +13342,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -13577,7 +13577,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.219999960927751</v>
+        <v>0.2199999413502922</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -13616,7 +13616,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.04463848126112946</v>
+        <v>0.04463849906162166</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.01229708144005519</v>
+        <v>0.01229731422239133</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -13733,7 +13733,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.05576809408005337</v>
+        <v>0.05576955744632621</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -25279,7 +25279,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42516,37 +42516,37 @@
         <v>1663.4</v>
       </c>
       <c r="X5" s="26" t="n">
-        <v>1817.47</v>
+        <v>1817.631</v>
       </c>
       <c r="Y5" s="26" t="n">
-        <v>1778.463</v>
+        <v>1778.623</v>
       </c>
       <c r="Z5" s="26" t="n">
-        <v>1724.872</v>
+        <v>1725.034</v>
       </c>
       <c r="AA5" s="26" t="n">
-        <v>1656.256</v>
+        <v>1656.42</v>
       </c>
       <c r="AB5" s="26" t="n">
-        <v>1656.256</v>
+        <v>1656.42</v>
       </c>
       <c r="AC5" s="26" t="n">
-        <v>1406.999</v>
+        <v>1407.16</v>
       </c>
       <c r="AD5" s="26" t="n">
-        <v>1305.612</v>
+        <v>1305.773</v>
       </c>
       <c r="AE5" s="26" t="n">
-        <v>1260.857</v>
+        <v>1261.02</v>
       </c>
       <c r="AF5" s="26" t="n">
-        <v>1081.789</v>
+        <v>1081.952</v>
       </c>
       <c r="AG5" s="26" t="n">
-        <v>757.11</v>
+        <v>757.27</v>
       </c>
       <c r="AH5" s="26" t="n">
-        <v>589.7569999999999</v>
+        <v>589.865</v>
       </c>
       <c r="AI5" s="26" t="n">
         <v>431.834</v>
@@ -42576,16 +42576,16 @@
         <v>3538.059</v>
       </c>
       <c r="AR5" s="26" t="n">
-        <v>6362.735</v>
+        <v>6362.896</v>
       </c>
       <c r="AS5" s="26" t="n">
-        <v>6815.847</v>
+        <v>6816.497</v>
       </c>
       <c r="AT5" s="26" t="n">
-        <v>5055.257</v>
+        <v>5055.905</v>
       </c>
       <c r="AU5" s="26" t="n">
-        <v>2036.07</v>
+        <v>2036.338</v>
       </c>
       <c r="AV5" s="26" t="n">
         <v>392.138</v>
@@ -42660,37 +42660,37 @@
         <v>1574.265</v>
       </c>
       <c r="X6" s="26" t="n">
-        <v>1728.334</v>
+        <v>1728.496</v>
       </c>
       <c r="Y6" s="26" t="n">
-        <v>1691.265</v>
+        <v>1691.425</v>
       </c>
       <c r="Z6" s="26" t="n">
-        <v>1677.704</v>
+        <v>1677.866</v>
       </c>
       <c r="AA6" s="26" t="n">
-        <v>1628.955</v>
+        <v>1629.119</v>
       </c>
       <c r="AB6" s="26" t="n">
-        <v>1628.955</v>
+        <v>1629.119</v>
       </c>
       <c r="AC6" s="26" t="n">
-        <v>1406.999</v>
+        <v>1407.16</v>
       </c>
       <c r="AD6" s="26" t="n">
-        <v>1305.612</v>
+        <v>1305.773</v>
       </c>
       <c r="AE6" s="26" t="n">
-        <v>1260.857</v>
+        <v>1261.02</v>
       </c>
       <c r="AF6" s="26" t="n">
-        <v>1081.789</v>
+        <v>1081.952</v>
       </c>
       <c r="AG6" s="26" t="n">
-        <v>757.11</v>
+        <v>757.27</v>
       </c>
       <c r="AH6" s="26" t="n">
-        <v>589.7569999999999</v>
+        <v>589.865</v>
       </c>
       <c r="AI6" s="26" t="n">
         <v>431.834</v>
@@ -42720,16 +42720,16 @@
         <v>2891.417</v>
       </c>
       <c r="AR6" s="26" t="n">
-        <v>6009.1</v>
+        <v>6009.262</v>
       </c>
       <c r="AS6" s="26" t="n">
-        <v>6626.879</v>
+        <v>6627.529</v>
       </c>
       <c r="AT6" s="26" t="n">
-        <v>5055.257</v>
+        <v>5055.905</v>
       </c>
       <c r="AU6" s="26" t="n">
-        <v>2036.07</v>
+        <v>2036.338</v>
       </c>
       <c r="AV6" s="26" t="n">
         <v>392.138</v>
@@ -43134,37 +43134,37 @@
         <v>722.163</v>
       </c>
       <c r="X10" s="26" t="n">
-        <v>833.139</v>
+        <v>833.301</v>
       </c>
       <c r="Y10" s="26" t="n">
-        <v>815.5309999999999</v>
+        <v>815.691</v>
       </c>
       <c r="Z10" s="26" t="n">
-        <v>792.239</v>
+        <v>792.401</v>
       </c>
       <c r="AA10" s="26" t="n">
-        <v>733.76</v>
+        <v>733.923</v>
       </c>
       <c r="AB10" s="26" t="n">
-        <v>733.76</v>
+        <v>733.923</v>
       </c>
       <c r="AC10" s="26" t="n">
-        <v>691.8630000000001</v>
+        <v>692.025</v>
       </c>
       <c r="AD10" s="26" t="n">
-        <v>665.298</v>
+        <v>665.4589999999999</v>
       </c>
       <c r="AE10" s="26" t="n">
-        <v>625.842</v>
+        <v>626.006</v>
       </c>
       <c r="AF10" s="26" t="n">
-        <v>448.244</v>
+        <v>448.407</v>
       </c>
       <c r="AG10" s="26" t="n">
-        <v>315.92</v>
+        <v>316.08</v>
       </c>
       <c r="AH10" s="26" t="n">
-        <v>199.998</v>
+        <v>200.107</v>
       </c>
       <c r="AI10" s="26" t="n">
         <v>80.166</v>
@@ -43176,16 +43176,16 @@
         <v>845.6369999999999</v>
       </c>
       <c r="AR10" s="26" t="n">
-        <v>2584.045</v>
+        <v>2584.207</v>
       </c>
       <c r="AS10" s="26" t="n">
-        <v>3075.29</v>
+        <v>3075.938</v>
       </c>
       <c r="AT10" s="26" t="n">
-        <v>2431.247</v>
+        <v>2431.897</v>
       </c>
       <c r="AU10" s="26" t="n">
-        <v>596.0839999999999</v>
+        <v>596.353</v>
       </c>
     </row>
     <row r="11">
@@ -43446,37 +43446,37 @@
         <v>1574.265</v>
       </c>
       <c r="X13" s="26" t="n">
-        <v>1728.334</v>
+        <v>1728.496</v>
       </c>
       <c r="Y13" s="26" t="n">
-        <v>1691.265</v>
+        <v>1691.425</v>
       </c>
       <c r="Z13" s="26" t="n">
-        <v>1677.704</v>
+        <v>1677.866</v>
       </c>
       <c r="AA13" s="26" t="n">
-        <v>1628.955</v>
+        <v>1629.119</v>
       </c>
       <c r="AB13" s="26" t="n">
-        <v>1628.955</v>
+        <v>1629.119</v>
       </c>
       <c r="AC13" s="26" t="n">
-        <v>1406.999</v>
+        <v>1407.16</v>
       </c>
       <c r="AD13" s="26" t="n">
-        <v>1305.612</v>
+        <v>1305.773</v>
       </c>
       <c r="AE13" s="26" t="n">
-        <v>1260.857</v>
+        <v>1261.02</v>
       </c>
       <c r="AF13" s="26" t="n">
-        <v>1081.789</v>
+        <v>1081.952</v>
       </c>
       <c r="AG13" s="26" t="n">
-        <v>757.11</v>
+        <v>757.27</v>
       </c>
       <c r="AH13" s="26" t="n">
-        <v>589.7569999999999</v>
+        <v>589.865</v>
       </c>
       <c r="AI13" s="26" t="n">
         <v>431.834</v>
@@ -43506,16 +43506,16 @@
         <v>2294.984</v>
       </c>
       <c r="AR13" s="26" t="n">
-        <v>5485.161</v>
+        <v>5485.323</v>
       </c>
       <c r="AS13" s="26" t="n">
-        <v>6626.879</v>
+        <v>6627.529</v>
       </c>
       <c r="AT13" s="26" t="n">
-        <v>5055.257</v>
+        <v>5055.905</v>
       </c>
       <c r="AU13" s="26" t="n">
-        <v>2036.07</v>
+        <v>2036.338</v>
       </c>
       <c r="AV13" s="26" t="n">
         <v>392.138</v>
@@ -43806,37 +43806,37 @@
         <v>1442.98</v>
       </c>
       <c r="X16" s="13" t="n">
-        <v>1438.95</v>
+        <v>1438.83</v>
       </c>
       <c r="Y16" s="13" t="n">
-        <v>1438.93</v>
+        <v>1438.8</v>
       </c>
       <c r="Z16" s="13" t="n">
-        <v>1441.71</v>
+        <v>1441.58</v>
       </c>
       <c r="AA16" s="13" t="n">
-        <v>1443.71</v>
+        <v>1443.57</v>
       </c>
       <c r="AB16" s="13" t="n">
-        <v>1443.71</v>
+        <v>1443.57</v>
       </c>
       <c r="AC16" s="13" t="n">
-        <v>1452.41</v>
+        <v>1452.25</v>
       </c>
       <c r="AD16" s="13" t="n">
-        <v>1452.66</v>
+        <v>1452.48</v>
       </c>
       <c r="AE16" s="13" t="n">
-        <v>1453.69</v>
+        <v>1453.5</v>
       </c>
       <c r="AF16" s="13" t="n">
-        <v>1457.41</v>
+        <v>1457.19</v>
       </c>
       <c r="AG16" s="13" t="n">
-        <v>1463</v>
+        <v>1462.69</v>
       </c>
       <c r="AH16" s="13" t="n">
-        <v>1465.55</v>
+        <v>1465.28</v>
       </c>
       <c r="AI16" s="13" t="n">
         <v>1471.2</v>
@@ -43923,52 +43923,52 @@
         <v>1418.75</v>
       </c>
       <c r="X17" s="13" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="Y17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AA17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AC17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AD17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AK17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM17" s="13" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
     </row>
     <row r="18">
@@ -44040,52 +44040,52 @@
         <v>1435.71</v>
       </c>
       <c r="X18" s="13" t="n">
-        <v>1409.9</v>
+        <v>1408.42</v>
       </c>
       <c r="Y18" s="13" t="n">
-        <v>1406.88</v>
+        <v>1404.49</v>
       </c>
       <c r="Z18" s="13" t="n">
-        <v>1408.83</v>
+        <v>1406.44</v>
       </c>
       <c r="AA18" s="13" t="n">
-        <v>1410.23</v>
+        <v>1407.83</v>
       </c>
       <c r="AB18" s="13" t="n">
-        <v>1410.23</v>
+        <v>1407.83</v>
       </c>
       <c r="AC18" s="13" t="n">
-        <v>1416.32</v>
+        <v>1413.91</v>
       </c>
       <c r="AD18" s="13" t="n">
-        <v>1416.49</v>
+        <v>1414.07</v>
       </c>
       <c r="AE18" s="13" t="n">
-        <v>1417.21</v>
+        <v>1414.78</v>
       </c>
       <c r="AF18" s="13" t="n">
-        <v>1419.82</v>
+        <v>1417.37</v>
       </c>
       <c r="AG18" s="13" t="n">
-        <v>1423.73</v>
+        <v>1421.22</v>
       </c>
       <c r="AH18" s="13" t="n">
-        <v>1425.52</v>
+        <v>1423.03</v>
       </c>
       <c r="AI18" s="13" t="n">
-        <v>1429.47</v>
+        <v>1427.17</v>
       </c>
       <c r="AJ18" s="13" t="n">
-        <v>1439.4</v>
+        <v>1437.11</v>
       </c>
       <c r="AK18" s="13" t="n">
-        <v>1447.59</v>
+        <v>1445.29</v>
       </c>
       <c r="AL18" s="13" t="n">
-        <v>1450.86</v>
+        <v>1448.56</v>
       </c>
       <c r="AM18" s="13" t="n">
-        <v>1450.86</v>
+        <v>1448.56</v>
       </c>
     </row>
     <row r="19">
@@ -44157,52 +44157,52 @@
         <v>2388165.2</v>
       </c>
       <c r="X19" s="18" t="n">
-        <v>2562450.9</v>
+        <v>2559996.8</v>
       </c>
       <c r="Y19" s="18" t="n">
-        <v>2502080.6</v>
+        <v>2498062.6</v>
       </c>
       <c r="Z19" s="18" t="n">
-        <v>2430049.5</v>
+        <v>2426155.2</v>
       </c>
       <c r="AA19" s="18" t="n">
-        <v>2335697.1</v>
+        <v>2331960.9</v>
       </c>
       <c r="AB19" s="18" t="n">
-        <v>2335697.1</v>
+        <v>2331960.9</v>
       </c>
       <c r="AC19" s="18" t="n">
-        <v>1992758.4</v>
+        <v>1989593.6</v>
       </c>
       <c r="AD19" s="18" t="n">
-        <v>1849390.4</v>
+        <v>1846458.3</v>
       </c>
       <c r="AE19" s="18" t="n">
-        <v>1786898.2</v>
+        <v>1784069.5</v>
       </c>
       <c r="AF19" s="18" t="n">
-        <v>1535944.9</v>
+        <v>1533527.2</v>
       </c>
       <c r="AG19" s="18" t="n">
-        <v>1077920.6</v>
+        <v>1076246.6</v>
       </c>
       <c r="AH19" s="18" t="n">
-        <v>840707.4</v>
+        <v>839397</v>
       </c>
       <c r="AI19" s="18" t="n">
-        <v>617293.3</v>
+        <v>616302.2</v>
       </c>
       <c r="AJ19" s="18" t="n">
-        <v>370457.1</v>
+        <v>369866.4</v>
       </c>
       <c r="AK19" s="18" t="n">
-        <v>263593.6</v>
+        <v>263175.7</v>
       </c>
       <c r="AL19" s="18" t="n">
-        <v>252109.2</v>
+        <v>251710.4</v>
       </c>
       <c r="AM19" s="18" t="n">
-        <v>52638.2</v>
+        <v>52554.9</v>
       </c>
       <c r="AN19" s="18" t="n">
         <v>337530.2</v>
@@ -44217,19 +44217,19 @@
         <v>4956225.8</v>
       </c>
       <c r="AR19" s="18" t="n">
-        <v>9099759.1</v>
+        <v>9097305</v>
       </c>
       <c r="AS19" s="18" t="n">
-        <v>9603524.300000001</v>
+        <v>9588139.6</v>
       </c>
       <c r="AT19" s="18" t="n">
-        <v>7164991.9</v>
+        <v>7153648.6</v>
       </c>
       <c r="AU19" s="18" t="n">
-        <v>2906378.4</v>
+        <v>2901812.2</v>
       </c>
       <c r="AV19" s="18" t="n">
-        <v>568341</v>
+        <v>567441</v>
       </c>
     </row>
     <row r="20">
@@ -44301,52 +44301,52 @@
         <v>2264929.3</v>
       </c>
       <c r="X20" s="18" t="n">
-        <v>2441264.4</v>
+        <v>2438933.9</v>
       </c>
       <c r="Y20" s="18" t="n">
-        <v>2383790.4</v>
+        <v>2379972.5</v>
       </c>
       <c r="Z20" s="18" t="n">
-        <v>2366633.8</v>
+        <v>2362847.7</v>
       </c>
       <c r="AA20" s="18" t="n">
-        <v>2299522</v>
+        <v>2295848.6</v>
       </c>
       <c r="AB20" s="18" t="n">
-        <v>2299522</v>
+        <v>2295848.6</v>
       </c>
       <c r="AC20" s="18" t="n">
-        <v>1992758.4</v>
+        <v>1989593.6</v>
       </c>
       <c r="AD20" s="18" t="n">
-        <v>1849390.4</v>
+        <v>1846458.3</v>
       </c>
       <c r="AE20" s="18" t="n">
-        <v>1786898.2</v>
+        <v>1784069.5</v>
       </c>
       <c r="AF20" s="18" t="n">
-        <v>1535944.9</v>
+        <v>1533527.2</v>
       </c>
       <c r="AG20" s="18" t="n">
-        <v>1077920.6</v>
+        <v>1076246.6</v>
       </c>
       <c r="AH20" s="18" t="n">
-        <v>840707.4</v>
+        <v>839397</v>
       </c>
       <c r="AI20" s="18" t="n">
-        <v>617293.3</v>
+        <v>616302.2</v>
       </c>
       <c r="AJ20" s="18" t="n">
-        <v>370457.1</v>
+        <v>369866.4</v>
       </c>
       <c r="AK20" s="18" t="n">
-        <v>263593.6</v>
+        <v>263175.7</v>
       </c>
       <c r="AL20" s="18" t="n">
-        <v>252109.2</v>
+        <v>251710.4</v>
       </c>
       <c r="AM20" s="18" t="n">
-        <v>52638.2</v>
+        <v>52554.9</v>
       </c>
       <c r="AN20" s="18" t="n">
         <v>188345.4</v>
@@ -44361,19 +44361,19 @@
         <v>4062931.9</v>
       </c>
       <c r="AR20" s="18" t="n">
-        <v>8609448.9</v>
+        <v>8607118.4</v>
       </c>
       <c r="AS20" s="18" t="n">
-        <v>9349468.199999999</v>
+        <v>9334517.4</v>
       </c>
       <c r="AT20" s="18" t="n">
-        <v>7164991.9</v>
+        <v>7153648.6</v>
       </c>
       <c r="AU20" s="18" t="n">
-        <v>2906378.4</v>
+        <v>2901812.2</v>
       </c>
       <c r="AV20" s="18" t="n">
-        <v>568341</v>
+        <v>567441</v>
       </c>
     </row>
     <row r="21">
@@ -44445,52 +44445,52 @@
         <v>2160295.9</v>
       </c>
       <c r="X21" s="18" t="n">
-        <v>2125796.1</v>
+        <v>2123716.3</v>
       </c>
       <c r="Y21" s="18" t="n">
-        <v>2075175</v>
+        <v>2071806.2</v>
       </c>
       <c r="Z21" s="18" t="n">
-        <v>2054589.3</v>
+        <v>2051257.3</v>
       </c>
       <c r="AA21" s="18" t="n">
-        <v>1984048.5</v>
+        <v>1980834.1</v>
       </c>
       <c r="AB21" s="18" t="n">
-        <v>1984048.5</v>
+        <v>1980834.1</v>
       </c>
       <c r="AC21" s="18" t="n">
-        <v>1680713.9</v>
+        <v>1678003.2</v>
       </c>
       <c r="AD21" s="18" t="n">
-        <v>1537346</v>
+        <v>1534867.9</v>
       </c>
       <c r="AE21" s="18" t="n">
-        <v>1471424.7</v>
+        <v>1469055</v>
       </c>
       <c r="AF21" s="18" t="n">
-        <v>1222517.6</v>
+        <v>1220555.6</v>
       </c>
       <c r="AG21" s="18" t="n">
-        <v>815345.1</v>
+        <v>814044.3</v>
       </c>
       <c r="AH21" s="18" t="n">
-        <v>608216.7</v>
+        <v>607249.1</v>
       </c>
       <c r="AI21" s="18" t="n">
-        <v>468952.5</v>
+        <v>468205.9</v>
       </c>
       <c r="AJ21" s="18" t="n">
-        <v>348229.1</v>
+        <v>347675.1</v>
       </c>
       <c r="AK21" s="18" t="n">
-        <v>249338.8</v>
+        <v>248944.4</v>
       </c>
       <c r="AL21" s="18" t="n">
-        <v>252109.2</v>
+        <v>251710.4</v>
       </c>
       <c r="AM21" s="18" t="n">
-        <v>52638.2</v>
+        <v>52554.9</v>
       </c>
     </row>
     <row r="22">
@@ -44562,46 +44562,46 @@
         <v>104633.4</v>
       </c>
       <c r="X22" s="18" t="n">
-        <v>315468.4</v>
+        <v>315217.5</v>
       </c>
       <c r="Y22" s="18" t="n">
-        <v>308615.4</v>
+        <v>308166.3</v>
       </c>
       <c r="Z22" s="18" t="n">
-        <v>312044.5</v>
+        <v>311590.4</v>
       </c>
       <c r="AA22" s="18" t="n">
-        <v>315473.5</v>
+        <v>315014.5</v>
       </c>
       <c r="AB22" s="18" t="n">
-        <v>315473.5</v>
+        <v>315014.5</v>
       </c>
       <c r="AC22" s="18" t="n">
-        <v>312044.5</v>
+        <v>311590.4</v>
       </c>
       <c r="AD22" s="18" t="n">
-        <v>312044.5</v>
+        <v>311590.4</v>
       </c>
       <c r="AE22" s="18" t="n">
-        <v>315473.5</v>
+        <v>315014.5</v>
       </c>
       <c r="AF22" s="18" t="n">
-        <v>313427.3</v>
+        <v>312971.6</v>
       </c>
       <c r="AG22" s="18" t="n">
-        <v>262575.5</v>
+        <v>262202.3</v>
       </c>
       <c r="AH22" s="18" t="n">
-        <v>232490.7</v>
+        <v>232147.9</v>
       </c>
       <c r="AI22" s="18" t="n">
-        <v>148340.7</v>
+        <v>148096.3</v>
       </c>
       <c r="AJ22" s="18" t="n">
-        <v>22227.9</v>
+        <v>22191.3</v>
       </c>
       <c r="AK22" s="18" t="n">
-        <v>14254.9</v>
+        <v>14231.4</v>
       </c>
       <c r="AL22" s="18" t="n">
         <v>0</v>
@@ -44855,67 +44855,67 @@
         <v/>
       </c>
       <c r="X28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1342.11)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(X$1,변수H,0),0),1337.49)</f>
         <v/>
       </c>
       <c r="Y28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Y$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="Z28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(Z$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AA28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AA$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AB28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AB$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AC28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AC$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AD28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AD$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AE28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AE$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AF28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AF$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AG28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AG$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AH28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AH$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AI28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AI$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AJ28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AJ$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AK28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AK$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AL28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AL$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
       <c r="AM28" s="13">
-        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1332.1)</f>
+        <f>IFERROR(VLOOKUP(" 원/달러(평균)",환율,MATCH(AM$1,변수H,0),0),1324.45)</f>
         <v/>
       </c>
     </row>
@@ -49522,43 +49522,43 @@
         </is>
       </c>
       <c r="X84" s="26" t="n">
-        <v>46.842</v>
+        <v>47.004</v>
       </c>
       <c r="Y84" s="26" t="n">
-        <v>46.328</v>
+        <v>46.488</v>
       </c>
       <c r="Z84" s="26" t="n">
-        <v>46.842</v>
+        <v>47.004</v>
       </c>
       <c r="AA84" s="26" t="n">
-        <v>47.357</v>
+        <v>47.521</v>
       </c>
       <c r="AB84" s="26" t="n">
-        <v>47.357</v>
+        <v>47.521</v>
       </c>
       <c r="AC84" s="26" t="n">
-        <v>46.842</v>
+        <v>47.004</v>
       </c>
       <c r="AD84" s="26" t="n">
-        <v>46.842</v>
+        <v>47.004</v>
       </c>
       <c r="AE84" s="26" t="n">
-        <v>47.357</v>
+        <v>47.521</v>
       </c>
       <c r="AF84" s="26" t="n">
-        <v>47.357</v>
+        <v>47.521</v>
       </c>
       <c r="AG84" s="26" t="n">
-        <v>46.328</v>
+        <v>46.488</v>
       </c>
       <c r="AH84" s="26" t="n">
-        <v>31.401</v>
+        <v>31.507</v>
       </c>
       <c r="AX84" s="35" t="n">
         <v>0</v>
       </c>
       <c r="AY84" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AZ84" s="42" t="n">
         <v>1</v>
@@ -49577,7 +49577,7 @@
         </is>
       </c>
       <c r="BD84" s="26" t="n">
-        <v>500.853</v>
+        <v>502.583</v>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -55167,7 +55167,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -56441,7 +56441,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>④호황</t>
+          <t>③중마진</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -56716,10 +56716,10 @@
         <v>672200</v>
       </c>
       <c r="E197" t="n">
-        <v>500.853</v>
+        <v>502.583</v>
       </c>
       <c r="F197" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 1%, ③중마진 69%, ④호황 30%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
+          <t>⚠ 코호트 기본 모드 reference_anchor: 2025~ 수주 물량(백만$) 판정 ⑤초호황 100%. reference_anchor 는 수주연도 → 등급(≤2020 ③중마진 · 2021 ④호황 · 2022~ ⑤초호황; 출처 사용자 레퍼런스 모델 HD현대미포 SLS 의 클락슨 기반 판정을 건조기간 2~3년으로 되돌린 표 — 외부 신조선가 지수 미보유). ledger_relative 는 원장 내부 상대 등급(2025~ 판정 ②BEP 1%, ③중마진 72%, ④호황 27%; 2021 이후 절대 호황 수준 미반영). 대안 모드는 by_cohort_alt·target_opm_alt·calibration_alt 에 함께 저장. 타겟 OPM 은 기본 모드 기준이며 calibrated_shift(실측 − 타겟)로 실측 OPM 에 맞춘다 — 음수일 수 있다</t>
         </is>
       </c>
     </row>
@@ -58493,7 +58493,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -64266,7 +64266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
